--- a/data/hrm_sync_actual_2.xlsx
+++ b/data/hrm_sync_actual_2.xlsx
@@ -70,280 +70,304 @@
     <t>Trạng thái duyệt</t>
   </si>
   <si>
+    <t>02223526</t>
+  </si>
+  <si>
+    <t>Nguyễn Thiên Phú</t>
+  </si>
+  <si>
+    <t>Plastic Extrusion</t>
+  </si>
+  <si>
+    <t>Pulverize</t>
+  </si>
+  <si>
+    <t>Tăng cường sản xuất</t>
+  </si>
+  <si>
+    <t>Nguyễn Chí Cường</t>
+  </si>
+  <si>
+    <t>Thân Trọng Tuấn</t>
+  </si>
+  <si>
+    <t>19/09/2026 22:00:00</t>
+  </si>
+  <si>
+    <t>20/09/2026 06:00:00</t>
+  </si>
+  <si>
+    <t>Bằng KH</t>
+  </si>
+  <si>
+    <t>Đã duyệt</t>
+  </si>
+  <si>
+    <t>02644057</t>
+  </si>
+  <si>
+    <t>Phạm Văn Công</t>
+  </si>
+  <si>
+    <t>tăng ca đáp ứng tiến độ sản xuất</t>
+  </si>
+  <si>
+    <t>17/09/2026 20:30:00</t>
+  </si>
+  <si>
+    <t>17/09/2026 22:00:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tăng cường sản xuất </t>
+  </si>
+  <si>
+    <t>12/09/2026 06:00:00</t>
+  </si>
+  <si>
+    <t>12/09/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>14/09/2026 20:30:00</t>
+  </si>
+  <si>
+    <t>14/09/2026 22:00:00</t>
+  </si>
+  <si>
+    <t>21/09/2026 12:30:00</t>
+  </si>
+  <si>
+    <t>21/09/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>23/09/2026 12:30:00</t>
+  </si>
+  <si>
+    <t>23/09/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>16/09/2026 20:30:00</t>
+  </si>
+  <si>
+    <t>16/09/2026 22:00:00</t>
+  </si>
+  <si>
+    <t>22/09/2026 12:30:00</t>
+  </si>
+  <si>
+    <t>22/09/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>18/09/2026 20:30:00</t>
+  </si>
+  <si>
+    <t>18/09/2026 22:00:00</t>
+  </si>
+  <si>
+    <t>02222350</t>
+  </si>
+  <si>
+    <t>Hoàng Văn Nguyên</t>
+  </si>
+  <si>
+    <t>19/09/2026 06:00:00</t>
+  </si>
+  <si>
+    <t>19/09/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>02020947</t>
+  </si>
+  <si>
+    <t>Nguyễn Hoàng Duy</t>
+  </si>
+  <si>
+    <t>chuẩn bị kiểm kê</t>
+  </si>
+  <si>
+    <t>23/09/2026 16:30:00</t>
+  </si>
+  <si>
+    <t>23/09/2026 18:00:00</t>
+  </si>
+  <si>
+    <t>02243654</t>
+  </si>
+  <si>
+    <t>Lưu Văn Giang</t>
+  </si>
+  <si>
+    <t>Tăng Cường Sản Xuất</t>
+  </si>
+  <si>
+    <t>15/09/2026 20:30:00</t>
+  </si>
+  <si>
+    <t>15/09/2026 22:00:00</t>
+  </si>
+  <si>
+    <t>02644075</t>
+  </si>
+  <si>
+    <t>Huỳnh Đại Nhân</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tăng cường sản xuất </t>
+  </si>
+  <si>
+    <t>14/09/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>14/09/2026 15:30:00</t>
+  </si>
+  <si>
+    <t>12/09/2026 22:00:00</t>
+  </si>
+  <si>
+    <t>13/09/2026 06:00:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">chuẩn bị kiểm kê </t>
+  </si>
+  <si>
+    <t>24/09/2026 16:30:00</t>
+  </si>
+  <si>
+    <t>24/09/2026 18:00:00</t>
+  </si>
+  <si>
+    <t>02644066</t>
+  </si>
+  <si>
+    <t>Nguyễn Hữu Tình</t>
+  </si>
+  <si>
+    <t>tang ca van hanh may nghien</t>
+  </si>
+  <si>
+    <t>23/09/2026 20:30:00</t>
+  </si>
+  <si>
+    <t>23/09/2026 22:00:00</t>
+  </si>
+  <si>
+    <t>Chờ cấp trên gian tiếp</t>
+  </si>
+  <si>
+    <t>tang ca cat ong nhua</t>
+  </si>
+  <si>
+    <t>18/09/2026 12:30:00</t>
+  </si>
+  <si>
+    <t>18/09/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>22/09/2026 20:30:00</t>
+  </si>
+  <si>
+    <t>22/09/2026 22:00:00</t>
+  </si>
+  <si>
+    <t>02223605</t>
+  </si>
+  <si>
+    <t>Võ Minh Bắc</t>
+  </si>
+  <si>
+    <t>tăng cường sản xuất</t>
+  </si>
+  <si>
+    <t>22/09/2026 16:30:00</t>
+  </si>
+  <si>
+    <t>22/09/2026 18:00:00</t>
+  </si>
+  <si>
+    <t>24/09/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>24/09/2026 15:30:00</t>
+  </si>
+  <si>
+    <t>17/09/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>17/09/2026 15:30:00</t>
+  </si>
+  <si>
+    <t>21/09/2026 20:30:00</t>
+  </si>
+  <si>
+    <t>21/09/2026 22:00:00</t>
+  </si>
+  <si>
+    <t>23/09/2026 15:30:00</t>
+  </si>
+  <si>
+    <t>lắp đặt thiết bị</t>
+  </si>
+  <si>
+    <t>12/09/2026 07:45:00</t>
+  </si>
+  <si>
+    <t>12/09/2026 16:30:00</t>
+  </si>
+  <si>
+    <t>21/09/2026 15:30:00</t>
+  </si>
+  <si>
+    <t>17/09/2026 12:30:00</t>
+  </si>
+  <si>
+    <t>tăng ca cǎt ông nhua</t>
+  </si>
+  <si>
+    <t>14/09/2026 12:30:00</t>
+  </si>
+  <si>
+    <t>22/09/2026 15:30:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">vận chuyển nguyên vật liệu nghiền </t>
+  </si>
+  <si>
+    <t>19/09/2026 07:45:00</t>
+  </si>
+  <si>
+    <t>19/09/2026 16:30:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tang ca cat ong nhua </t>
+  </si>
+  <si>
+    <t>15/09/2026 12:30:00</t>
+  </si>
+  <si>
+    <t>15/09/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>02622116</t>
+  </si>
+  <si>
+    <t>Trịnh Nhựt Khánh</t>
+  </si>
+  <si>
+    <t>16/09/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>16/09/2026 15:30:00</t>
+  </si>
+  <si>
+    <t>18/09/2026 15:30:00</t>
+  </si>
+  <si>
+    <t>15/09/2026 15:30:00</t>
+  </si>
+  <si>
     <t>02121404</t>
   </si>
   <si>
     <t>Lê Hoàng Minh Tâm</t>
-  </si>
-  <si>
-    <t>Plastic Extrusion</t>
-  </si>
-  <si>
-    <t>Pulverize</t>
-  </si>
-  <si>
-    <t>tăng cường sản xuất</t>
-  </si>
-  <si>
-    <t>Nguyễn Chí Cường</t>
-  </si>
-  <si>
-    <t>Thân Trọng Tuấn</t>
-  </si>
-  <si>
-    <t>19/09/2026 06:00:00</t>
-  </si>
-  <si>
-    <t>19/09/2026 14:00:00</t>
-  </si>
-  <si>
-    <t>Bằng KH</t>
-  </si>
-  <si>
-    <t>Đã duyệt</t>
-  </si>
-  <si>
-    <t>12/09/2026 14:00:00</t>
-  </si>
-  <si>
-    <t>12/09/2026 22:00:00</t>
-  </si>
-  <si>
-    <t>02020947</t>
-  </si>
-  <si>
-    <t>Nguyễn Hoàng Duy</t>
-  </si>
-  <si>
-    <t>chuẩn bị kiểm kê</t>
-  </si>
-  <si>
-    <t>23/09/2026 16:30:00</t>
-  </si>
-  <si>
-    <t>23/09/2026 18:00:00</t>
-  </si>
-  <si>
-    <t>02644057</t>
-  </si>
-  <si>
-    <t>Phạm Văn Công</t>
-  </si>
-  <si>
-    <t>tăng ca đáp ứng tiến độ sản xuất</t>
-  </si>
-  <si>
-    <t>14/09/2026 20:30:00</t>
-  </si>
-  <si>
-    <t>14/09/2026 22:00:00</t>
-  </si>
-  <si>
-    <t>17/09/2026 20:30:00</t>
-  </si>
-  <si>
-    <t>17/09/2026 22:00:00</t>
-  </si>
-  <si>
-    <t>lắp đặt thiết bị</t>
-  </si>
-  <si>
-    <t>12/09/2026 07:45:00</t>
-  </si>
-  <si>
-    <t>12/09/2026 16:30:00</t>
-  </si>
-  <si>
-    <t>21/09/2026 12:30:00</t>
-  </si>
-  <si>
-    <t>21/09/2026 14:00:00</t>
-  </si>
-  <si>
-    <t>22/09/2026 16:30:00</t>
-  </si>
-  <si>
-    <t>22/09/2026 18:00:00</t>
-  </si>
-  <si>
-    <t>19/09/2026 22:00:00</t>
-  </si>
-  <si>
-    <t>20/09/2026 06:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">vận chuyển nguyên vật liệu nghiền </t>
-  </si>
-  <si>
-    <t>19/09/2026 07:45:00</t>
-  </si>
-  <si>
-    <t>19/09/2026 16:30:00</t>
-  </si>
-  <si>
-    <t>12/09/2026 06:00:00</t>
-  </si>
-  <si>
-    <t>02222350</t>
-  </si>
-  <si>
-    <t>Hoàng Văn Nguyên</t>
-  </si>
-  <si>
-    <t>Tăng cường sản xuất</t>
-  </si>
-  <si>
-    <t>02243654</t>
-  </si>
-  <si>
-    <t>Lưu Văn Giang</t>
-  </si>
-  <si>
-    <t>Tăng Cường Sản Xuất</t>
-  </si>
-  <si>
-    <t>02223526</t>
-  </si>
-  <si>
-    <t>Nguyễn Thiên Phú</t>
-  </si>
-  <si>
-    <t>23/09/2026 12:30:00</t>
-  </si>
-  <si>
-    <t>23/09/2026 14:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tăng cường sản xuất </t>
-  </si>
-  <si>
-    <t>13/09/2026 06:00:00</t>
-  </si>
-  <si>
-    <t>18/09/2026 20:30:00</t>
-  </si>
-  <si>
-    <t>18/09/2026 22:00:00</t>
-  </si>
-  <si>
-    <t>02644066</t>
-  </si>
-  <si>
-    <t>Nguyễn Hữu Tình</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tang ca cat ong nhua </t>
-  </si>
-  <si>
-    <t>15/09/2026 12:30:00</t>
-  </si>
-  <si>
-    <t>15/09/2026 14:00:00</t>
-  </si>
-  <si>
-    <t>02223605</t>
-  </si>
-  <si>
-    <t>Võ Minh Bắc</t>
-  </si>
-  <si>
-    <t>tang ca cat ong nhua</t>
-  </si>
-  <si>
-    <t>18/09/2026 12:30:00</t>
-  </si>
-  <si>
-    <t>18/09/2026 14:00:00</t>
-  </si>
-  <si>
-    <t>21/09/2026 15:30:00</t>
-  </si>
-  <si>
-    <t>22/09/2026 12:30:00</t>
-  </si>
-  <si>
-    <t>22/09/2026 14:00:00</t>
-  </si>
-  <si>
-    <t>23/09/2026 15:30:00</t>
-  </si>
-  <si>
-    <t>16/09/2026 20:30:00</t>
-  </si>
-  <si>
-    <t>16/09/2026 22:00:00</t>
-  </si>
-  <si>
-    <t>tăng ca cǎt ông nhua</t>
-  </si>
-  <si>
-    <t>14/09/2026 12:30:00</t>
-  </si>
-  <si>
-    <t>14/09/2026 14:00:00</t>
-  </si>
-  <si>
-    <t>15/09/2026 20:30:00</t>
-  </si>
-  <si>
-    <t>15/09/2026 22:00:00</t>
-  </si>
-  <si>
-    <t>02644075</t>
-  </si>
-  <si>
-    <t>Huỳnh Đại Nhân</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tăng cường sản xuất </t>
-  </si>
-  <si>
-    <t>14/09/2026 15:30:00</t>
-  </si>
-  <si>
-    <t>22/09/2026 15:30:00</t>
-  </si>
-  <si>
-    <t>15/09/2026 15:30:00</t>
-  </si>
-  <si>
-    <t>22/09/2026 20:30:00</t>
-  </si>
-  <si>
-    <t>22/09/2026 22:00:00</t>
-  </si>
-  <si>
-    <t>17/09/2026 12:30:00</t>
-  </si>
-  <si>
-    <t>17/09/2026 14:00:00</t>
-  </si>
-  <si>
-    <t>tang ca van hanh may nghien</t>
-  </si>
-  <si>
-    <t>17/09/2026 15:30:00</t>
-  </si>
-  <si>
-    <t>21/09/2026 20:30:00</t>
-  </si>
-  <si>
-    <t>21/09/2026 22:00:00</t>
-  </si>
-  <si>
-    <t>16/09/2026 14:00:00</t>
-  </si>
-  <si>
-    <t>16/09/2026 15:30:00</t>
-  </si>
-  <si>
-    <t>18/09/2026 15:30:00</t>
-  </si>
-  <si>
-    <t>02622116</t>
-  </si>
-  <si>
-    <t>Trịnh Nhựt Khánh</t>
   </si>
 </sst>
 </file>
@@ -878,10 +902,10 @@
     </row>
     <row r="4" s="2" customFormat="1">
       <c r="A4" s="7" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="C4" s="7" t="s">
         <v>19</v>
@@ -890,7 +914,7 @@
         <v>20</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="F4" s="7" t="s">
         <v>22</v>
@@ -899,19 +923,19 @@
         <v>23</v>
       </c>
       <c r="H4" s="8" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="I4" s="8" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="J4" s="8">
-        <v>480</v>
+        <v>90</v>
       </c>
       <c r="K4" s="8" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="L4" s="8" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="M4" s="8">
         <v>0</v>
@@ -926,10 +950,10 @@
     </row>
     <row r="5" s="2" customFormat="1">
       <c r="A5" s="7" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="C5" s="7" t="s">
         <v>19</v>
@@ -938,7 +962,7 @@
         <v>20</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F5" s="7" t="s">
         <v>22</v>
@@ -947,19 +971,19 @@
         <v>23</v>
       </c>
       <c r="H5" s="8" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="I5" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="J5" s="8">
+        <v>480</v>
+      </c>
+      <c r="K5" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="J5" s="8">
-        <v>90</v>
-      </c>
-      <c r="K5" s="8" t="s">
-        <v>33</v>
-      </c>
       <c r="L5" s="8" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="M5" s="8">
         <v>0</v>
@@ -974,40 +998,40 @@
     </row>
     <row r="6" s="2" customFormat="1">
       <c r="A6" s="7" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="B6" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="F6" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G6" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="H6" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="C6" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="D6" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="E6" s="7" t="s">
+      <c r="I6" s="8" t="s">
         <v>37</v>
-      </c>
-      <c r="F6" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="G6" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="H6" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="I6" s="8" t="s">
-        <v>39</v>
       </c>
       <c r="J6" s="8">
         <v>90</v>
       </c>
       <c r="K6" s="8" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="L6" s="8" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="M6" s="8">
         <v>0</v>
@@ -1022,10 +1046,10 @@
     </row>
     <row r="7" s="2" customFormat="1">
       <c r="A7" s="7" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="C7" s="7" t="s">
         <v>19</v>
@@ -1034,7 +1058,7 @@
         <v>20</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="F7" s="7" t="s">
         <v>22</v>
@@ -1043,19 +1067,19 @@
         <v>23</v>
       </c>
       <c r="H7" s="8" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="I7" s="8" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="J7" s="8">
         <v>90</v>
       </c>
       <c r="K7" s="8" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="L7" s="8" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="M7" s="8">
         <v>0</v>
@@ -1070,20 +1094,20 @@
     </row>
     <row r="8" s="2" customFormat="1">
       <c r="A8" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E8" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="B8" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="C8" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="D8" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="E8" s="7" t="s">
-        <v>42</v>
-      </c>
       <c r="F8" s="7" t="s">
         <v>22</v>
       </c>
@@ -1091,19 +1115,19 @@
         <v>23</v>
       </c>
       <c r="H8" s="8" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="I8" s="8" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="J8" s="8">
-        <v>480</v>
+        <v>90</v>
       </c>
       <c r="K8" s="8" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="L8" s="8" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="M8" s="8">
         <v>0</v>
@@ -1118,10 +1142,10 @@
     </row>
     <row r="9" s="2" customFormat="1">
       <c r="A9" s="7" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="C9" s="7" t="s">
         <v>19</v>
@@ -1130,7 +1154,7 @@
         <v>20</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="F9" s="7" t="s">
         <v>22</v>
@@ -1139,19 +1163,19 @@
         <v>23</v>
       </c>
       <c r="H9" s="8" t="s">
-        <v>45</v>
+        <v>24</v>
       </c>
       <c r="I9" s="8" t="s">
-        <v>46</v>
+        <v>25</v>
       </c>
       <c r="J9" s="8">
-        <v>90</v>
+        <v>480</v>
       </c>
       <c r="K9" s="8" t="s">
-        <v>45</v>
+        <v>24</v>
       </c>
       <c r="L9" s="8" t="s">
-        <v>46</v>
+        <v>25</v>
       </c>
       <c r="M9" s="8">
         <v>0</v>
@@ -1166,20 +1190,20 @@
     </row>
     <row r="10" s="2" customFormat="1">
       <c r="A10" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E10" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="B10" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="C10" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="D10" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="E10" s="7" t="s">
-        <v>32</v>
-      </c>
       <c r="F10" s="7" t="s">
         <v>22</v>
       </c>
@@ -1187,19 +1211,19 @@
         <v>23</v>
       </c>
       <c r="H10" s="8" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="I10" s="8" t="s">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="J10" s="8">
-        <v>90</v>
+        <v>480</v>
       </c>
       <c r="K10" s="8" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="L10" s="8" t="s">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="M10" s="8">
         <v>0</v>
@@ -1214,10 +1238,10 @@
     </row>
     <row r="11" s="2" customFormat="1">
       <c r="A11" s="7" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="C11" s="7" t="s">
         <v>19</v>
@@ -1226,7 +1250,7 @@
         <v>20</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="F11" s="7" t="s">
         <v>22</v>
@@ -1235,19 +1259,19 @@
         <v>23</v>
       </c>
       <c r="H11" s="8" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="I11" s="8" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="J11" s="8">
-        <v>480</v>
+        <v>90</v>
       </c>
       <c r="K11" s="8" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="L11" s="8" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="M11" s="8">
         <v>0</v>
@@ -1262,20 +1286,20 @@
     </row>
     <row r="12" s="2" customFormat="1">
       <c r="A12" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E12" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="B12" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="C12" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="D12" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="E12" s="7" t="s">
-        <v>51</v>
-      </c>
       <c r="F12" s="7" t="s">
         <v>22</v>
       </c>
@@ -1283,19 +1307,19 @@
         <v>23</v>
       </c>
       <c r="H12" s="8" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="I12" s="8" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="J12" s="8">
-        <v>480</v>
+        <v>90</v>
       </c>
       <c r="K12" s="8" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="L12" s="8" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="M12" s="8">
         <v>0</v>
@@ -1310,10 +1334,10 @@
     </row>
     <row r="13" s="2" customFormat="1">
       <c r="A13" s="7" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="C13" s="7" t="s">
         <v>19</v>
@@ -1322,7 +1346,7 @@
         <v>20</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="F13" s="7" t="s">
         <v>22</v>
@@ -1331,19 +1355,19 @@
         <v>23</v>
       </c>
       <c r="H13" s="8" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="I13" s="8" t="s">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="J13" s="8">
-        <v>480</v>
+        <v>90</v>
       </c>
       <c r="K13" s="8" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="L13" s="8" t="s">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="M13" s="8">
         <v>0</v>
@@ -1358,10 +1382,10 @@
     </row>
     <row r="14" s="2" customFormat="1">
       <c r="A14" s="7" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="C14" s="7" t="s">
         <v>19</v>
@@ -1370,7 +1394,7 @@
         <v>20</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>57</v>
+        <v>21</v>
       </c>
       <c r="F14" s="7" t="s">
         <v>22</v>
@@ -1379,19 +1403,19 @@
         <v>23</v>
       </c>
       <c r="H14" s="8" t="s">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="I14" s="8" t="s">
-        <v>25</v>
+        <v>51</v>
       </c>
       <c r="J14" s="8">
         <v>480</v>
       </c>
       <c r="K14" s="8" t="s">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="L14" s="8" t="s">
-        <v>25</v>
+        <v>51</v>
       </c>
       <c r="M14" s="8">
         <v>0</v>
@@ -1406,10 +1430,10 @@
     </row>
     <row r="15" s="2" customFormat="1">
       <c r="A15" s="7" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="C15" s="7" t="s">
         <v>19</v>
@@ -1418,7 +1442,7 @@
         <v>20</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="F15" s="7" t="s">
         <v>22</v>
@@ -1427,19 +1451,19 @@
         <v>23</v>
       </c>
       <c r="H15" s="8" t="s">
-        <v>25</v>
+        <v>55</v>
       </c>
       <c r="I15" s="8" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="J15" s="8">
-        <v>480</v>
+        <v>90</v>
       </c>
       <c r="K15" s="8" t="s">
-        <v>25</v>
+        <v>55</v>
       </c>
       <c r="L15" s="8" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="M15" s="8">
         <v>0</v>
@@ -1454,10 +1478,10 @@
     </row>
     <row r="16" s="2" customFormat="1">
       <c r="A16" s="7" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="C16" s="7" t="s">
         <v>19</v>
@@ -1466,7 +1490,7 @@
         <v>20</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F16" s="7" t="s">
         <v>22</v>
@@ -1475,19 +1499,19 @@
         <v>23</v>
       </c>
       <c r="H16" s="8" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="I16" s="8" t="s">
-        <v>50</v>
+        <v>24</v>
       </c>
       <c r="J16" s="8">
         <v>480</v>
       </c>
       <c r="K16" s="8" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="L16" s="8" t="s">
-        <v>50</v>
+        <v>24</v>
       </c>
       <c r="M16" s="8">
         <v>0</v>
@@ -1502,10 +1526,10 @@
     </row>
     <row r="17" s="2" customFormat="1">
       <c r="A17" s="7" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="C17" s="7" t="s">
         <v>19</v>
@@ -1514,7 +1538,7 @@
         <v>20</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="F17" s="7" t="s">
         <v>22</v>
@@ -1523,19 +1547,19 @@
         <v>23</v>
       </c>
       <c r="H17" s="8" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="I17" s="8" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="J17" s="8">
         <v>90</v>
       </c>
       <c r="K17" s="8" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="L17" s="8" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="M17" s="8">
         <v>0</v>
@@ -1550,10 +1574,10 @@
     </row>
     <row r="18" s="2" customFormat="1">
       <c r="A18" s="7" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C18" s="7" t="s">
         <v>19</v>
@@ -1562,28 +1586,28 @@
         <v>20</v>
       </c>
       <c r="E18" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="F18" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G18" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="H18" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="F18" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="G18" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="H18" s="8" t="s">
-        <v>54</v>
-      </c>
       <c r="I18" s="8" t="s">
-        <v>28</v>
+        <v>66</v>
       </c>
       <c r="J18" s="8">
-        <v>480</v>
+        <v>90</v>
       </c>
       <c r="K18" s="8" t="s">
-        <v>54</v>
+        <v>65</v>
       </c>
       <c r="L18" s="8" t="s">
-        <v>28</v>
+        <v>66</v>
       </c>
       <c r="M18" s="8">
         <v>0</v>
@@ -1598,10 +1622,10 @@
     </row>
     <row r="19" s="2" customFormat="1">
       <c r="A19" s="7" t="s">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="C19" s="7" t="s">
         <v>19</v>
@@ -1610,7 +1634,7 @@
         <v>20</v>
       </c>
       <c r="E19" s="7" t="s">
-        <v>60</v>
+        <v>21</v>
       </c>
       <c r="F19" s="7" t="s">
         <v>22</v>
@@ -1619,19 +1643,19 @@
         <v>23</v>
       </c>
       <c r="H19" s="8" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="I19" s="8" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="J19" s="8">
         <v>480</v>
       </c>
       <c r="K19" s="8" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="L19" s="8" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="M19" s="8">
         <v>0</v>
@@ -1646,10 +1670,10 @@
     </row>
     <row r="20" s="2" customFormat="1">
       <c r="A20" s="7" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C20" s="7" t="s">
         <v>19</v>
@@ -1658,7 +1682,7 @@
         <v>20</v>
       </c>
       <c r="E20" s="7" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F20" s="7" t="s">
         <v>22</v>
@@ -1667,19 +1691,19 @@
         <v>23</v>
       </c>
       <c r="H20" s="8" t="s">
-        <v>28</v>
+        <v>67</v>
       </c>
       <c r="I20" s="8" t="s">
-        <v>29</v>
+        <v>68</v>
       </c>
       <c r="J20" s="8">
         <v>480</v>
       </c>
       <c r="K20" s="8" t="s">
-        <v>28</v>
+        <v>67</v>
       </c>
       <c r="L20" s="8" t="s">
-        <v>29</v>
+        <v>68</v>
       </c>
       <c r="M20" s="8">
         <v>0</v>
@@ -1694,10 +1718,10 @@
     </row>
     <row r="21" s="2" customFormat="1">
       <c r="A21" s="7" t="s">
-        <v>35</v>
+        <v>52</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="C21" s="7" t="s">
         <v>19</v>
@@ -1706,7 +1730,7 @@
         <v>20</v>
       </c>
       <c r="E21" s="7" t="s">
-        <v>37</v>
+        <v>69</v>
       </c>
       <c r="F21" s="7" t="s">
         <v>22</v>
@@ -1715,19 +1739,19 @@
         <v>23</v>
       </c>
       <c r="H21" s="8" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="I21" s="8" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="J21" s="8">
         <v>90</v>
       </c>
       <c r="K21" s="8" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="L21" s="8" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="M21" s="8">
         <v>0</v>
@@ -1742,10 +1766,10 @@
     </row>
     <row r="22" s="2" customFormat="1">
       <c r="A22" s="7" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C22" s="7" t="s">
         <v>19</v>
@@ -1754,7 +1778,7 @@
         <v>20</v>
       </c>
       <c r="E22" s="7" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="F22" s="7" t="s">
         <v>22</v>
@@ -1763,19 +1787,19 @@
         <v>23</v>
       </c>
       <c r="H22" s="8" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="I22" s="8" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="J22" s="8">
-        <v>90</v>
+        <v>480</v>
       </c>
       <c r="K22" s="8" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="L22" s="8" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="M22" s="8">
         <v>0</v>
@@ -1790,40 +1814,40 @@
     </row>
     <row r="23" s="2" customFormat="1">
       <c r="A23" s="7" t="s">
-        <v>74</v>
+        <v>62</v>
       </c>
       <c r="B23" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="C23" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D23" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E23" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="F23" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G23" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="H23" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="C23" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="D23" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="E23" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="F23" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="G23" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="H23" s="8" t="s">
-        <v>25</v>
-      </c>
       <c r="I23" s="8" t="s">
-        <v>49</v>
+        <v>76</v>
       </c>
       <c r="J23" s="8">
-        <v>480</v>
+        <v>90</v>
       </c>
       <c r="K23" s="8" t="s">
-        <v>25</v>
+        <v>75</v>
       </c>
       <c r="L23" s="8" t="s">
-        <v>49</v>
+        <v>76</v>
       </c>
       <c r="M23" s="8">
         <v>0</v>
@@ -1833,15 +1857,15 @@
         <v>26</v>
       </c>
       <c r="P23" s="8" t="s">
-        <v>27</v>
+        <v>77</v>
       </c>
     </row>
     <row r="24" s="2" customFormat="1">
       <c r="A24" s="7" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C24" s="7" t="s">
         <v>19</v>
@@ -1850,7 +1874,7 @@
         <v>20</v>
       </c>
       <c r="E24" s="7" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="F24" s="7" t="s">
         <v>22</v>
@@ -1859,19 +1883,19 @@
         <v>23</v>
       </c>
       <c r="H24" s="8" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="I24" s="8" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="J24" s="8">
         <v>90</v>
       </c>
       <c r="K24" s="8" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="L24" s="8" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="M24" s="8">
         <v>0</v>
@@ -1886,10 +1910,10 @@
     </row>
     <row r="25" s="2" customFormat="1">
       <c r="A25" s="7" t="s">
-        <v>74</v>
+        <v>62</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>75</v>
+        <v>63</v>
       </c>
       <c r="C25" s="7" t="s">
         <v>19</v>
@@ -1898,7 +1922,7 @@
         <v>20</v>
       </c>
       <c r="E25" s="7" t="s">
-        <v>21</v>
+        <v>64</v>
       </c>
       <c r="F25" s="7" t="s">
         <v>22</v>
@@ -1907,19 +1931,19 @@
         <v>23</v>
       </c>
       <c r="H25" s="8" t="s">
-        <v>29</v>
+        <v>81</v>
       </c>
       <c r="I25" s="8" t="s">
-        <v>66</v>
+        <v>82</v>
       </c>
       <c r="J25" s="8">
-        <v>480</v>
+        <v>90</v>
       </c>
       <c r="K25" s="8" t="s">
-        <v>29</v>
+        <v>81</v>
       </c>
       <c r="L25" s="8" t="s">
-        <v>66</v>
+        <v>82</v>
       </c>
       <c r="M25" s="8">
         <v>0</v>
@@ -1934,10 +1958,10 @@
     </row>
     <row r="26" s="2" customFormat="1">
       <c r="A26" s="7" t="s">
-        <v>69</v>
+        <v>83</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>70</v>
+        <v>84</v>
       </c>
       <c r="C26" s="7" t="s">
         <v>19</v>
@@ -1946,7 +1970,7 @@
         <v>20</v>
       </c>
       <c r="E26" s="7" t="s">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="F26" s="7" t="s">
         <v>22</v>
@@ -1955,19 +1979,19 @@
         <v>23</v>
       </c>
       <c r="H26" s="8" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="I26" s="8" t="s">
-        <v>79</v>
+        <v>24</v>
       </c>
       <c r="J26" s="8">
-        <v>90</v>
+        <v>480</v>
       </c>
       <c r="K26" s="8" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="L26" s="8" t="s">
-        <v>79</v>
+        <v>24</v>
       </c>
       <c r="M26" s="8">
         <v>0</v>
@@ -1982,10 +2006,10 @@
     </row>
     <row r="27" s="2" customFormat="1">
       <c r="A27" s="7" t="s">
-        <v>35</v>
+        <v>52</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="C27" s="7" t="s">
         <v>19</v>
@@ -1994,7 +2018,7 @@
         <v>20</v>
       </c>
       <c r="E27" s="7" t="s">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="F27" s="7" t="s">
         <v>22</v>
@@ -2003,19 +2027,19 @@
         <v>23</v>
       </c>
       <c r="H27" s="8" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="I27" s="8" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="J27" s="8">
         <v>90</v>
       </c>
       <c r="K27" s="8" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="L27" s="8" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="M27" s="8">
         <v>0</v>
@@ -2030,10 +2054,10 @@
     </row>
     <row r="28" s="2" customFormat="1">
       <c r="A28" s="7" t="s">
-        <v>69</v>
+        <v>83</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>70</v>
+        <v>84</v>
       </c>
       <c r="C28" s="7" t="s">
         <v>19</v>
@@ -2042,7 +2066,7 @@
         <v>20</v>
       </c>
       <c r="E28" s="7" t="s">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="F28" s="7" t="s">
         <v>22</v>
@@ -2051,19 +2075,19 @@
         <v>23</v>
       </c>
       <c r="H28" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="I28" s="8" t="s">
-        <v>82</v>
+        <v>68</v>
       </c>
       <c r="J28" s="8">
-        <v>90</v>
+        <v>480</v>
       </c>
       <c r="K28" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="L28" s="8" t="s">
-        <v>82</v>
+        <v>68</v>
       </c>
       <c r="M28" s="8">
         <v>0</v>
@@ -2078,10 +2102,10 @@
     </row>
     <row r="29" s="2" customFormat="1">
       <c r="A29" s="7" t="s">
-        <v>35</v>
+        <v>72</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>36</v>
+        <v>73</v>
       </c>
       <c r="C29" s="7" t="s">
         <v>19</v>
@@ -2090,7 +2114,7 @@
         <v>20</v>
       </c>
       <c r="E29" s="7" t="s">
-        <v>37</v>
+        <v>78</v>
       </c>
       <c r="F29" s="7" t="s">
         <v>22</v>
@@ -2099,19 +2123,19 @@
         <v>23</v>
       </c>
       <c r="H29" s="8" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="I29" s="8" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="J29" s="8">
         <v>90</v>
       </c>
       <c r="K29" s="8" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="L29" s="8" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="M29" s="8">
         <v>0</v>
@@ -2126,10 +2150,10 @@
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="C30" s="3" t="s">
         <v>19</v>
@@ -2138,7 +2162,7 @@
         <v>20</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>85</v>
+        <v>64</v>
       </c>
       <c r="F30" s="3" t="s">
         <v>22</v>
@@ -2147,19 +2171,19 @@
         <v>23</v>
       </c>
       <c r="H30" s="4" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="I30" s="4" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="J30" s="4">
         <v>90</v>
       </c>
       <c r="K30" s="4" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="L30" s="4" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="M30" s="4">
         <v>0</v>
@@ -2174,10 +2198,10 @@
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>36</v>
+        <v>63</v>
       </c>
       <c r="C31" s="3" t="s">
         <v>19</v>
@@ -2186,7 +2210,7 @@
         <v>20</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>37</v>
+        <v>64</v>
       </c>
       <c r="F31" s="3" t="s">
         <v>22</v>
@@ -2195,19 +2219,19 @@
         <v>23</v>
       </c>
       <c r="H31" s="4" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="I31" s="4" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="J31" s="4">
         <v>90</v>
       </c>
       <c r="K31" s="4" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="L31" s="4" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="M31" s="4">
         <v>0</v>
@@ -2222,10 +2246,10 @@
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
-        <v>90</v>
+        <v>72</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>91</v>
+        <v>73</v>
       </c>
       <c r="C32" s="3" t="s">
         <v>19</v>
@@ -2234,7 +2258,7 @@
         <v>20</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>92</v>
+        <v>78</v>
       </c>
       <c r="F32" s="3" t="s">
         <v>22</v>
@@ -2243,19 +2267,19 @@
         <v>23</v>
       </c>
       <c r="H32" s="4" t="s">
-        <v>87</v>
+        <v>41</v>
       </c>
       <c r="I32" s="4" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J32" s="4">
         <v>90</v>
       </c>
       <c r="K32" s="4" t="s">
-        <v>87</v>
+        <v>41</v>
       </c>
       <c r="L32" s="4" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="M32" s="4">
         <v>0</v>
@@ -2270,10 +2294,10 @@
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="C33" s="3" t="s">
         <v>19</v>
@@ -2282,7 +2306,7 @@
         <v>20</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>76</v>
+        <v>64</v>
       </c>
       <c r="F33" s="3" t="s">
         <v>22</v>
@@ -2291,19 +2315,19 @@
         <v>23</v>
       </c>
       <c r="H33" s="4" t="s">
-        <v>81</v>
+        <v>35</v>
       </c>
       <c r="I33" s="4" t="s">
-        <v>94</v>
+        <v>67</v>
       </c>
       <c r="J33" s="4">
-        <v>90</v>
+        <v>480</v>
       </c>
       <c r="K33" s="4" t="s">
-        <v>81</v>
+        <v>35</v>
       </c>
       <c r="L33" s="4" t="s">
-        <v>94</v>
+        <v>67</v>
       </c>
       <c r="M33" s="4">
         <v>0</v>
@@ -2318,10 +2342,10 @@
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
-        <v>90</v>
+        <v>52</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>91</v>
+        <v>53</v>
       </c>
       <c r="C34" s="3" t="s">
         <v>19</v>
@@ -2330,7 +2354,7 @@
         <v>20</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="F34" s="3" t="s">
         <v>22</v>
@@ -2339,19 +2363,19 @@
         <v>23</v>
       </c>
       <c r="H34" s="4" t="s">
-        <v>73</v>
+        <v>96</v>
       </c>
       <c r="I34" s="4" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="J34" s="4">
-        <v>90</v>
+        <v>480</v>
       </c>
       <c r="K34" s="4" t="s">
-        <v>73</v>
+        <v>96</v>
       </c>
       <c r="L34" s="4" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="M34" s="4">
         <v>0</v>
@@ -2366,10 +2390,10 @@
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
-        <v>90</v>
+        <v>72</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>91</v>
+        <v>73</v>
       </c>
       <c r="C35" s="3" t="s">
         <v>19</v>
@@ -2378,7 +2402,7 @@
         <v>20</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>92</v>
+        <v>78</v>
       </c>
       <c r="F35" s="3" t="s">
         <v>22</v>
@@ -2387,19 +2411,19 @@
         <v>23</v>
       </c>
       <c r="H35" s="4" t="s">
-        <v>96</v>
+        <v>39</v>
       </c>
       <c r="I35" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="J35" s="4">
         <v>90</v>
       </c>
       <c r="K35" s="4" t="s">
-        <v>96</v>
+        <v>39</v>
       </c>
       <c r="L35" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="M35" s="4">
         <v>0</v>
@@ -2414,10 +2438,10 @@
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C36" s="3" t="s">
         <v>19</v>
@@ -2426,7 +2450,7 @@
         <v>20</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="F36" s="3" t="s">
         <v>22</v>
@@ -2435,19 +2459,19 @@
         <v>23</v>
       </c>
       <c r="H36" s="4" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I36" s="4" t="s">
-        <v>99</v>
+        <v>90</v>
       </c>
       <c r="J36" s="4">
         <v>90</v>
       </c>
       <c r="K36" s="4" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="L36" s="4" t="s">
-        <v>99</v>
+        <v>90</v>
       </c>
       <c r="M36" s="4">
         <v>0</v>
@@ -2462,10 +2486,10 @@
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C37" s="3" t="s">
         <v>19</v>
@@ -2483,19 +2507,19 @@
         <v>23</v>
       </c>
       <c r="H37" s="4" t="s">
-        <v>29</v>
+        <v>101</v>
       </c>
       <c r="I37" s="4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="J37" s="4">
-        <v>480</v>
+        <v>90</v>
       </c>
       <c r="K37" s="4" t="s">
-        <v>29</v>
+        <v>101</v>
       </c>
       <c r="L37" s="4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="M37" s="4">
         <v>0</v>
@@ -2510,10 +2534,10 @@
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
-        <v>90</v>
+        <v>62</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>91</v>
+        <v>63</v>
       </c>
       <c r="C38" s="3" t="s">
         <v>19</v>
@@ -2522,7 +2546,7 @@
         <v>20</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>92</v>
+        <v>64</v>
       </c>
       <c r="F38" s="3" t="s">
         <v>22</v>
@@ -2531,19 +2555,19 @@
         <v>23</v>
       </c>
       <c r="H38" s="4" t="s">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="I38" s="4" t="s">
-        <v>29</v>
+        <v>51</v>
       </c>
       <c r="J38" s="4">
         <v>480</v>
       </c>
       <c r="K38" s="4" t="s">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="L38" s="4" t="s">
-        <v>29</v>
+        <v>51</v>
       </c>
       <c r="M38" s="4">
         <v>0</v>
@@ -2558,10 +2582,10 @@
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
-        <v>90</v>
+        <v>72</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>91</v>
+        <v>73</v>
       </c>
       <c r="C39" s="3" t="s">
         <v>19</v>
@@ -2570,7 +2594,7 @@
         <v>20</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>92</v>
+        <v>78</v>
       </c>
       <c r="F39" s="3" t="s">
         <v>22</v>
@@ -2579,19 +2603,19 @@
         <v>23</v>
       </c>
       <c r="H39" s="4" t="s">
-        <v>99</v>
+        <v>45</v>
       </c>
       <c r="I39" s="4" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="J39" s="4">
         <v>90</v>
       </c>
       <c r="K39" s="4" t="s">
-        <v>99</v>
+        <v>45</v>
       </c>
       <c r="L39" s="4" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="M39" s="4">
         <v>0</v>
@@ -2606,10 +2630,10 @@
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
-        <v>90</v>
+        <v>52</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>91</v>
+        <v>53</v>
       </c>
       <c r="C40" s="3" t="s">
         <v>19</v>
@@ -2618,7 +2642,7 @@
         <v>20</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>92</v>
+        <v>103</v>
       </c>
       <c r="F40" s="3" t="s">
         <v>22</v>
@@ -2627,19 +2651,19 @@
         <v>23</v>
       </c>
       <c r="H40" s="4" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="I40" s="4" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="J40" s="4">
-        <v>90</v>
+        <v>480</v>
       </c>
       <c r="K40" s="4" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="L40" s="4" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="M40" s="4">
         <v>0</v>
@@ -2654,10 +2678,10 @@
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C41" s="3" t="s">
         <v>19</v>
@@ -2666,7 +2690,7 @@
         <v>20</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="F41" s="3" t="s">
         <v>22</v>
@@ -2675,19 +2699,19 @@
         <v>23</v>
       </c>
       <c r="H41" s="4" t="s">
-        <v>25</v>
+        <v>107</v>
       </c>
       <c r="I41" s="4" t="s">
-        <v>49</v>
+        <v>108</v>
       </c>
       <c r="J41" s="4">
-        <v>480</v>
+        <v>90</v>
       </c>
       <c r="K41" s="4" t="s">
-        <v>25</v>
+        <v>107</v>
       </c>
       <c r="L41" s="4" t="s">
-        <v>49</v>
+        <v>108</v>
       </c>
       <c r="M41" s="4">
         <v>0</v>
@@ -2702,10 +2726,10 @@
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
-        <v>90</v>
+        <v>72</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>91</v>
+        <v>73</v>
       </c>
       <c r="C42" s="3" t="s">
         <v>19</v>
@@ -2714,7 +2738,7 @@
         <v>20</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>92</v>
+        <v>74</v>
       </c>
       <c r="F42" s="3" t="s">
         <v>22</v>
@@ -2723,19 +2747,19 @@
         <v>23</v>
       </c>
       <c r="H42" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="I42" s="4" t="s">
         <v>24</v>
-      </c>
-      <c r="I42" s="4" t="s">
-        <v>25</v>
       </c>
       <c r="J42" s="4">
         <v>480</v>
       </c>
       <c r="K42" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="L42" s="4" t="s">
         <v>24</v>
-      </c>
-      <c r="L42" s="4" t="s">
-        <v>25</v>
       </c>
       <c r="M42" s="4">
         <v>0</v>
@@ -2750,10 +2774,10 @@
     </row>
     <row r="43">
       <c r="A43" s="3" t="s">
-        <v>90</v>
+        <v>109</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>91</v>
+        <v>110</v>
       </c>
       <c r="C43" s="3" t="s">
         <v>19</v>
@@ -2762,7 +2786,7 @@
         <v>20</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="F43" s="3" t="s">
         <v>22</v>
@@ -2771,19 +2795,19 @@
         <v>23</v>
       </c>
       <c r="H43" s="4" t="s">
-        <v>104</v>
+        <v>34</v>
       </c>
       <c r="I43" s="4" t="s">
-        <v>105</v>
+        <v>35</v>
       </c>
       <c r="J43" s="4">
-        <v>90</v>
+        <v>480</v>
       </c>
       <c r="K43" s="4" t="s">
-        <v>104</v>
+        <v>34</v>
       </c>
       <c r="L43" s="4" t="s">
-        <v>105</v>
+        <v>35</v>
       </c>
       <c r="M43" s="4">
         <v>0</v>
@@ -2798,10 +2822,10 @@
     </row>
     <row r="44">
       <c r="A44" s="3" t="s">
-        <v>90</v>
+        <v>62</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>91</v>
+        <v>63</v>
       </c>
       <c r="C44" s="3" t="s">
         <v>19</v>
@@ -2810,7 +2834,7 @@
         <v>20</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>92</v>
+        <v>64</v>
       </c>
       <c r="F44" s="3" t="s">
         <v>22</v>
@@ -2819,19 +2843,19 @@
         <v>23</v>
       </c>
       <c r="H44" s="4" t="s">
-        <v>78</v>
+        <v>111</v>
       </c>
       <c r="I44" s="4" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="J44" s="4">
         <v>90</v>
       </c>
       <c r="K44" s="4" t="s">
-        <v>78</v>
+        <v>111</v>
       </c>
       <c r="L44" s="4" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="M44" s="4">
         <v>0</v>
@@ -2846,10 +2870,10 @@
     </row>
     <row r="45">
       <c r="A45" s="3" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C45" s="3" t="s">
         <v>19</v>
@@ -2858,7 +2882,7 @@
         <v>20</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>21</v>
+        <v>85</v>
       </c>
       <c r="F45" s="3" t="s">
         <v>22</v>
@@ -2867,19 +2891,19 @@
         <v>23</v>
       </c>
       <c r="H45" s="4" t="s">
-        <v>49</v>
+        <v>24</v>
       </c>
       <c r="I45" s="4" t="s">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="J45" s="4">
         <v>480</v>
       </c>
       <c r="K45" s="4" t="s">
-        <v>49</v>
+        <v>24</v>
       </c>
       <c r="L45" s="4" t="s">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="M45" s="4">
         <v>0</v>
@@ -2894,10 +2918,10 @@
     </row>
     <row r="46">
       <c r="A46" s="3" t="s">
-        <v>107</v>
+        <v>62</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>108</v>
+        <v>63</v>
       </c>
       <c r="C46" s="3" t="s">
         <v>19</v>
@@ -2906,7 +2930,7 @@
         <v>20</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>21</v>
+        <v>64</v>
       </c>
       <c r="F46" s="3" t="s">
         <v>22</v>
@@ -2915,19 +2939,19 @@
         <v>23</v>
       </c>
       <c r="H46" s="4" t="s">
-        <v>54</v>
+        <v>80</v>
       </c>
       <c r="I46" s="4" t="s">
-        <v>28</v>
+        <v>113</v>
       </c>
       <c r="J46" s="4">
-        <v>480</v>
+        <v>90</v>
       </c>
       <c r="K46" s="4" t="s">
-        <v>54</v>
+        <v>80</v>
       </c>
       <c r="L46" s="4" t="s">
-        <v>28</v>
+        <v>113</v>
       </c>
       <c r="M46" s="4">
         <v>0</v>
@@ -2937,6 +2961,150 @@
         <v>26</v>
       </c>
       <c r="P46" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="C47" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D47" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H47" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="I47" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="J47" s="4">
+        <v>90</v>
+      </c>
+      <c r="K47" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="L47" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="M47" s="4">
+        <v>0</v>
+      </c>
+      <c r="N47" s="3"/>
+      <c r="O47" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="P47" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="C48" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D48" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E48" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="F48" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G48" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H48" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="I48" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="J48" s="4">
+        <v>480</v>
+      </c>
+      <c r="K48" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="L48" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="M48" s="4">
+        <v>0</v>
+      </c>
+      <c r="N48" s="3"/>
+      <c r="O48" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="P48" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="C49" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D49" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E49" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="F49" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G49" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H49" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="I49" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="J49" s="4">
+        <v>480</v>
+      </c>
+      <c r="K49" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="L49" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="M49" s="4">
+        <v>0</v>
+      </c>
+      <c r="N49" s="3"/>
+      <c r="O49" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="P49" s="4" t="s">
         <v>27</v>
       </c>
     </row>

--- a/data/hrm_sync_actual_2.xlsx
+++ b/data/hrm_sync_actual_2.xlsx
@@ -70,39 +70,66 @@
     <t>Trạng thái duyệt</t>
   </si>
   <si>
+    <t>02121404</t>
+  </si>
+  <si>
+    <t>Lê Hoàng Minh Tâm</t>
+  </si>
+  <si>
+    <t>Plastic Extrusion</t>
+  </si>
+  <si>
+    <t>Pulverize</t>
+  </si>
+  <si>
+    <t>tăng cường sản xuất</t>
+  </si>
+  <si>
+    <t>Nguyễn Chí Cường</t>
+  </si>
+  <si>
+    <t>Thân Trọng Tuấn</t>
+  </si>
+  <si>
+    <t>19/09/2026 06:00:00</t>
+  </si>
+  <si>
+    <t>19/09/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>Bằng KH</t>
+  </si>
+  <si>
+    <t>Đã duyệt</t>
+  </si>
+  <si>
+    <t>02222350</t>
+  </si>
+  <si>
+    <t>Hoàng Văn Nguyên</t>
+  </si>
+  <si>
+    <t>Tăng cường sản xuất</t>
+  </si>
+  <si>
+    <t>12/09/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>12/09/2026 22:00:00</t>
+  </si>
+  <si>
     <t>02223526</t>
   </si>
   <si>
     <t>Nguyễn Thiên Phú</t>
   </si>
   <si>
-    <t>Plastic Extrusion</t>
-  </si>
-  <si>
-    <t>Pulverize</t>
-  </si>
-  <si>
-    <t>Tăng cường sản xuất</t>
-  </si>
-  <si>
-    <t>Nguyễn Chí Cường</t>
-  </si>
-  <si>
-    <t>Thân Trọng Tuấn</t>
-  </si>
-  <si>
     <t>19/09/2026 22:00:00</t>
   </si>
   <si>
     <t>20/09/2026 06:00:00</t>
   </si>
   <si>
-    <t>Bằng KH</t>
-  </si>
-  <si>
-    <t>Đã duyệt</t>
-  </si>
-  <si>
     <t>02644057</t>
   </si>
   <si>
@@ -118,19 +145,46 @@
     <t>17/09/2026 22:00:00</t>
   </si>
   <si>
+    <t>02223605</t>
+  </si>
+  <si>
+    <t>Võ Minh Bắc</t>
+  </si>
+  <si>
+    <t>02622116</t>
+  </si>
+  <si>
+    <t>Trịnh Nhựt Khánh</t>
+  </si>
+  <si>
+    <t>14/09/2026 20:30:00</t>
+  </si>
+  <si>
+    <t>14/09/2026 22:00:00</t>
+  </si>
+  <si>
+    <t>12/09/2026 06:00:00</t>
+  </si>
+  <si>
     <t xml:space="preserve">Tăng cường sản xuất </t>
   </si>
   <si>
-    <t>12/09/2026 06:00:00</t>
-  </si>
-  <si>
-    <t>12/09/2026 14:00:00</t>
-  </si>
-  <si>
-    <t>14/09/2026 20:30:00</t>
-  </si>
-  <si>
-    <t>14/09/2026 22:00:00</t>
+    <t>13/09/2026 06:00:00</t>
+  </si>
+  <si>
+    <t>02020947</t>
+  </si>
+  <si>
+    <t>Nguyễn Hoàng Duy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">chuẩn bị kiểm kê </t>
+  </si>
+  <si>
+    <t>24/09/2026 16:30:00</t>
+  </si>
+  <si>
+    <t>24/09/2026 18:00:00</t>
   </si>
   <si>
     <t>21/09/2026 12:30:00</t>
@@ -139,6 +193,24 @@
     <t>21/09/2026 14:00:00</t>
   </si>
   <si>
+    <t>chuẩn bị kiểm kê</t>
+  </si>
+  <si>
+    <t>23/09/2026 16:30:00</t>
+  </si>
+  <si>
+    <t>23/09/2026 18:00:00</t>
+  </si>
+  <si>
+    <t>24/09/2026 12:30:00</t>
+  </si>
+  <si>
+    <t>24/09/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>Chờ cấp trên gian tiếp</t>
+  </si>
+  <si>
     <t>23/09/2026 12:30:00</t>
   </si>
   <si>
@@ -151,43 +223,145 @@
     <t>16/09/2026 22:00:00</t>
   </si>
   <si>
+    <t>lắp đặt thiết bị</t>
+  </si>
+  <si>
+    <t>12/09/2026 07:45:00</t>
+  </si>
+  <si>
+    <t>12/09/2026 16:30:00</t>
+  </si>
+  <si>
+    <t>18/09/2026 20:30:00</t>
+  </si>
+  <si>
+    <t>18/09/2026 22:00:00</t>
+  </si>
+  <si>
     <t>22/09/2026 12:30:00</t>
   </si>
   <si>
     <t>22/09/2026 14:00:00</t>
   </si>
   <si>
-    <t>18/09/2026 20:30:00</t>
-  </si>
-  <si>
-    <t>18/09/2026 22:00:00</t>
-  </si>
-  <si>
-    <t>02222350</t>
-  </si>
-  <si>
-    <t>Hoàng Văn Nguyên</t>
-  </si>
-  <si>
-    <t>19/09/2026 06:00:00</t>
-  </si>
-  <si>
-    <t>19/09/2026 14:00:00</t>
-  </si>
-  <si>
-    <t>02020947</t>
-  </si>
-  <si>
-    <t>Nguyễn Hoàng Duy</t>
-  </si>
-  <si>
-    <t>chuẩn bị kiểm kê</t>
-  </si>
-  <si>
-    <t>23/09/2026 16:30:00</t>
-  </si>
-  <si>
-    <t>23/09/2026 18:00:00</t>
+    <t>15/09/2026 20:30:00</t>
+  </si>
+  <si>
+    <t>15/09/2026 22:00:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">vận chuyển nguyên vật liệu nghiền </t>
+  </si>
+  <si>
+    <t>19/09/2026 07:45:00</t>
+  </si>
+  <si>
+    <t>19/09/2026 16:30:00</t>
+  </si>
+  <si>
+    <t>22/09/2026 16:30:00</t>
+  </si>
+  <si>
+    <t>22/09/2026 18:00:00</t>
+  </si>
+  <si>
+    <t>02644075</t>
+  </si>
+  <si>
+    <t>Huỳnh Đại Nhân</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tăng cường sản xuất </t>
+  </si>
+  <si>
+    <t>14/09/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>14/09/2026 15:30:00</t>
+  </si>
+  <si>
+    <t>18/09/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>18/09/2026 15:30:00</t>
+  </si>
+  <si>
+    <t>23/09/2026 20:30:00</t>
+  </si>
+  <si>
+    <t>23/09/2026 22:00:00</t>
+  </si>
+  <si>
+    <t>17/09/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>17/09/2026 15:30:00</t>
+  </si>
+  <si>
+    <t>16/09/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>16/09/2026 15:30:00</t>
+  </si>
+  <si>
+    <t>22/09/2026 20:30:00</t>
+  </si>
+  <si>
+    <t>22/09/2026 22:00:00</t>
+  </si>
+  <si>
+    <t>21/09/2026 20:30:00</t>
+  </si>
+  <si>
+    <t>21/09/2026 22:00:00</t>
+  </si>
+  <si>
+    <t>15/09/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>15/09/2026 15:30:00</t>
+  </si>
+  <si>
+    <t>02644066</t>
+  </si>
+  <si>
+    <t>Nguyễn Hữu Tình</t>
+  </si>
+  <si>
+    <t>tang ca cat ong nhua</t>
+  </si>
+  <si>
+    <t>18/09/2026 12:30:00</t>
+  </si>
+  <si>
+    <t>tang ca van hanh may nghien</t>
+  </si>
+  <si>
+    <t>21/09/2026 15:30:00</t>
+  </si>
+  <si>
+    <t>24/09/2026 15:30:00</t>
+  </si>
+  <si>
+    <t>17/09/2026 12:30:00</t>
+  </si>
+  <si>
+    <t>tăng ca cǎt ông nhua</t>
+  </si>
+  <si>
+    <t>14/09/2026 12:30:00</t>
+  </si>
+  <si>
+    <t>23/09/2026 15:30:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tang ca cat ong nhua </t>
+  </si>
+  <si>
+    <t>15/09/2026 12:30:00</t>
+  </si>
+  <si>
+    <t>22/09/2026 15:30:00</t>
   </si>
   <si>
     <t>02243654</t>
@@ -197,177 +371,6 @@
   </si>
   <si>
     <t>Tăng Cường Sản Xuất</t>
-  </si>
-  <si>
-    <t>15/09/2026 20:30:00</t>
-  </si>
-  <si>
-    <t>15/09/2026 22:00:00</t>
-  </si>
-  <si>
-    <t>02644075</t>
-  </si>
-  <si>
-    <t>Huỳnh Đại Nhân</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tăng cường sản xuất </t>
-  </si>
-  <si>
-    <t>14/09/2026 14:00:00</t>
-  </si>
-  <si>
-    <t>14/09/2026 15:30:00</t>
-  </si>
-  <si>
-    <t>12/09/2026 22:00:00</t>
-  </si>
-  <si>
-    <t>13/09/2026 06:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">chuẩn bị kiểm kê </t>
-  </si>
-  <si>
-    <t>24/09/2026 16:30:00</t>
-  </si>
-  <si>
-    <t>24/09/2026 18:00:00</t>
-  </si>
-  <si>
-    <t>02644066</t>
-  </si>
-  <si>
-    <t>Nguyễn Hữu Tình</t>
-  </si>
-  <si>
-    <t>tang ca van hanh may nghien</t>
-  </si>
-  <si>
-    <t>23/09/2026 20:30:00</t>
-  </si>
-  <si>
-    <t>23/09/2026 22:00:00</t>
-  </si>
-  <si>
-    <t>Chờ cấp trên gian tiếp</t>
-  </si>
-  <si>
-    <t>tang ca cat ong nhua</t>
-  </si>
-  <si>
-    <t>18/09/2026 12:30:00</t>
-  </si>
-  <si>
-    <t>18/09/2026 14:00:00</t>
-  </si>
-  <si>
-    <t>22/09/2026 20:30:00</t>
-  </si>
-  <si>
-    <t>22/09/2026 22:00:00</t>
-  </si>
-  <si>
-    <t>02223605</t>
-  </si>
-  <si>
-    <t>Võ Minh Bắc</t>
-  </si>
-  <si>
-    <t>tăng cường sản xuất</t>
-  </si>
-  <si>
-    <t>22/09/2026 16:30:00</t>
-  </si>
-  <si>
-    <t>22/09/2026 18:00:00</t>
-  </si>
-  <si>
-    <t>24/09/2026 14:00:00</t>
-  </si>
-  <si>
-    <t>24/09/2026 15:30:00</t>
-  </si>
-  <si>
-    <t>17/09/2026 14:00:00</t>
-  </si>
-  <si>
-    <t>17/09/2026 15:30:00</t>
-  </si>
-  <si>
-    <t>21/09/2026 20:30:00</t>
-  </si>
-  <si>
-    <t>21/09/2026 22:00:00</t>
-  </si>
-  <si>
-    <t>23/09/2026 15:30:00</t>
-  </si>
-  <si>
-    <t>lắp đặt thiết bị</t>
-  </si>
-  <si>
-    <t>12/09/2026 07:45:00</t>
-  </si>
-  <si>
-    <t>12/09/2026 16:30:00</t>
-  </si>
-  <si>
-    <t>21/09/2026 15:30:00</t>
-  </si>
-  <si>
-    <t>17/09/2026 12:30:00</t>
-  </si>
-  <si>
-    <t>tăng ca cǎt ông nhua</t>
-  </si>
-  <si>
-    <t>14/09/2026 12:30:00</t>
-  </si>
-  <si>
-    <t>22/09/2026 15:30:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">vận chuyển nguyên vật liệu nghiền </t>
-  </si>
-  <si>
-    <t>19/09/2026 07:45:00</t>
-  </si>
-  <si>
-    <t>19/09/2026 16:30:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tang ca cat ong nhua </t>
-  </si>
-  <si>
-    <t>15/09/2026 12:30:00</t>
-  </si>
-  <si>
-    <t>15/09/2026 14:00:00</t>
-  </si>
-  <si>
-    <t>02622116</t>
-  </si>
-  <si>
-    <t>Trịnh Nhựt Khánh</t>
-  </si>
-  <si>
-    <t>16/09/2026 14:00:00</t>
-  </si>
-  <si>
-    <t>16/09/2026 15:30:00</t>
-  </si>
-  <si>
-    <t>18/09/2026 15:30:00</t>
-  </si>
-  <si>
-    <t>15/09/2026 15:30:00</t>
-  </si>
-  <si>
-    <t>02121404</t>
-  </si>
-  <si>
-    <t>Lê Hoàng Minh Tâm</t>
   </si>
 </sst>
 </file>
@@ -923,19 +926,19 @@
         <v>23</v>
       </c>
       <c r="H4" s="8" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="I4" s="8" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="J4" s="8">
-        <v>90</v>
+        <v>480</v>
       </c>
       <c r="K4" s="8" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="L4" s="8" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="M4" s="8">
         <v>0</v>
@@ -962,7 +965,7 @@
         <v>20</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="F5" s="7" t="s">
         <v>22</v>
@@ -971,19 +974,19 @@
         <v>23</v>
       </c>
       <c r="H5" s="8" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="I5" s="8" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="J5" s="8">
         <v>480</v>
       </c>
       <c r="K5" s="8" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="L5" s="8" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="M5" s="8">
         <v>0</v>
@@ -1019,19 +1022,19 @@
         <v>23</v>
       </c>
       <c r="H6" s="8" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="I6" s="8" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="J6" s="8">
-        <v>90</v>
+        <v>480</v>
       </c>
       <c r="K6" s="8" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="L6" s="8" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="M6" s="8">
         <v>0</v>
@@ -1046,10 +1049,10 @@
     </row>
     <row r="7" s="2" customFormat="1">
       <c r="A7" s="7" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="C7" s="7" t="s">
         <v>19</v>
@@ -1067,19 +1070,19 @@
         <v>23</v>
       </c>
       <c r="H7" s="8" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="I7" s="8" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="J7" s="8">
-        <v>90</v>
+        <v>480</v>
       </c>
       <c r="K7" s="8" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="L7" s="8" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="M7" s="8">
         <v>0</v>
@@ -1094,10 +1097,10 @@
     </row>
     <row r="8" s="2" customFormat="1">
       <c r="A8" s="7" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="C8" s="7" t="s">
         <v>19</v>
@@ -1106,7 +1109,7 @@
         <v>20</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="F8" s="7" t="s">
         <v>22</v>
@@ -1142,10 +1145,10 @@
     </row>
     <row r="9" s="2" customFormat="1">
       <c r="A9" s="7" t="s">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="C9" s="7" t="s">
         <v>19</v>
@@ -1154,7 +1157,7 @@
         <v>20</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="F9" s="7" t="s">
         <v>22</v>
@@ -1163,19 +1166,19 @@
         <v>23</v>
       </c>
       <c r="H9" s="8" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I9" s="8" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="J9" s="8">
         <v>480</v>
       </c>
       <c r="K9" s="8" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L9" s="8" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="M9" s="8">
         <v>0</v>
@@ -1190,10 +1193,10 @@
     </row>
     <row r="10" s="2" customFormat="1">
       <c r="A10" s="7" t="s">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="C10" s="7" t="s">
         <v>19</v>
@@ -1202,7 +1205,7 @@
         <v>20</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="F10" s="7" t="s">
         <v>22</v>
@@ -1211,19 +1214,19 @@
         <v>23</v>
       </c>
       <c r="H10" s="8" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I10" s="8" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J10" s="8">
         <v>480</v>
       </c>
       <c r="K10" s="8" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="L10" s="8" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="M10" s="8">
         <v>0</v>
@@ -1238,10 +1241,10 @@
     </row>
     <row r="11" s="2" customFormat="1">
       <c r="A11" s="7" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="C11" s="7" t="s">
         <v>19</v>
@@ -1250,7 +1253,7 @@
         <v>20</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="F11" s="7" t="s">
         <v>22</v>
@@ -1259,19 +1262,19 @@
         <v>23</v>
       </c>
       <c r="H11" s="8" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="I11" s="8" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="J11" s="8">
         <v>90</v>
       </c>
       <c r="K11" s="8" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="L11" s="8" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="M11" s="8">
         <v>0</v>
@@ -1286,10 +1289,10 @@
     </row>
     <row r="12" s="2" customFormat="1">
       <c r="A12" s="7" t="s">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="C12" s="7" t="s">
         <v>19</v>
@@ -1298,7 +1301,7 @@
         <v>20</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="F12" s="7" t="s">
         <v>22</v>
@@ -1307,19 +1310,19 @@
         <v>23</v>
       </c>
       <c r="H12" s="8" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="I12" s="8" t="s">
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="J12" s="8">
-        <v>90</v>
+        <v>480</v>
       </c>
       <c r="K12" s="8" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="L12" s="8" t="s">
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="M12" s="8">
         <v>0</v>
@@ -1334,10 +1337,10 @@
     </row>
     <row r="13" s="2" customFormat="1">
       <c r="A13" s="7" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="C13" s="7" t="s">
         <v>19</v>
@@ -1346,7 +1349,7 @@
         <v>20</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>30</v>
+        <v>49</v>
       </c>
       <c r="F13" s="7" t="s">
         <v>22</v>
@@ -1355,19 +1358,19 @@
         <v>23</v>
       </c>
       <c r="H13" s="8" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="I13" s="8" t="s">
-        <v>47</v>
+        <v>31</v>
       </c>
       <c r="J13" s="8">
-        <v>90</v>
+        <v>480</v>
       </c>
       <c r="K13" s="8" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="L13" s="8" t="s">
-        <v>47</v>
+        <v>31</v>
       </c>
       <c r="M13" s="8">
         <v>0</v>
@@ -1382,10 +1385,10 @@
     </row>
     <row r="14" s="2" customFormat="1">
       <c r="A14" s="7" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="C14" s="7" t="s">
         <v>19</v>
@@ -1394,7 +1397,7 @@
         <v>20</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="F14" s="7" t="s">
         <v>22</v>
@@ -1403,19 +1406,19 @@
         <v>23</v>
       </c>
       <c r="H14" s="8" t="s">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="I14" s="8" t="s">
-        <v>51</v>
+        <v>36</v>
       </c>
       <c r="J14" s="8">
         <v>480</v>
       </c>
       <c r="K14" s="8" t="s">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="L14" s="8" t="s">
-        <v>51</v>
+        <v>36</v>
       </c>
       <c r="M14" s="8">
         <v>0</v>
@@ -1430,10 +1433,10 @@
     </row>
     <row r="15" s="2" customFormat="1">
       <c r="A15" s="7" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="C15" s="7" t="s">
         <v>19</v>
@@ -1442,7 +1445,7 @@
         <v>20</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>54</v>
+        <v>21</v>
       </c>
       <c r="F15" s="7" t="s">
         <v>22</v>
@@ -1451,19 +1454,19 @@
         <v>23</v>
       </c>
       <c r="H15" s="8" t="s">
-        <v>55</v>
+        <v>32</v>
       </c>
       <c r="I15" s="8" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="J15" s="8">
-        <v>90</v>
+        <v>480</v>
       </c>
       <c r="K15" s="8" t="s">
-        <v>55</v>
+        <v>32</v>
       </c>
       <c r="L15" s="8" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="M15" s="8">
         <v>0</v>
@@ -1478,10 +1481,10 @@
     </row>
     <row r="16" s="2" customFormat="1">
       <c r="A16" s="7" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="C16" s="7" t="s">
         <v>19</v>
@@ -1490,7 +1493,7 @@
         <v>20</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="F16" s="7" t="s">
         <v>22</v>
@@ -1499,19 +1502,19 @@
         <v>23</v>
       </c>
       <c r="H16" s="8" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="I16" s="8" t="s">
-        <v>24</v>
+        <v>55</v>
       </c>
       <c r="J16" s="8">
-        <v>480</v>
+        <v>90</v>
       </c>
       <c r="K16" s="8" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="L16" s="8" t="s">
-        <v>24</v>
+        <v>55</v>
       </c>
       <c r="M16" s="8">
         <v>0</v>
@@ -1526,10 +1529,10 @@
     </row>
     <row r="17" s="2" customFormat="1">
       <c r="A17" s="7" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="C17" s="7" t="s">
         <v>19</v>
@@ -1538,7 +1541,7 @@
         <v>20</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="F17" s="7" t="s">
         <v>22</v>
@@ -1547,19 +1550,19 @@
         <v>23</v>
       </c>
       <c r="H17" s="8" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="I17" s="8" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="J17" s="8">
         <v>90</v>
       </c>
       <c r="K17" s="8" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="L17" s="8" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="M17" s="8">
         <v>0</v>
@@ -1574,10 +1577,10 @@
     </row>
     <row r="18" s="2" customFormat="1">
       <c r="A18" s="7" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="C18" s="7" t="s">
         <v>19</v>
@@ -1586,7 +1589,7 @@
         <v>20</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="F18" s="7" t="s">
         <v>22</v>
@@ -1595,19 +1598,19 @@
         <v>23</v>
       </c>
       <c r="H18" s="8" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="I18" s="8" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="J18" s="8">
         <v>90</v>
       </c>
       <c r="K18" s="8" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="L18" s="8" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="M18" s="8">
         <v>0</v>
@@ -1622,10 +1625,10 @@
     </row>
     <row r="19" s="2" customFormat="1">
       <c r="A19" s="7" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="C19" s="7" t="s">
         <v>19</v>
@@ -1634,7 +1637,7 @@
         <v>20</v>
       </c>
       <c r="E19" s="7" t="s">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="F19" s="7" t="s">
         <v>22</v>
@@ -1643,19 +1646,19 @@
         <v>23</v>
       </c>
       <c r="H19" s="8" t="s">
-        <v>35</v>
+        <v>61</v>
       </c>
       <c r="I19" s="8" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="J19" s="8">
-        <v>480</v>
+        <v>90</v>
       </c>
       <c r="K19" s="8" t="s">
-        <v>35</v>
+        <v>61</v>
       </c>
       <c r="L19" s="8" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="M19" s="8">
         <v>0</v>
@@ -1665,15 +1668,15 @@
         <v>26</v>
       </c>
       <c r="P19" s="8" t="s">
-        <v>27</v>
+        <v>63</v>
       </c>
     </row>
     <row r="20" s="2" customFormat="1">
       <c r="A20" s="7" t="s">
-        <v>57</v>
+        <v>37</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="C20" s="7" t="s">
         <v>19</v>
@@ -1682,7 +1685,7 @@
         <v>20</v>
       </c>
       <c r="E20" s="7" t="s">
-        <v>59</v>
+        <v>39</v>
       </c>
       <c r="F20" s="7" t="s">
         <v>22</v>
@@ -1691,19 +1694,19 @@
         <v>23</v>
       </c>
       <c r="H20" s="8" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="I20" s="8" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="J20" s="8">
-        <v>480</v>
+        <v>90</v>
       </c>
       <c r="K20" s="8" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="L20" s="8" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="M20" s="8">
         <v>0</v>
@@ -1718,10 +1721,10 @@
     </row>
     <row r="21" s="2" customFormat="1">
       <c r="A21" s="7" t="s">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>53</v>
+        <v>38</v>
       </c>
       <c r="C21" s="7" t="s">
         <v>19</v>
@@ -1730,7 +1733,7 @@
         <v>20</v>
       </c>
       <c r="E21" s="7" t="s">
-        <v>69</v>
+        <v>39</v>
       </c>
       <c r="F21" s="7" t="s">
         <v>22</v>
@@ -1739,19 +1742,19 @@
         <v>23</v>
       </c>
       <c r="H21" s="8" t="s">
-        <v>70</v>
+        <v>48</v>
       </c>
       <c r="I21" s="8" t="s">
-        <v>71</v>
+        <v>31</v>
       </c>
       <c r="J21" s="8">
-        <v>90</v>
+        <v>480</v>
       </c>
       <c r="K21" s="8" t="s">
-        <v>70</v>
+        <v>48</v>
       </c>
       <c r="L21" s="8" t="s">
-        <v>71</v>
+        <v>31</v>
       </c>
       <c r="M21" s="8">
         <v>0</v>
@@ -1766,10 +1769,10 @@
     </row>
     <row r="22" s="2" customFormat="1">
       <c r="A22" s="7" t="s">
-        <v>72</v>
+        <v>37</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>73</v>
+        <v>38</v>
       </c>
       <c r="C22" s="7" t="s">
         <v>19</v>
@@ -1778,7 +1781,7 @@
         <v>20</v>
       </c>
       <c r="E22" s="7" t="s">
-        <v>74</v>
+        <v>39</v>
       </c>
       <c r="F22" s="7" t="s">
         <v>22</v>
@@ -1787,19 +1790,19 @@
         <v>23</v>
       </c>
       <c r="H22" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="I22" s="8" t="s">
         <v>67</v>
       </c>
-      <c r="I22" s="8" t="s">
-        <v>68</v>
-      </c>
       <c r="J22" s="8">
-        <v>480</v>
+        <v>90</v>
       </c>
       <c r="K22" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="L22" s="8" t="s">
         <v>67</v>
-      </c>
-      <c r="L22" s="8" t="s">
-        <v>68</v>
       </c>
       <c r="M22" s="8">
         <v>0</v>
@@ -1814,10 +1817,10 @@
     </row>
     <row r="23" s="2" customFormat="1">
       <c r="A23" s="7" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="C23" s="7" t="s">
         <v>19</v>
@@ -1826,7 +1829,7 @@
         <v>20</v>
       </c>
       <c r="E23" s="7" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="F23" s="7" t="s">
         <v>22</v>
@@ -1835,19 +1838,19 @@
         <v>23</v>
       </c>
       <c r="H23" s="8" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="I23" s="8" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="J23" s="8">
-        <v>90</v>
+        <v>480</v>
       </c>
       <c r="K23" s="8" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="L23" s="8" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="M23" s="8">
         <v>0</v>
@@ -1857,45 +1860,45 @@
         <v>26</v>
       </c>
       <c r="P23" s="8" t="s">
-        <v>77</v>
+        <v>27</v>
       </c>
     </row>
     <row r="24" s="2" customFormat="1">
       <c r="A24" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="B24" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="C24" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D24" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E24" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="F24" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G24" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="H24" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="I24" s="8" t="s">
         <v>72</v>
-      </c>
-      <c r="B24" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="C24" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="D24" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="E24" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="F24" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="G24" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="H24" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="I24" s="8" t="s">
-        <v>80</v>
       </c>
       <c r="J24" s="8">
         <v>90</v>
       </c>
       <c r="K24" s="8" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="L24" s="8" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="M24" s="8">
         <v>0</v>
@@ -1910,10 +1913,10 @@
     </row>
     <row r="25" s="2" customFormat="1">
       <c r="A25" s="7" t="s">
-        <v>62</v>
+        <v>37</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>63</v>
+        <v>38</v>
       </c>
       <c r="C25" s="7" t="s">
         <v>19</v>
@@ -1922,7 +1925,7 @@
         <v>20</v>
       </c>
       <c r="E25" s="7" t="s">
-        <v>64</v>
+        <v>39</v>
       </c>
       <c r="F25" s="7" t="s">
         <v>22</v>
@@ -1931,19 +1934,19 @@
         <v>23</v>
       </c>
       <c r="H25" s="8" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="I25" s="8" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="J25" s="8">
         <v>90</v>
       </c>
       <c r="K25" s="8" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="L25" s="8" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="M25" s="8">
         <v>0</v>
@@ -1958,10 +1961,10 @@
     </row>
     <row r="26" s="2" customFormat="1">
       <c r="A26" s="7" t="s">
-        <v>83</v>
+        <v>37</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>84</v>
+        <v>38</v>
       </c>
       <c r="C26" s="7" t="s">
         <v>19</v>
@@ -1970,7 +1973,7 @@
         <v>20</v>
       </c>
       <c r="E26" s="7" t="s">
-        <v>85</v>
+        <v>39</v>
       </c>
       <c r="F26" s="7" t="s">
         <v>22</v>
@@ -1979,19 +1982,19 @@
         <v>23</v>
       </c>
       <c r="H26" s="8" t="s">
-        <v>51</v>
+        <v>75</v>
       </c>
       <c r="I26" s="8" t="s">
-        <v>24</v>
+        <v>76</v>
       </c>
       <c r="J26" s="8">
-        <v>480</v>
+        <v>90</v>
       </c>
       <c r="K26" s="8" t="s">
-        <v>51</v>
+        <v>75</v>
       </c>
       <c r="L26" s="8" t="s">
-        <v>24</v>
+        <v>76</v>
       </c>
       <c r="M26" s="8">
         <v>0</v>
@@ -2006,11 +2009,11 @@
     </row>
     <row r="27" s="2" customFormat="1">
       <c r="A27" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="B27" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="B27" s="7" t="s">
-        <v>53</v>
-      </c>
       <c r="C27" s="7" t="s">
         <v>19</v>
       </c>
@@ -2018,7 +2021,7 @@
         <v>20</v>
       </c>
       <c r="E27" s="7" t="s">
-        <v>54</v>
+        <v>77</v>
       </c>
       <c r="F27" s="7" t="s">
         <v>22</v>
@@ -2027,19 +2030,19 @@
         <v>23</v>
       </c>
       <c r="H27" s="8" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="I27" s="8" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="J27" s="8">
-        <v>90</v>
+        <v>480</v>
       </c>
       <c r="K27" s="8" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="L27" s="8" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="M27" s="8">
         <v>0</v>
@@ -2054,10 +2057,10 @@
     </row>
     <row r="28" s="2" customFormat="1">
       <c r="A28" s="7" t="s">
-        <v>83</v>
+        <v>51</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>84</v>
+        <v>52</v>
       </c>
       <c r="C28" s="7" t="s">
         <v>19</v>
@@ -2066,7 +2069,7 @@
         <v>20</v>
       </c>
       <c r="E28" s="7" t="s">
-        <v>85</v>
+        <v>58</v>
       </c>
       <c r="F28" s="7" t="s">
         <v>22</v>
@@ -2075,19 +2078,19 @@
         <v>23</v>
       </c>
       <c r="H28" s="8" t="s">
-        <v>67</v>
+        <v>80</v>
       </c>
       <c r="I28" s="8" t="s">
-        <v>68</v>
+        <v>81</v>
       </c>
       <c r="J28" s="8">
-        <v>480</v>
+        <v>90</v>
       </c>
       <c r="K28" s="8" t="s">
-        <v>67</v>
+        <v>80</v>
       </c>
       <c r="L28" s="8" t="s">
-        <v>68</v>
+        <v>81</v>
       </c>
       <c r="M28" s="8">
         <v>0</v>
@@ -2102,10 +2105,10 @@
     </row>
     <row r="29" s="2" customFormat="1">
       <c r="A29" s="7" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="C29" s="7" t="s">
         <v>19</v>
@@ -2114,7 +2117,7 @@
         <v>20</v>
       </c>
       <c r="E29" s="7" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="F29" s="7" t="s">
         <v>22</v>
@@ -2123,19 +2126,19 @@
         <v>23</v>
       </c>
       <c r="H29" s="8" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="I29" s="8" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="J29" s="8">
         <v>90</v>
       </c>
       <c r="K29" s="8" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="L29" s="8" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="M29" s="8">
         <v>0</v>
@@ -2150,10 +2153,10 @@
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>62</v>
+        <v>82</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>63</v>
+        <v>83</v>
       </c>
       <c r="C30" s="3" t="s">
         <v>19</v>
@@ -2162,7 +2165,7 @@
         <v>20</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>64</v>
+        <v>84</v>
       </c>
       <c r="F30" s="3" t="s">
         <v>22</v>
@@ -2171,19 +2174,19 @@
         <v>23</v>
       </c>
       <c r="H30" s="4" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="I30" s="4" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="J30" s="4">
         <v>90</v>
       </c>
       <c r="K30" s="4" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="L30" s="4" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="M30" s="4">
         <v>0</v>
@@ -2198,10 +2201,10 @@
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
-        <v>62</v>
+        <v>82</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>63</v>
+        <v>83</v>
       </c>
       <c r="C31" s="3" t="s">
         <v>19</v>
@@ -2210,7 +2213,7 @@
         <v>20</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>64</v>
+        <v>84</v>
       </c>
       <c r="F31" s="3" t="s">
         <v>22</v>
@@ -2219,19 +2222,19 @@
         <v>23</v>
       </c>
       <c r="H31" s="4" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="I31" s="4" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="J31" s="4">
         <v>90</v>
       </c>
       <c r="K31" s="4" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="L31" s="4" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="M31" s="4">
         <v>0</v>
@@ -2246,10 +2249,10 @@
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="C32" s="3" t="s">
         <v>19</v>
@@ -2258,7 +2261,7 @@
         <v>20</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="F32" s="3" t="s">
         <v>22</v>
@@ -2267,19 +2270,19 @@
         <v>23</v>
       </c>
       <c r="H32" s="4" t="s">
-        <v>41</v>
+        <v>91</v>
       </c>
       <c r="I32" s="4" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="J32" s="4">
         <v>90</v>
       </c>
       <c r="K32" s="4" t="s">
-        <v>41</v>
+        <v>91</v>
       </c>
       <c r="L32" s="4" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="M32" s="4">
         <v>0</v>
@@ -2294,10 +2297,10 @@
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
-        <v>62</v>
+        <v>82</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>63</v>
+        <v>83</v>
       </c>
       <c r="C33" s="3" t="s">
         <v>19</v>
@@ -2306,7 +2309,7 @@
         <v>20</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>64</v>
+        <v>84</v>
       </c>
       <c r="F33" s="3" t="s">
         <v>22</v>
@@ -2315,19 +2318,19 @@
         <v>23</v>
       </c>
       <c r="H33" s="4" t="s">
-        <v>35</v>
+        <v>93</v>
       </c>
       <c r="I33" s="4" t="s">
-        <v>67</v>
+        <v>94</v>
       </c>
       <c r="J33" s="4">
-        <v>480</v>
+        <v>90</v>
       </c>
       <c r="K33" s="4" t="s">
-        <v>35</v>
+        <v>93</v>
       </c>
       <c r="L33" s="4" t="s">
-        <v>67</v>
+        <v>94</v>
       </c>
       <c r="M33" s="4">
         <v>0</v>
@@ -2342,10 +2345,10 @@
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
-        <v>52</v>
+        <v>82</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>53</v>
+        <v>83</v>
       </c>
       <c r="C34" s="3" t="s">
         <v>19</v>
@@ -2354,28 +2357,28 @@
         <v>20</v>
       </c>
       <c r="E34" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="F34" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G34" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H34" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="F34" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G34" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H34" s="4" t="s">
+      <c r="I34" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="I34" s="4" t="s">
-        <v>97</v>
-      </c>
       <c r="J34" s="4">
-        <v>480</v>
+        <v>90</v>
       </c>
       <c r="K34" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="L34" s="4" t="s">
         <v>96</v>
-      </c>
-      <c r="L34" s="4" t="s">
-        <v>97</v>
       </c>
       <c r="M34" s="4">
         <v>0</v>
@@ -2390,10 +2393,10 @@
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="C35" s="3" t="s">
         <v>19</v>
@@ -2402,7 +2405,7 @@
         <v>20</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="F35" s="3" t="s">
         <v>22</v>
@@ -2411,19 +2414,19 @@
         <v>23</v>
       </c>
       <c r="H35" s="4" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="I35" s="4" t="s">
-        <v>98</v>
+        <v>32</v>
       </c>
       <c r="J35" s="4">
-        <v>90</v>
+        <v>480</v>
       </c>
       <c r="K35" s="4" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="L35" s="4" t="s">
-        <v>98</v>
+        <v>32</v>
       </c>
       <c r="M35" s="4">
         <v>0</v>
@@ -2438,10 +2441,10 @@
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="C36" s="3" t="s">
         <v>19</v>
@@ -2450,7 +2453,7 @@
         <v>20</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="F36" s="3" t="s">
         <v>22</v>
@@ -2459,19 +2462,19 @@
         <v>23</v>
       </c>
       <c r="H36" s="4" t="s">
-        <v>99</v>
+        <v>24</v>
       </c>
       <c r="I36" s="4" t="s">
-        <v>90</v>
+        <v>25</v>
       </c>
       <c r="J36" s="4">
-        <v>90</v>
+        <v>480</v>
       </c>
       <c r="K36" s="4" t="s">
-        <v>99</v>
+        <v>24</v>
       </c>
       <c r="L36" s="4" t="s">
-        <v>90</v>
+        <v>25</v>
       </c>
       <c r="M36" s="4">
         <v>0</v>
@@ -2486,10 +2489,10 @@
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="C37" s="3" t="s">
         <v>19</v>
@@ -2498,7 +2501,7 @@
         <v>20</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>100</v>
+        <v>84</v>
       </c>
       <c r="F37" s="3" t="s">
         <v>22</v>
@@ -2507,19 +2510,19 @@
         <v>23</v>
       </c>
       <c r="H37" s="4" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="I37" s="4" t="s">
-        <v>65</v>
+        <v>98</v>
       </c>
       <c r="J37" s="4">
         <v>90</v>
       </c>
       <c r="K37" s="4" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="L37" s="4" t="s">
-        <v>65</v>
+        <v>98</v>
       </c>
       <c r="M37" s="4">
         <v>0</v>
@@ -2534,10 +2537,10 @@
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
-        <v>62</v>
+        <v>82</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>63</v>
+        <v>83</v>
       </c>
       <c r="C38" s="3" t="s">
         <v>19</v>
@@ -2546,7 +2549,7 @@
         <v>20</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>64</v>
+        <v>84</v>
       </c>
       <c r="F38" s="3" t="s">
         <v>22</v>
@@ -2555,19 +2558,19 @@
         <v>23</v>
       </c>
       <c r="H38" s="4" t="s">
-        <v>50</v>
+        <v>99</v>
       </c>
       <c r="I38" s="4" t="s">
-        <v>51</v>
+        <v>100</v>
       </c>
       <c r="J38" s="4">
-        <v>480</v>
+        <v>90</v>
       </c>
       <c r="K38" s="4" t="s">
-        <v>50</v>
+        <v>99</v>
       </c>
       <c r="L38" s="4" t="s">
-        <v>51</v>
+        <v>100</v>
       </c>
       <c r="M38" s="4">
         <v>0</v>
@@ -2582,10 +2585,10 @@
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
-        <v>72</v>
+        <v>101</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>73</v>
+        <v>102</v>
       </c>
       <c r="C39" s="3" t="s">
         <v>19</v>
@@ -2594,7 +2597,7 @@
         <v>20</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>78</v>
+        <v>103</v>
       </c>
       <c r="F39" s="3" t="s">
         <v>22</v>
@@ -2603,19 +2606,19 @@
         <v>23</v>
       </c>
       <c r="H39" s="4" t="s">
-        <v>45</v>
+        <v>104</v>
       </c>
       <c r="I39" s="4" t="s">
-        <v>102</v>
+        <v>87</v>
       </c>
       <c r="J39" s="4">
         <v>90</v>
       </c>
       <c r="K39" s="4" t="s">
-        <v>45</v>
+        <v>104</v>
       </c>
       <c r="L39" s="4" t="s">
-        <v>102</v>
+        <v>87</v>
       </c>
       <c r="M39" s="4">
         <v>0</v>
@@ -2630,10 +2633,10 @@
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
-        <v>52</v>
+        <v>101</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>53</v>
+        <v>102</v>
       </c>
       <c r="C40" s="3" t="s">
         <v>19</v>
@@ -2642,7 +2645,7 @@
         <v>20</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="F40" s="3" t="s">
         <v>22</v>
@@ -2651,19 +2654,19 @@
         <v>23</v>
       </c>
       <c r="H40" s="4" t="s">
-        <v>104</v>
+        <v>25</v>
       </c>
       <c r="I40" s="4" t="s">
-        <v>105</v>
+        <v>35</v>
       </c>
       <c r="J40" s="4">
         <v>480</v>
       </c>
       <c r="K40" s="4" t="s">
-        <v>104</v>
+        <v>25</v>
       </c>
       <c r="L40" s="4" t="s">
-        <v>105</v>
+        <v>35</v>
       </c>
       <c r="M40" s="4">
         <v>0</v>
@@ -2678,10 +2681,10 @@
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
-        <v>72</v>
+        <v>101</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>73</v>
+        <v>102</v>
       </c>
       <c r="C41" s="3" t="s">
         <v>19</v>
@@ -2690,28 +2693,28 @@
         <v>20</v>
       </c>
       <c r="E41" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="F41" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G41" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H41" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="I41" s="4" t="s">
         <v>106</v>
-      </c>
-      <c r="F41" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G41" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H41" s="4" t="s">
-        <v>107</v>
-      </c>
-      <c r="I41" s="4" t="s">
-        <v>108</v>
       </c>
       <c r="J41" s="4">
         <v>90</v>
       </c>
       <c r="K41" s="4" t="s">
-        <v>107</v>
+        <v>57</v>
       </c>
       <c r="L41" s="4" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="M41" s="4">
         <v>0</v>
@@ -2726,10 +2729,10 @@
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
-        <v>72</v>
+        <v>101</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>73</v>
+        <v>102</v>
       </c>
       <c r="C42" s="3" t="s">
         <v>19</v>
@@ -2738,7 +2741,7 @@
         <v>20</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>74</v>
+        <v>103</v>
       </c>
       <c r="F42" s="3" t="s">
         <v>22</v>
@@ -2747,19 +2750,19 @@
         <v>23</v>
       </c>
       <c r="H42" s="4" t="s">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="I42" s="4" t="s">
-        <v>24</v>
+        <v>107</v>
       </c>
       <c r="J42" s="4">
-        <v>480</v>
+        <v>90</v>
       </c>
       <c r="K42" s="4" t="s">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="L42" s="4" t="s">
-        <v>24</v>
+        <v>107</v>
       </c>
       <c r="M42" s="4">
         <v>0</v>
@@ -2774,10 +2777,10 @@
     </row>
     <row r="43">
       <c r="A43" s="3" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="C43" s="3" t="s">
         <v>19</v>
@@ -2786,7 +2789,7 @@
         <v>20</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>85</v>
+        <v>103</v>
       </c>
       <c r="F43" s="3" t="s">
         <v>22</v>
@@ -2795,19 +2798,19 @@
         <v>23</v>
       </c>
       <c r="H43" s="4" t="s">
-        <v>34</v>
+        <v>108</v>
       </c>
       <c r="I43" s="4" t="s">
-        <v>35</v>
+        <v>91</v>
       </c>
       <c r="J43" s="4">
-        <v>480</v>
+        <v>90</v>
       </c>
       <c r="K43" s="4" t="s">
-        <v>34</v>
+        <v>108</v>
       </c>
       <c r="L43" s="4" t="s">
-        <v>35</v>
+        <v>91</v>
       </c>
       <c r="M43" s="4">
         <v>0</v>
@@ -2822,10 +2825,10 @@
     </row>
     <row r="44">
       <c r="A44" s="3" t="s">
-        <v>62</v>
+        <v>101</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>63</v>
+        <v>102</v>
       </c>
       <c r="C44" s="3" t="s">
         <v>19</v>
@@ -2834,7 +2837,7 @@
         <v>20</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>64</v>
+        <v>109</v>
       </c>
       <c r="F44" s="3" t="s">
         <v>22</v>
@@ -2843,19 +2846,19 @@
         <v>23</v>
       </c>
       <c r="H44" s="4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="I44" s="4" t="s">
-        <v>112</v>
+        <v>85</v>
       </c>
       <c r="J44" s="4">
         <v>90</v>
       </c>
       <c r="K44" s="4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="L44" s="4" t="s">
-        <v>112</v>
+        <v>85</v>
       </c>
       <c r="M44" s="4">
         <v>0</v>
@@ -2870,10 +2873,10 @@
     </row>
     <row r="45">
       <c r="A45" s="3" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="C45" s="3" t="s">
         <v>19</v>
@@ -2882,7 +2885,7 @@
         <v>20</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>85</v>
+        <v>103</v>
       </c>
       <c r="F45" s="3" t="s">
         <v>22</v>
@@ -2891,19 +2894,19 @@
         <v>23</v>
       </c>
       <c r="H45" s="4" t="s">
-        <v>24</v>
+        <v>65</v>
       </c>
       <c r="I45" s="4" t="s">
-        <v>25</v>
+        <v>111</v>
       </c>
       <c r="J45" s="4">
-        <v>480</v>
+        <v>90</v>
       </c>
       <c r="K45" s="4" t="s">
-        <v>24</v>
+        <v>65</v>
       </c>
       <c r="L45" s="4" t="s">
-        <v>25</v>
+        <v>111</v>
       </c>
       <c r="M45" s="4">
         <v>0</v>
@@ -2918,10 +2921,10 @@
     </row>
     <row r="46">
       <c r="A46" s="3" t="s">
-        <v>62</v>
+        <v>101</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>63</v>
+        <v>102</v>
       </c>
       <c r="C46" s="3" t="s">
         <v>19</v>
@@ -2930,7 +2933,7 @@
         <v>20</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>64</v>
+        <v>112</v>
       </c>
       <c r="F46" s="3" t="s">
         <v>22</v>
@@ -2939,19 +2942,19 @@
         <v>23</v>
       </c>
       <c r="H46" s="4" t="s">
-        <v>80</v>
+        <v>113</v>
       </c>
       <c r="I46" s="4" t="s">
-        <v>113</v>
+        <v>99</v>
       </c>
       <c r="J46" s="4">
         <v>90</v>
       </c>
       <c r="K46" s="4" t="s">
-        <v>80</v>
+        <v>113</v>
       </c>
       <c r="L46" s="4" t="s">
-        <v>113</v>
+        <v>99</v>
       </c>
       <c r="M46" s="4">
         <v>0</v>
@@ -2966,10 +2969,10 @@
     </row>
     <row r="47">
       <c r="A47" s="3" t="s">
-        <v>62</v>
+        <v>101</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>63</v>
+        <v>102</v>
       </c>
       <c r="C47" s="3" t="s">
         <v>19</v>
@@ -2978,7 +2981,7 @@
         <v>20</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>64</v>
+        <v>105</v>
       </c>
       <c r="F47" s="3" t="s">
         <v>22</v>
@@ -2987,19 +2990,19 @@
         <v>23</v>
       </c>
       <c r="H47" s="4" t="s">
-        <v>108</v>
+        <v>32</v>
       </c>
       <c r="I47" s="4" t="s">
-        <v>114</v>
+        <v>50</v>
       </c>
       <c r="J47" s="4">
-        <v>90</v>
+        <v>480</v>
       </c>
       <c r="K47" s="4" t="s">
-        <v>108</v>
+        <v>32</v>
       </c>
       <c r="L47" s="4" t="s">
-        <v>114</v>
+        <v>50</v>
       </c>
       <c r="M47" s="4">
         <v>0</v>
@@ -3014,10 +3017,10 @@
     </row>
     <row r="48">
       <c r="A48" s="3" t="s">
-        <v>115</v>
+        <v>101</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>116</v>
+        <v>102</v>
       </c>
       <c r="C48" s="3" t="s">
         <v>19</v>
@@ -3026,7 +3029,7 @@
         <v>20</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>85</v>
+        <v>103</v>
       </c>
       <c r="F48" s="3" t="s">
         <v>22</v>
@@ -3035,19 +3038,19 @@
         <v>23</v>
       </c>
       <c r="H48" s="4" t="s">
-        <v>50</v>
+        <v>74</v>
       </c>
       <c r="I48" s="4" t="s">
-        <v>51</v>
+        <v>114</v>
       </c>
       <c r="J48" s="4">
-        <v>480</v>
+        <v>90</v>
       </c>
       <c r="K48" s="4" t="s">
-        <v>50</v>
+        <v>74</v>
       </c>
       <c r="L48" s="4" t="s">
-        <v>51</v>
+        <v>114</v>
       </c>
       <c r="M48" s="4">
         <v>0</v>
@@ -3074,7 +3077,7 @@
         <v>20</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>85</v>
+        <v>117</v>
       </c>
       <c r="F49" s="3" t="s">
         <v>22</v>
@@ -3083,19 +3086,19 @@
         <v>23</v>
       </c>
       <c r="H49" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="I49" s="4" t="s">
         <v>35</v>
-      </c>
-      <c r="I49" s="4" t="s">
-        <v>67</v>
       </c>
       <c r="J49" s="4">
         <v>480</v>
       </c>
       <c r="K49" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="L49" s="4" t="s">
         <v>35</v>
-      </c>
-      <c r="L49" s="4" t="s">
-        <v>67</v>
       </c>
       <c r="M49" s="4">
         <v>0</v>
@@ -3105,6 +3108,54 @@
         <v>26</v>
       </c>
       <c r="P49" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="C50" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D50" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E50" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="F50" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G50" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H50" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="I50" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="J50" s="4">
+        <v>480</v>
+      </c>
+      <c r="K50" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="L50" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="M50" s="4">
+        <v>0</v>
+      </c>
+      <c r="N50" s="3"/>
+      <c r="O50" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="P50" s="4" t="s">
         <v>27</v>
       </c>
     </row>

--- a/data/hrm_sync_actual_2.xlsx
+++ b/data/hrm_sync_actual_2.xlsx
@@ -70,37 +70,166 @@
     <t>Trạng thái duyệt</t>
   </si>
   <si>
+    <t>02223526</t>
+  </si>
+  <si>
+    <t>Nguyễn Thiên Phú</t>
+  </si>
+  <si>
+    <t>Plastic Extrusion</t>
+  </si>
+  <si>
+    <t>Pulverize</t>
+  </si>
+  <si>
+    <t>Tăng cường sản xuất</t>
+  </si>
+  <si>
+    <t>Nguyễn Chí Cường</t>
+  </si>
+  <si>
+    <t>Thân Trọng Tuấn</t>
+  </si>
+  <si>
+    <t>19/09/2026 22:00:00</t>
+  </si>
+  <si>
+    <t>20/09/2026 06:00:00</t>
+  </si>
+  <si>
+    <t>Bằng KH</t>
+  </si>
+  <si>
+    <t>Đã duyệt</t>
+  </si>
+  <si>
+    <t>02622116</t>
+  </si>
+  <si>
+    <t>Trịnh Nhựt Khánh</t>
+  </si>
+  <si>
+    <t>tăng cường sản xuất</t>
+  </si>
+  <si>
+    <t>26/09/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>26/09/2026 22:00:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tăng cường sản xuất </t>
+  </si>
+  <si>
+    <t>12/09/2026 06:00:00</t>
+  </si>
+  <si>
+    <t>12/09/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>02644057</t>
+  </si>
+  <si>
+    <t>Phạm Văn Công</t>
+  </si>
+  <si>
+    <t>tăng ca đáp ứng tiến độ sản xuất</t>
+  </si>
+  <si>
+    <t>17/09/2026 20:30:00</t>
+  </si>
+  <si>
+    <t>17/09/2026 22:00:00</t>
+  </si>
+  <si>
+    <t>14/09/2026 20:30:00</t>
+  </si>
+  <si>
+    <t>14/09/2026 22:00:00</t>
+  </si>
+  <si>
+    <t>02644066</t>
+  </si>
+  <si>
+    <t>Nguyễn Hữu Tình</t>
+  </si>
+  <si>
+    <t>tang ca cat ong nhua</t>
+  </si>
+  <si>
+    <t>18/09/2026 12:30:00</t>
+  </si>
+  <si>
+    <t>18/09/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>21/09/2026 12:30:00</t>
+  </si>
+  <si>
+    <t>21/09/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>02222350</t>
+  </si>
+  <si>
+    <t>Hoàng Văn Nguyên</t>
+  </si>
+  <si>
+    <t>19/09/2026 06:00:00</t>
+  </si>
+  <si>
+    <t>19/09/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>tang ca van hanh may nghien</t>
+  </si>
+  <si>
+    <t>12/09/2026 22:00:00</t>
+  </si>
+  <si>
     <t>02020947</t>
   </si>
   <si>
     <t>Nguyễn Hoàng Duy</t>
   </si>
   <si>
-    <t>Plastic Extrusion</t>
-  </si>
-  <si>
-    <t>Pulverize</t>
-  </si>
-  <si>
     <t xml:space="preserve">chuẩn bị kiểm kê </t>
   </si>
   <si>
-    <t>Nguyễn Chí Cường</t>
-  </si>
-  <si>
-    <t>Thân Trọng Tuấn</t>
-  </si>
-  <si>
     <t>24/09/2026 16:30:00</t>
   </si>
   <si>
     <t>24/09/2026 18:00:00</t>
   </si>
   <si>
-    <t>Bằng KH</t>
-  </si>
-  <si>
-    <t>Đã duyệt</t>
+    <t xml:space="preserve">tang ca cat ong nhua </t>
+  </si>
+  <si>
+    <t>15/09/2026 12:30:00</t>
+  </si>
+  <si>
+    <t>15/09/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>chuẩn bị kiểm kê</t>
+  </si>
+  <si>
+    <t>23/09/2026 16:30:00</t>
+  </si>
+  <si>
+    <t>23/09/2026 18:00:00</t>
+  </si>
+  <si>
+    <t>27/09/2026 06:00:00</t>
+  </si>
+  <si>
+    <t>21/09/2026 15:30:00</t>
+  </si>
+  <si>
+    <t>02223605</t>
+  </si>
+  <si>
+    <t>Võ Minh Bắc</t>
   </si>
   <si>
     <t>lắp đặt thiết bị</t>
@@ -112,13 +241,25 @@
     <t>12/09/2026 16:30:00</t>
   </si>
   <si>
-    <t>chuẩn bị kiểm kê</t>
-  </si>
-  <si>
-    <t>23/09/2026 16:30:00</t>
-  </si>
-  <si>
-    <t>23/09/2026 18:00:00</t>
+    <t>25/09/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>25/09/2026 15:30:00</t>
+  </si>
+  <si>
+    <t>24/09/2026 12:30:00</t>
+  </si>
+  <si>
+    <t>24/09/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>tăng ca cǎt ông nhua</t>
+  </si>
+  <si>
+    <t>14/09/2026 12:30:00</t>
+  </si>
+  <si>
+    <t>14/09/2026 14:00:00</t>
   </si>
   <si>
     <t xml:space="preserve">vận chuyển nguyên vật liệu </t>
@@ -130,6 +271,9 @@
     <t>26/09/2026 16:30:00</t>
   </si>
   <si>
+    <t>13/09/2026 06:00:00</t>
+  </si>
+  <si>
     <t xml:space="preserve">vận chuyển nguyên vật liệu nghiền </t>
   </si>
   <si>
@@ -139,148 +283,85 @@
     <t>19/09/2026 16:30:00</t>
   </si>
   <si>
+    <t>26/09/2026 06:00:00</t>
+  </si>
+  <si>
+    <t>25/09/2026 12:30:00</t>
+  </si>
+  <si>
     <t>22/09/2026 16:30:00</t>
   </si>
   <si>
     <t>22/09/2026 18:00:00</t>
   </si>
   <si>
-    <t>02644066</t>
-  </si>
-  <si>
-    <t>Nguyễn Hữu Tình</t>
-  </si>
-  <si>
-    <t>tang ca cat ong nhua</t>
-  </si>
-  <si>
-    <t>18/09/2026 12:30:00</t>
-  </si>
-  <si>
-    <t>18/09/2026 14:00:00</t>
-  </si>
-  <si>
-    <t>tang ca van hanh may nghien</t>
-  </si>
-  <si>
-    <t>19/09/2026 14:00:00</t>
-  </si>
-  <si>
-    <t>19/09/2026 22:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tang ca cat ong nhua </t>
-  </si>
-  <si>
-    <t>15/09/2026 12:30:00</t>
-  </si>
-  <si>
-    <t>15/09/2026 14:00:00</t>
-  </si>
-  <si>
-    <t>25/09/2026 14:00:00</t>
-  </si>
-  <si>
-    <t>25/09/2026 15:30:00</t>
-  </si>
-  <si>
-    <t>02222350</t>
-  </si>
-  <si>
-    <t>Hoàng Văn Nguyên</t>
-  </si>
-  <si>
-    <t>Tăng cường sản xuất</t>
-  </si>
-  <si>
-    <t>26/09/2026 22:00:00</t>
-  </si>
-  <si>
-    <t>27/09/2026 06:00:00</t>
-  </si>
-  <si>
-    <t>tăng ca cǎt ông nhua</t>
-  </si>
-  <si>
-    <t>14/09/2026 12:30:00</t>
-  </si>
-  <si>
-    <t>14/09/2026 14:00:00</t>
-  </si>
-  <si>
-    <t>02223526</t>
-  </si>
-  <si>
-    <t>Nguyễn Thiên Phú</t>
-  </si>
-  <si>
-    <t>26/09/2026 14:00:00</t>
-  </si>
-  <si>
-    <t>02644057</t>
-  </si>
-  <si>
-    <t>Phạm Văn Công</t>
-  </si>
-  <si>
-    <t>tăng ca đáp ứng tiến độ sản xuất</t>
-  </si>
-  <si>
-    <t>17/09/2026 20:30:00</t>
-  </si>
-  <si>
-    <t>17/09/2026 22:00:00</t>
-  </si>
-  <si>
-    <t>20/09/2026 06:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tăng cường sản xuất </t>
-  </si>
-  <si>
-    <t>12/09/2026 06:00:00</t>
-  </si>
-  <si>
-    <t>12/09/2026 14:00:00</t>
-  </si>
-  <si>
-    <t>21/09/2026 14:00:00</t>
-  </si>
-  <si>
-    <t>21/09/2026 15:30:00</t>
-  </si>
-  <si>
-    <t>24/09/2026 14:00:00</t>
-  </si>
-  <si>
     <t>24/09/2026 15:30:00</t>
   </si>
   <si>
-    <t>26/09/2026 06:00:00</t>
-  </si>
-  <si>
     <t>17/09/2026 12:30:00</t>
   </si>
   <si>
     <t>17/09/2026 14:00:00</t>
   </si>
   <si>
+    <t>15/09/2026 20:30:00</t>
+  </si>
+  <si>
+    <t>15/09/2026 22:00:00</t>
+  </si>
+  <si>
+    <t>22/09/2026 12:30:00</t>
+  </si>
+  <si>
+    <t>22/09/2026 14:00:00</t>
+  </si>
+  <si>
     <t>23/09/2026 14:00:00</t>
   </si>
   <si>
     <t>23/09/2026 15:30:00</t>
   </si>
   <si>
-    <t>22/09/2026 14:00:00</t>
+    <t>23/09/2026 12:30:00</t>
+  </si>
+  <si>
+    <t>16/09/2026 20:30:00</t>
+  </si>
+  <si>
+    <t>16/09/2026 22:00:00</t>
+  </si>
+  <si>
+    <t>18/09/2026 20:30:00</t>
+  </si>
+  <si>
+    <t>18/09/2026 22:00:00</t>
   </si>
   <si>
     <t>22/09/2026 15:30:00</t>
   </si>
   <si>
-    <t>12/09/2026 22:00:00</t>
-  </si>
-  <si>
-    <t>13/09/2026 06:00:00</t>
+    <t>02644075</t>
+  </si>
+  <si>
+    <t>Huỳnh Đại Nhân</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tăng cường sản xuất </t>
+  </si>
+  <si>
+    <t>14/09/2026 15:30:00</t>
+  </si>
+  <si>
+    <t>24/09/2026 20:30:00</t>
+  </si>
+  <si>
+    <t>24/09/2026 22:00:00</t>
+  </si>
+  <si>
+    <t>23/09/2026 20:30:00</t>
+  </si>
+  <si>
+    <t>23/09/2026 22:00:00</t>
   </si>
   <si>
     <t>02243654</t>
@@ -292,70 +373,7 @@
     <t>Tăng Cường Sản Xuất</t>
   </si>
   <si>
-    <t>02622116</t>
-  </si>
-  <si>
-    <t>Trịnh Nhựt Khánh</t>
-  </si>
-  <si>
-    <t>tăng cường sản xuất</t>
-  </si>
-  <si>
-    <t>14/09/2026 20:30:00</t>
-  </si>
-  <si>
-    <t>14/09/2026 22:00:00</t>
-  </si>
-  <si>
-    <t>21/09/2026 12:30:00</t>
-  </si>
-  <si>
-    <t>15/09/2026 20:30:00</t>
-  </si>
-  <si>
-    <t>15/09/2026 22:00:00</t>
-  </si>
-  <si>
-    <t>22/09/2026 12:30:00</t>
-  </si>
-  <si>
-    <t>25/09/2026 12:30:00</t>
-  </si>
-  <si>
-    <t>24/09/2026 12:30:00</t>
-  </si>
-  <si>
-    <t>23/09/2026 12:30:00</t>
-  </si>
-  <si>
-    <t>16/09/2026 20:30:00</t>
-  </si>
-  <si>
-    <t>16/09/2026 22:00:00</t>
-  </si>
-  <si>
-    <t>18/09/2026 20:30:00</t>
-  </si>
-  <si>
-    <t>18/09/2026 22:00:00</t>
-  </si>
-  <si>
-    <t>02644075</t>
-  </si>
-  <si>
-    <t>Huỳnh Đại Nhân</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tăng cường sản xuất </t>
-  </si>
-  <si>
-    <t>14/09/2026 15:30:00</t>
-  </si>
-  <si>
-    <t>24/09/2026 20:30:00</t>
-  </si>
-  <si>
-    <t>24/09/2026 22:00:00</t>
+    <t>17/09/2026 15:30:00</t>
   </si>
   <si>
     <t>25/09/2026 20:30:00</t>
@@ -364,55 +382,34 @@
     <t>25/09/2026 22:30:00</t>
   </si>
   <si>
-    <t>23/09/2026 20:30:00</t>
-  </si>
-  <si>
-    <t>23/09/2026 22:00:00</t>
-  </si>
-  <si>
-    <t>17/09/2026 15:30:00</t>
+    <t>21/09/2026 20:30:00</t>
+  </si>
+  <si>
+    <t>21/09/2026 22:00:00</t>
+  </si>
+  <si>
+    <t>15/09/2026 15:30:00</t>
+  </si>
+  <si>
+    <t>22/09/2026 20:30:00</t>
+  </si>
+  <si>
+    <t>22/09/2026 22:00:00</t>
+  </si>
+  <si>
+    <t>16/09/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>16/09/2026 15:30:00</t>
   </si>
   <si>
     <t>18/09/2026 15:30:00</t>
   </si>
   <si>
-    <t>15/09/2026 15:30:00</t>
-  </si>
-  <si>
-    <t>21/09/2026 20:30:00</t>
-  </si>
-  <si>
-    <t>21/09/2026 22:00:00</t>
-  </si>
-  <si>
-    <t>16/09/2026 14:00:00</t>
-  </si>
-  <si>
-    <t>16/09/2026 15:30:00</t>
-  </si>
-  <si>
-    <t>22/09/2026 20:30:00</t>
-  </si>
-  <si>
-    <t>22/09/2026 22:00:00</t>
-  </si>
-  <si>
-    <t>19/09/2026 06:00:00</t>
-  </si>
-  <si>
     <t>02121404</t>
   </si>
   <si>
     <t>Lê Hoàng Minh Tâm</t>
-  </si>
-  <si>
-    <t>Chờ cấp trên gian tiếp</t>
-  </si>
-  <si>
-    <t>02223605</t>
-  </si>
-  <si>
-    <t>Võ Minh Bắc</t>
   </si>
 </sst>
 </file>
@@ -926,7 +923,7 @@
         <v>25</v>
       </c>
       <c r="J3" s="8">
-        <v>90</v>
+        <v>480</v>
       </c>
       <c r="K3" s="8" t="s">
         <v>24</v>
@@ -947,10 +944,10 @@
     </row>
     <row r="4" s="2" customFormat="1">
       <c r="A4" s="7" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="C4" s="7" t="s">
         <v>19</v>
@@ -959,7 +956,7 @@
         <v>20</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F4" s="7" t="s">
         <v>22</v>
@@ -968,19 +965,19 @@
         <v>23</v>
       </c>
       <c r="H4" s="8" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="I4" s="8" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="J4" s="8">
         <v>480</v>
       </c>
       <c r="K4" s="8" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="L4" s="8" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="M4" s="8">
         <v>0</v>
@@ -1007,7 +1004,7 @@
         <v>20</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F5" s="7" t="s">
         <v>22</v>
@@ -1016,19 +1013,19 @@
         <v>23</v>
       </c>
       <c r="H5" s="8" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="I5" s="8" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="J5" s="8">
-        <v>90</v>
+        <v>480</v>
       </c>
       <c r="K5" s="8" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="L5" s="8" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="M5" s="8">
         <v>0</v>
@@ -1043,10 +1040,10 @@
     </row>
     <row r="6" s="2" customFormat="1">
       <c r="A6" s="7" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="C6" s="7" t="s">
         <v>19</v>
@@ -1055,7 +1052,7 @@
         <v>20</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="F6" s="7" t="s">
         <v>22</v>
@@ -1064,19 +1061,19 @@
         <v>23</v>
       </c>
       <c r="H6" s="8" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="I6" s="8" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="J6" s="8">
         <v>480</v>
       </c>
       <c r="K6" s="8" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="L6" s="8" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="M6" s="8">
         <v>0</v>
@@ -1091,10 +1088,10 @@
     </row>
     <row r="7" s="2" customFormat="1">
       <c r="A7" s="7" t="s">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="C7" s="7" t="s">
         <v>19</v>
@@ -1103,7 +1100,7 @@
         <v>20</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F7" s="7" t="s">
         <v>22</v>
@@ -1112,19 +1109,19 @@
         <v>23</v>
       </c>
       <c r="H7" s="8" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I7" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="J7" s="8">
+        <v>90</v>
+      </c>
+      <c r="K7" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="J7" s="8">
-        <v>480</v>
-      </c>
-      <c r="K7" s="8" t="s">
-        <v>38</v>
-      </c>
       <c r="L7" s="8" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="M7" s="8">
         <v>0</v>
@@ -1139,10 +1136,10 @@
     </row>
     <row r="8" s="2" customFormat="1">
       <c r="A8" s="7" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="C8" s="7" t="s">
         <v>19</v>
@@ -1151,7 +1148,7 @@
         <v>20</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F8" s="7" t="s">
         <v>22</v>
@@ -1160,19 +1157,19 @@
         <v>23</v>
       </c>
       <c r="H8" s="8" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="I8" s="8" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="J8" s="8">
-        <v>90</v>
+        <v>480</v>
       </c>
       <c r="K8" s="8" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="L8" s="8" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="M8" s="8">
         <v>0</v>
@@ -1187,40 +1184,40 @@
     </row>
     <row r="9" s="2" customFormat="1">
       <c r="A9" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="F9" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G9" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="H9" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="I9" s="8" t="s">
         <v>42</v>
-      </c>
-      <c r="B9" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="C9" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="D9" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="E9" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="F9" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="G9" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="H9" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="I9" s="8" t="s">
-        <v>46</v>
       </c>
       <c r="J9" s="8">
         <v>90</v>
       </c>
       <c r="K9" s="8" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="L9" s="8" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="M9" s="8">
         <v>0</v>
@@ -1235,10 +1232,10 @@
     </row>
     <row r="10" s="2" customFormat="1">
       <c r="A10" s="7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C10" s="7" t="s">
         <v>19</v>
@@ -1247,28 +1244,28 @@
         <v>20</v>
       </c>
       <c r="E10" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="F10" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G10" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="H10" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="I10" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="F10" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="G10" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="H10" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="I10" s="8" t="s">
-        <v>49</v>
-      </c>
       <c r="J10" s="8">
-        <v>480</v>
+        <v>90</v>
       </c>
       <c r="K10" s="8" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="L10" s="8" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="M10" s="8">
         <v>0</v>
@@ -1283,10 +1280,10 @@
     </row>
     <row r="11" s="2" customFormat="1">
       <c r="A11" s="7" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="C11" s="7" t="s">
         <v>19</v>
@@ -1295,7 +1292,7 @@
         <v>20</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="F11" s="7" t="s">
         <v>22</v>
@@ -1304,19 +1301,19 @@
         <v>23</v>
       </c>
       <c r="H11" s="8" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="I11" s="8" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="J11" s="8">
         <v>90</v>
       </c>
       <c r="K11" s="8" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="L11" s="8" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="M11" s="8">
         <v>0</v>
@@ -1331,10 +1328,10 @@
     </row>
     <row r="12" s="2" customFormat="1">
       <c r="A12" s="7" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="C12" s="7" t="s">
         <v>19</v>
@@ -1343,7 +1340,7 @@
         <v>20</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>44</v>
+        <v>21</v>
       </c>
       <c r="F12" s="7" t="s">
         <v>22</v>
@@ -1352,19 +1349,19 @@
         <v>23</v>
       </c>
       <c r="H12" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="I12" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="I12" s="8" t="s">
-        <v>54</v>
-      </c>
       <c r="J12" s="8">
-        <v>90</v>
+        <v>480</v>
       </c>
       <c r="K12" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="L12" s="8" t="s">
         <v>53</v>
-      </c>
-      <c r="L12" s="8" t="s">
-        <v>54</v>
       </c>
       <c r="M12" s="8">
         <v>0</v>
@@ -1379,10 +1376,10 @@
     </row>
     <row r="13" s="2" customFormat="1">
       <c r="A13" s="7" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="C13" s="7" t="s">
         <v>19</v>
@@ -1391,7 +1388,7 @@
         <v>20</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="F13" s="7" t="s">
         <v>22</v>
@@ -1400,19 +1397,19 @@
         <v>23</v>
       </c>
       <c r="H13" s="8" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="I13" s="8" t="s">
-        <v>59</v>
+        <v>24</v>
       </c>
       <c r="J13" s="8">
         <v>480</v>
       </c>
       <c r="K13" s="8" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="L13" s="8" t="s">
-        <v>59</v>
+        <v>24</v>
       </c>
       <c r="M13" s="8">
         <v>0</v>
@@ -1427,10 +1424,10 @@
     </row>
     <row r="14" s="2" customFormat="1">
       <c r="A14" s="7" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="C14" s="7" t="s">
         <v>19</v>
@@ -1439,7 +1436,7 @@
         <v>20</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>60</v>
+        <v>38</v>
       </c>
       <c r="F14" s="7" t="s">
         <v>22</v>
@@ -1448,19 +1445,19 @@
         <v>23</v>
       </c>
       <c r="H14" s="8" t="s">
-        <v>61</v>
+        <v>24</v>
       </c>
       <c r="I14" s="8" t="s">
-        <v>62</v>
+        <v>25</v>
       </c>
       <c r="J14" s="8">
-        <v>90</v>
+        <v>480</v>
       </c>
       <c r="K14" s="8" t="s">
-        <v>61</v>
+        <v>24</v>
       </c>
       <c r="L14" s="8" t="s">
-        <v>62</v>
+        <v>25</v>
       </c>
       <c r="M14" s="8">
         <v>0</v>
@@ -1475,10 +1472,10 @@
     </row>
     <row r="15" s="2" customFormat="1">
       <c r="A15" s="7" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="C15" s="7" t="s">
         <v>19</v>
@@ -1487,7 +1484,7 @@
         <v>20</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>57</v>
+        <v>21</v>
       </c>
       <c r="F15" s="7" t="s">
         <v>22</v>
@@ -1496,19 +1493,19 @@
         <v>23</v>
       </c>
       <c r="H15" s="8" t="s">
-        <v>65</v>
+        <v>35</v>
       </c>
       <c r="I15" s="8" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="J15" s="8">
         <v>480</v>
       </c>
       <c r="K15" s="8" t="s">
-        <v>65</v>
+        <v>35</v>
       </c>
       <c r="L15" s="8" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="M15" s="8">
         <v>0</v>
@@ -1523,10 +1520,10 @@
     </row>
     <row r="16" s="2" customFormat="1">
       <c r="A16" s="7" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="C16" s="7" t="s">
         <v>19</v>
@@ -1535,7 +1532,7 @@
         <v>20</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="F16" s="7" t="s">
         <v>22</v>
@@ -1544,19 +1541,19 @@
         <v>23</v>
       </c>
       <c r="H16" s="8" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="I16" s="8" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="J16" s="8">
         <v>90</v>
       </c>
       <c r="K16" s="8" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="L16" s="8" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="M16" s="8">
         <v>0</v>
@@ -1571,40 +1568,40 @@
     </row>
     <row r="17" s="2" customFormat="1">
       <c r="A17" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E17" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="F17" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G17" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="H17" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="I17" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="B17" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="C17" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="D17" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="E17" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="F17" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="G17" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="H17" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="I17" s="8" t="s">
-        <v>71</v>
-      </c>
       <c r="J17" s="8">
-        <v>480</v>
+        <v>90</v>
       </c>
       <c r="K17" s="8" t="s">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="L17" s="8" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="M17" s="8">
         <v>0</v>
@@ -1619,20 +1616,20 @@
     </row>
     <row r="18" s="2" customFormat="1">
       <c r="A18" s="7" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="B18" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D18" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E18" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="C18" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="D18" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="E18" s="7" t="s">
-        <v>72</v>
-      </c>
       <c r="F18" s="7" t="s">
         <v>22</v>
       </c>
@@ -1640,19 +1637,19 @@
         <v>23</v>
       </c>
       <c r="H18" s="8" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="I18" s="8" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="J18" s="8">
-        <v>480</v>
+        <v>90</v>
       </c>
       <c r="K18" s="8" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="L18" s="8" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="M18" s="8">
         <v>0</v>
@@ -1667,10 +1664,10 @@
     </row>
     <row r="19" s="2" customFormat="1">
       <c r="A19" s="7" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="C19" s="7" t="s">
         <v>19</v>
@@ -1679,7 +1676,7 @@
         <v>20</v>
       </c>
       <c r="E19" s="7" t="s">
-        <v>44</v>
+        <v>21</v>
       </c>
       <c r="F19" s="7" t="s">
         <v>22</v>
@@ -1688,19 +1685,19 @@
         <v>23</v>
       </c>
       <c r="H19" s="8" t="s">
-        <v>75</v>
+        <v>32</v>
       </c>
       <c r="I19" s="8" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="J19" s="8">
-        <v>90</v>
+        <v>480</v>
       </c>
       <c r="K19" s="8" t="s">
-        <v>75</v>
+        <v>32</v>
       </c>
       <c r="L19" s="8" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="M19" s="8">
         <v>0</v>
@@ -1715,10 +1712,10 @@
     </row>
     <row r="20" s="2" customFormat="1">
       <c r="A20" s="7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C20" s="7" t="s">
         <v>19</v>
@@ -1727,7 +1724,7 @@
         <v>20</v>
       </c>
       <c r="E20" s="7" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F20" s="7" t="s">
         <v>22</v>
@@ -1736,19 +1733,19 @@
         <v>23</v>
       </c>
       <c r="H20" s="8" t="s">
-        <v>77</v>
+        <v>49</v>
       </c>
       <c r="I20" s="8" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="J20" s="8">
         <v>90</v>
       </c>
       <c r="K20" s="8" t="s">
-        <v>77</v>
+        <v>49</v>
       </c>
       <c r="L20" s="8" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="M20" s="8">
         <v>0</v>
@@ -1763,10 +1760,10 @@
     </row>
     <row r="21" s="2" customFormat="1">
       <c r="A21" s="7" t="s">
-        <v>42</v>
+        <v>69</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>43</v>
+        <v>70</v>
       </c>
       <c r="C21" s="7" t="s">
         <v>19</v>
@@ -1775,7 +1772,7 @@
         <v>20</v>
       </c>
       <c r="E21" s="7" t="s">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="F21" s="7" t="s">
         <v>22</v>
@@ -1784,19 +1781,19 @@
         <v>23</v>
       </c>
       <c r="H21" s="8" t="s">
-        <v>79</v>
+        <v>53</v>
       </c>
       <c r="I21" s="8" t="s">
-        <v>65</v>
+        <v>24</v>
       </c>
       <c r="J21" s="8">
         <v>480</v>
       </c>
       <c r="K21" s="8" t="s">
-        <v>79</v>
+        <v>53</v>
       </c>
       <c r="L21" s="8" t="s">
-        <v>65</v>
+        <v>24</v>
       </c>
       <c r="M21" s="8">
         <v>0</v>
@@ -1811,10 +1808,10 @@
     </row>
     <row r="22" s="2" customFormat="1">
       <c r="A22" s="7" t="s">
-        <v>42</v>
+        <v>17</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="C22" s="7" t="s">
         <v>19</v>
@@ -1823,7 +1820,7 @@
         <v>20</v>
       </c>
       <c r="E22" s="7" t="s">
-        <v>44</v>
+        <v>21</v>
       </c>
       <c r="F22" s="7" t="s">
         <v>22</v>
@@ -1832,19 +1829,19 @@
         <v>23</v>
       </c>
       <c r="H22" s="8" t="s">
-        <v>80</v>
+        <v>31</v>
       </c>
       <c r="I22" s="8" t="s">
-        <v>81</v>
+        <v>32</v>
       </c>
       <c r="J22" s="8">
-        <v>90</v>
+        <v>480</v>
       </c>
       <c r="K22" s="8" t="s">
-        <v>80</v>
+        <v>31</v>
       </c>
       <c r="L22" s="8" t="s">
-        <v>81</v>
+        <v>32</v>
       </c>
       <c r="M22" s="8">
         <v>0</v>
@@ -1859,10 +1856,10 @@
     </row>
     <row r="23" s="2" customFormat="1">
       <c r="A23" s="7" t="s">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="C23" s="7" t="s">
         <v>19</v>
@@ -1871,7 +1868,7 @@
         <v>20</v>
       </c>
       <c r="E23" s="7" t="s">
-        <v>44</v>
+        <v>71</v>
       </c>
       <c r="F23" s="7" t="s">
         <v>22</v>
@@ -1880,19 +1877,19 @@
         <v>23</v>
       </c>
       <c r="H23" s="8" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="I23" s="8" t="s">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="J23" s="8">
-        <v>90</v>
+        <v>480</v>
       </c>
       <c r="K23" s="8" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="L23" s="8" t="s">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="M23" s="8">
         <v>0</v>
@@ -1907,10 +1904,10 @@
     </row>
     <row r="24" s="2" customFormat="1">
       <c r="A24" s="7" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="C24" s="7" t="s">
         <v>19</v>
@@ -1919,7 +1916,7 @@
         <v>20</v>
       </c>
       <c r="E24" s="7" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="F24" s="7" t="s">
         <v>22</v>
@@ -1928,19 +1925,19 @@
         <v>23</v>
       </c>
       <c r="H24" s="8" t="s">
-        <v>84</v>
+        <v>34</v>
       </c>
       <c r="I24" s="8" t="s">
-        <v>85</v>
+        <v>35</v>
       </c>
       <c r="J24" s="8">
-        <v>90</v>
+        <v>480</v>
       </c>
       <c r="K24" s="8" t="s">
-        <v>84</v>
+        <v>34</v>
       </c>
       <c r="L24" s="8" t="s">
-        <v>85</v>
+        <v>35</v>
       </c>
       <c r="M24" s="8">
         <v>0</v>
@@ -1955,10 +1952,10 @@
     </row>
     <row r="25" s="2" customFormat="1">
       <c r="A25" s="7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C25" s="7" t="s">
         <v>19</v>
@@ -1967,7 +1964,7 @@
         <v>20</v>
       </c>
       <c r="E25" s="7" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="F25" s="7" t="s">
         <v>22</v>
@@ -1976,19 +1973,19 @@
         <v>23</v>
       </c>
       <c r="H25" s="8" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
       <c r="I25" s="8" t="s">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="J25" s="8">
-        <v>480</v>
+        <v>90</v>
       </c>
       <c r="K25" s="8" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
       <c r="L25" s="8" t="s">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="M25" s="8">
         <v>0</v>
@@ -2003,10 +2000,10 @@
     </row>
     <row r="26" s="2" customFormat="1">
       <c r="A26" s="7" t="s">
-        <v>88</v>
+        <v>36</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>89</v>
+        <v>37</v>
       </c>
       <c r="C26" s="7" t="s">
         <v>19</v>
@@ -2015,28 +2012,28 @@
         <v>20</v>
       </c>
       <c r="E26" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="F26" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G26" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="H26" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="I26" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="J26" s="8">
         <v>90</v>
       </c>
-      <c r="F26" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="G26" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="H26" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="I26" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="J26" s="8">
-        <v>480</v>
-      </c>
       <c r="K26" s="8" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="L26" s="8" t="s">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="M26" s="8">
         <v>0</v>
@@ -2051,10 +2048,10 @@
     </row>
     <row r="27" s="2" customFormat="1">
       <c r="A27" s="7" t="s">
-        <v>88</v>
+        <v>43</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>89</v>
+        <v>44</v>
       </c>
       <c r="C27" s="7" t="s">
         <v>19</v>
@@ -2063,28 +2060,28 @@
         <v>20</v>
       </c>
       <c r="E27" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="F27" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G27" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="H27" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="I27" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="J27" s="8">
         <v>90</v>
       </c>
-      <c r="F27" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="G27" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="H27" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="I27" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="J27" s="8">
-        <v>480</v>
-      </c>
       <c r="K27" s="8" t="s">
-        <v>48</v>
+        <v>79</v>
       </c>
       <c r="L27" s="8" t="s">
-        <v>49</v>
+        <v>80</v>
       </c>
       <c r="M27" s="8">
         <v>0</v>
@@ -2099,10 +2096,10 @@
     </row>
     <row r="28" s="2" customFormat="1">
       <c r="A28" s="7" t="s">
-        <v>88</v>
+        <v>56</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>89</v>
+        <v>57</v>
       </c>
       <c r="C28" s="7" t="s">
         <v>19</v>
@@ -2111,7 +2108,7 @@
         <v>20</v>
       </c>
       <c r="E28" s="7" t="s">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="F28" s="7" t="s">
         <v>22</v>
@@ -2120,19 +2117,19 @@
         <v>23</v>
       </c>
       <c r="H28" s="8" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="I28" s="8" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="J28" s="8">
         <v>480</v>
       </c>
       <c r="K28" s="8" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="L28" s="8" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="M28" s="8">
         <v>0</v>
@@ -2147,10 +2144,10 @@
     </row>
     <row r="29" s="2" customFormat="1">
       <c r="A29" s="7" t="s">
-        <v>91</v>
+        <v>69</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>92</v>
+        <v>70</v>
       </c>
       <c r="C29" s="7" t="s">
         <v>19</v>
@@ -2159,7 +2156,7 @@
         <v>20</v>
       </c>
       <c r="E29" s="7" t="s">
-        <v>93</v>
+        <v>30</v>
       </c>
       <c r="F29" s="7" t="s">
         <v>22</v>
@@ -2168,19 +2165,19 @@
         <v>23</v>
       </c>
       <c r="H29" s="8" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="I29" s="8" t="s">
-        <v>58</v>
+        <v>84</v>
       </c>
       <c r="J29" s="8">
         <v>480</v>
       </c>
       <c r="K29" s="8" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="L29" s="8" t="s">
-        <v>58</v>
+        <v>84</v>
       </c>
       <c r="M29" s="8">
         <v>0</v>
@@ -2195,10 +2192,10 @@
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>91</v>
+        <v>56</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>92</v>
+        <v>57</v>
       </c>
       <c r="C30" s="3" t="s">
         <v>19</v>
@@ -2207,7 +2204,7 @@
         <v>20</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="F30" s="3" t="s">
         <v>22</v>
@@ -2216,19 +2213,19 @@
         <v>23</v>
       </c>
       <c r="H30" s="4" t="s">
-        <v>49</v>
+        <v>86</v>
       </c>
       <c r="I30" s="4" t="s">
-        <v>71</v>
+        <v>87</v>
       </c>
       <c r="J30" s="4">
         <v>480</v>
       </c>
       <c r="K30" s="4" t="s">
-        <v>49</v>
+        <v>86</v>
       </c>
       <c r="L30" s="4" t="s">
-        <v>71</v>
+        <v>87</v>
       </c>
       <c r="M30" s="4">
         <v>0</v>
@@ -2243,10 +2240,10 @@
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
-        <v>91</v>
+        <v>69</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>92</v>
+        <v>70</v>
       </c>
       <c r="C31" s="3" t="s">
         <v>19</v>
@@ -2255,7 +2252,7 @@
         <v>20</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>93</v>
+        <v>30</v>
       </c>
       <c r="F31" s="3" t="s">
         <v>22</v>
@@ -2264,19 +2261,19 @@
         <v>23</v>
       </c>
       <c r="H31" s="4" t="s">
-        <v>73</v>
+        <v>88</v>
       </c>
       <c r="I31" s="4" t="s">
-        <v>74</v>
+        <v>31</v>
       </c>
       <c r="J31" s="4">
         <v>480</v>
       </c>
       <c r="K31" s="4" t="s">
-        <v>73</v>
+        <v>88</v>
       </c>
       <c r="L31" s="4" t="s">
-        <v>74</v>
+        <v>31</v>
       </c>
       <c r="M31" s="4">
         <v>0</v>
@@ -2291,10 +2288,10 @@
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
-        <v>66</v>
+        <v>36</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>67</v>
+        <v>37</v>
       </c>
       <c r="C32" s="3" t="s">
         <v>19</v>
@@ -2303,7 +2300,7 @@
         <v>20</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>68</v>
+        <v>38</v>
       </c>
       <c r="F32" s="3" t="s">
         <v>22</v>
@@ -2312,19 +2309,19 @@
         <v>23</v>
       </c>
       <c r="H32" s="4" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="I32" s="4" t="s">
-        <v>95</v>
+        <v>74</v>
       </c>
       <c r="J32" s="4">
         <v>90</v>
       </c>
       <c r="K32" s="4" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="L32" s="4" t="s">
-        <v>95</v>
+        <v>74</v>
       </c>
       <c r="M32" s="4">
         <v>0</v>
@@ -2339,10 +2336,10 @@
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="C33" s="3" t="s">
         <v>19</v>
@@ -2351,7 +2348,7 @@
         <v>20</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="F33" s="3" t="s">
         <v>22</v>
@@ -2360,19 +2357,19 @@
         <v>23</v>
       </c>
       <c r="H33" s="4" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="I33" s="4" t="s">
-        <v>75</v>
+        <v>91</v>
       </c>
       <c r="J33" s="4">
         <v>90</v>
       </c>
       <c r="K33" s="4" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="L33" s="4" t="s">
-        <v>75</v>
+        <v>91</v>
       </c>
       <c r="M33" s="4">
         <v>0</v>
@@ -2387,10 +2384,10 @@
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
-        <v>66</v>
+        <v>43</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>67</v>
+        <v>44</v>
       </c>
       <c r="C34" s="3" t="s">
         <v>19</v>
@@ -2399,7 +2396,7 @@
         <v>20</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>68</v>
+        <v>45</v>
       </c>
       <c r="F34" s="3" t="s">
         <v>22</v>
@@ -2408,19 +2405,19 @@
         <v>23</v>
       </c>
       <c r="H34" s="4" t="s">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="I34" s="4" t="s">
-        <v>58</v>
+        <v>92</v>
       </c>
       <c r="J34" s="4">
-        <v>480</v>
+        <v>90</v>
       </c>
       <c r="K34" s="4" t="s">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="L34" s="4" t="s">
-        <v>58</v>
+        <v>92</v>
       </c>
       <c r="M34" s="4">
         <v>0</v>
@@ -2435,10 +2432,10 @@
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
-        <v>66</v>
+        <v>43</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>67</v>
+        <v>44</v>
       </c>
       <c r="C35" s="3" t="s">
         <v>19</v>
@@ -2447,7 +2444,7 @@
         <v>20</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>68</v>
+        <v>45</v>
       </c>
       <c r="F35" s="3" t="s">
         <v>22</v>
@@ -2456,19 +2453,19 @@
         <v>23</v>
       </c>
       <c r="H35" s="4" t="s">
-        <v>49</v>
+        <v>93</v>
       </c>
       <c r="I35" s="4" t="s">
-        <v>71</v>
+        <v>94</v>
       </c>
       <c r="J35" s="4">
-        <v>480</v>
+        <v>90</v>
       </c>
       <c r="K35" s="4" t="s">
-        <v>49</v>
+        <v>93</v>
       </c>
       <c r="L35" s="4" t="s">
-        <v>71</v>
+        <v>94</v>
       </c>
       <c r="M35" s="4">
         <v>0</v>
@@ -2483,10 +2480,10 @@
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
-        <v>66</v>
+        <v>36</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>67</v>
+        <v>37</v>
       </c>
       <c r="C36" s="3" t="s">
         <v>19</v>
@@ -2495,7 +2492,7 @@
         <v>20</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>68</v>
+        <v>38</v>
       </c>
       <c r="F36" s="3" t="s">
         <v>22</v>
@@ -2504,19 +2501,19 @@
         <v>23</v>
       </c>
       <c r="H36" s="4" t="s">
-        <v>73</v>
+        <v>95</v>
       </c>
       <c r="I36" s="4" t="s">
-        <v>74</v>
+        <v>96</v>
       </c>
       <c r="J36" s="4">
-        <v>480</v>
+        <v>90</v>
       </c>
       <c r="K36" s="4" t="s">
-        <v>73</v>
+        <v>95</v>
       </c>
       <c r="L36" s="4" t="s">
-        <v>74</v>
+        <v>96</v>
       </c>
       <c r="M36" s="4">
         <v>0</v>
@@ -2531,10 +2528,10 @@
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
-        <v>66</v>
+        <v>36</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>67</v>
+        <v>37</v>
       </c>
       <c r="C37" s="3" t="s">
         <v>19</v>
@@ -2543,7 +2540,7 @@
         <v>20</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>68</v>
+        <v>38</v>
       </c>
       <c r="F37" s="3" t="s">
         <v>22</v>
@@ -2579,10 +2576,10 @@
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
-        <v>66</v>
+        <v>36</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>67</v>
+        <v>37</v>
       </c>
       <c r="C38" s="3" t="s">
         <v>19</v>
@@ -2591,7 +2588,7 @@
         <v>20</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>68</v>
+        <v>38</v>
       </c>
       <c r="F38" s="3" t="s">
         <v>22</v>
@@ -2600,19 +2597,19 @@
         <v>23</v>
       </c>
       <c r="H38" s="4" t="s">
-        <v>99</v>
+        <v>31</v>
       </c>
       <c r="I38" s="4" t="s">
-        <v>84</v>
+        <v>32</v>
       </c>
       <c r="J38" s="4">
-        <v>90</v>
+        <v>480</v>
       </c>
       <c r="K38" s="4" t="s">
-        <v>99</v>
+        <v>31</v>
       </c>
       <c r="L38" s="4" t="s">
-        <v>84</v>
+        <v>32</v>
       </c>
       <c r="M38" s="4">
         <v>0</v>
@@ -2627,10 +2624,10 @@
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
-        <v>66</v>
+        <v>43</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>67</v>
+        <v>44</v>
       </c>
       <c r="C39" s="3" t="s">
         <v>19</v>
@@ -2639,7 +2636,7 @@
         <v>20</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>68</v>
+        <v>45</v>
       </c>
       <c r="F39" s="3" t="s">
         <v>22</v>
@@ -2648,19 +2645,19 @@
         <v>23</v>
       </c>
       <c r="H39" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="I39" s="4" t="s">
         <v>100</v>
-      </c>
-      <c r="I39" s="4" t="s">
-        <v>53</v>
       </c>
       <c r="J39" s="4">
         <v>90</v>
       </c>
       <c r="K39" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="L39" s="4" t="s">
         <v>100</v>
-      </c>
-      <c r="L39" s="4" t="s">
-        <v>53</v>
       </c>
       <c r="M39" s="4">
         <v>0</v>
@@ -2675,10 +2672,10 @@
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
-        <v>66</v>
+        <v>36</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>67</v>
+        <v>37</v>
       </c>
       <c r="C40" s="3" t="s">
         <v>19</v>
@@ -2687,7 +2684,7 @@
         <v>20</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>68</v>
+        <v>38</v>
       </c>
       <c r="F40" s="3" t="s">
         <v>22</v>
@@ -2699,7 +2696,7 @@
         <v>101</v>
       </c>
       <c r="I40" s="4" t="s">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="J40" s="4">
         <v>90</v>
@@ -2708,7 +2705,7 @@
         <v>101</v>
       </c>
       <c r="L40" s="4" t="s">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="M40" s="4">
         <v>0</v>
@@ -2723,10 +2720,10 @@
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
-        <v>66</v>
+        <v>43</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>67</v>
+        <v>44</v>
       </c>
       <c r="C41" s="3" t="s">
         <v>19</v>
@@ -2735,7 +2732,7 @@
         <v>20</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>68</v>
+        <v>54</v>
       </c>
       <c r="F41" s="3" t="s">
         <v>22</v>
@@ -2744,19 +2741,19 @@
         <v>23</v>
       </c>
       <c r="H41" s="4" t="s">
-        <v>102</v>
+        <v>88</v>
       </c>
       <c r="I41" s="4" t="s">
-        <v>82</v>
+        <v>31</v>
       </c>
       <c r="J41" s="4">
-        <v>90</v>
+        <v>480</v>
       </c>
       <c r="K41" s="4" t="s">
-        <v>102</v>
+        <v>88</v>
       </c>
       <c r="L41" s="4" t="s">
-        <v>82</v>
+        <v>31</v>
       </c>
       <c r="M41" s="4">
         <v>0</v>
@@ -2771,10 +2768,10 @@
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
-        <v>66</v>
+        <v>36</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>67</v>
+        <v>37</v>
       </c>
       <c r="C42" s="3" t="s">
         <v>19</v>
@@ -2783,7 +2780,7 @@
         <v>20</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>68</v>
+        <v>38</v>
       </c>
       <c r="F42" s="3" t="s">
         <v>22</v>
@@ -2792,19 +2789,19 @@
         <v>23</v>
       </c>
       <c r="H42" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="I42" s="4" t="s">
         <v>103</v>
-      </c>
-      <c r="I42" s="4" t="s">
-        <v>104</v>
       </c>
       <c r="J42" s="4">
         <v>90</v>
       </c>
       <c r="K42" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="L42" s="4" t="s">
         <v>103</v>
-      </c>
-      <c r="L42" s="4" t="s">
-        <v>104</v>
       </c>
       <c r="M42" s="4">
         <v>0</v>
@@ -2819,10 +2816,10 @@
     </row>
     <row r="43">
       <c r="A43" s="3" t="s">
-        <v>66</v>
+        <v>43</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>67</v>
+        <v>44</v>
       </c>
       <c r="C43" s="3" t="s">
         <v>19</v>
@@ -2831,7 +2828,7 @@
         <v>20</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>68</v>
+        <v>54</v>
       </c>
       <c r="F43" s="3" t="s">
         <v>22</v>
@@ -2840,19 +2837,19 @@
         <v>23</v>
       </c>
       <c r="H43" s="4" t="s">
-        <v>105</v>
+        <v>55</v>
       </c>
       <c r="I43" s="4" t="s">
-        <v>106</v>
+        <v>84</v>
       </c>
       <c r="J43" s="4">
-        <v>90</v>
+        <v>480</v>
       </c>
       <c r="K43" s="4" t="s">
-        <v>105</v>
+        <v>55</v>
       </c>
       <c r="L43" s="4" t="s">
-        <v>106</v>
+        <v>84</v>
       </c>
       <c r="M43" s="4">
         <v>0</v>
@@ -2867,10 +2864,10 @@
     </row>
     <row r="44">
       <c r="A44" s="3" t="s">
-        <v>107</v>
+        <v>36</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>108</v>
+        <v>37</v>
       </c>
       <c r="C44" s="3" t="s">
         <v>19</v>
@@ -2879,7 +2876,7 @@
         <v>20</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>109</v>
+        <v>38</v>
       </c>
       <c r="F44" s="3" t="s">
         <v>22</v>
@@ -2888,19 +2885,19 @@
         <v>23</v>
       </c>
       <c r="H44" s="4" t="s">
-        <v>62</v>
+        <v>104</v>
       </c>
       <c r="I44" s="4" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="J44" s="4">
         <v>90</v>
       </c>
       <c r="K44" s="4" t="s">
-        <v>62</v>
+        <v>104</v>
       </c>
       <c r="L44" s="4" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="M44" s="4">
         <v>0</v>
@@ -2915,10 +2912,10 @@
     </row>
     <row r="45">
       <c r="A45" s="3" t="s">
-        <v>107</v>
+        <v>43</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>108</v>
+        <v>44</v>
       </c>
       <c r="C45" s="3" t="s">
         <v>19</v>
@@ -2927,7 +2924,7 @@
         <v>20</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>109</v>
+        <v>45</v>
       </c>
       <c r="F45" s="3" t="s">
         <v>22</v>
@@ -2936,19 +2933,19 @@
         <v>23</v>
       </c>
       <c r="H45" s="4" t="s">
-        <v>58</v>
+        <v>98</v>
       </c>
       <c r="I45" s="4" t="s">
-        <v>59</v>
+        <v>106</v>
       </c>
       <c r="J45" s="4">
-        <v>480</v>
+        <v>90</v>
       </c>
       <c r="K45" s="4" t="s">
-        <v>58</v>
+        <v>98</v>
       </c>
       <c r="L45" s="4" t="s">
-        <v>59</v>
+        <v>106</v>
       </c>
       <c r="M45" s="4">
         <v>0</v>
@@ -2984,19 +2981,19 @@
         <v>23</v>
       </c>
       <c r="H46" s="4" t="s">
-        <v>111</v>
+        <v>80</v>
       </c>
       <c r="I46" s="4" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="J46" s="4">
         <v>90</v>
       </c>
       <c r="K46" s="4" t="s">
-        <v>111</v>
+        <v>80</v>
       </c>
       <c r="L46" s="4" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="M46" s="4">
         <v>0</v>
@@ -3032,19 +3029,19 @@
         <v>23</v>
       </c>
       <c r="H47" s="4" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="I47" s="4" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="J47" s="4">
         <v>90</v>
       </c>
       <c r="K47" s="4" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="L47" s="4" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="M47" s="4">
         <v>0</v>
@@ -3080,19 +3077,19 @@
         <v>23</v>
       </c>
       <c r="H48" s="4" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="I48" s="4" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="J48" s="4">
         <v>90</v>
       </c>
       <c r="K48" s="4" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="L48" s="4" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="M48" s="4">
         <v>0</v>
@@ -3128,19 +3125,19 @@
         <v>23</v>
       </c>
       <c r="H49" s="4" t="s">
-        <v>81</v>
+        <v>32</v>
       </c>
       <c r="I49" s="4" t="s">
-        <v>117</v>
+        <v>67</v>
       </c>
       <c r="J49" s="4">
-        <v>90</v>
+        <v>480</v>
       </c>
       <c r="K49" s="4" t="s">
-        <v>81</v>
+        <v>32</v>
       </c>
       <c r="L49" s="4" t="s">
-        <v>117</v>
+        <v>67</v>
       </c>
       <c r="M49" s="4">
         <v>0</v>
@@ -3155,10 +3152,10 @@
     </row>
     <row r="50">
       <c r="A50" s="3" t="s">
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="C50" s="3" t="s">
         <v>19</v>
@@ -3167,7 +3164,7 @@
         <v>20</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="F50" s="3" t="s">
         <v>22</v>
@@ -3176,19 +3173,19 @@
         <v>23</v>
       </c>
       <c r="H50" s="4" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="I50" s="4" t="s">
-        <v>118</v>
+        <v>24</v>
       </c>
       <c r="J50" s="4">
-        <v>90</v>
+        <v>480</v>
       </c>
       <c r="K50" s="4" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="L50" s="4" t="s">
-        <v>118</v>
+        <v>24</v>
       </c>
       <c r="M50" s="4">
         <v>0</v>
@@ -3224,19 +3221,19 @@
         <v>23</v>
       </c>
       <c r="H51" s="4" t="s">
-        <v>52</v>
+        <v>94</v>
       </c>
       <c r="I51" s="4" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="J51" s="4">
         <v>90</v>
       </c>
       <c r="K51" s="4" t="s">
-        <v>52</v>
+        <v>94</v>
       </c>
       <c r="L51" s="4" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="M51" s="4">
         <v>0</v>
@@ -3251,10 +3248,10 @@
     </row>
     <row r="52">
       <c r="A52" s="3" t="s">
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="C52" s="3" t="s">
         <v>19</v>
@@ -3263,7 +3260,7 @@
         <v>20</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="F52" s="3" t="s">
         <v>22</v>
@@ -3272,19 +3269,19 @@
         <v>23</v>
       </c>
       <c r="H52" s="4" t="s">
-        <v>120</v>
+        <v>55</v>
       </c>
       <c r="I52" s="4" t="s">
-        <v>121</v>
+        <v>84</v>
       </c>
       <c r="J52" s="4">
-        <v>90</v>
+        <v>480</v>
       </c>
       <c r="K52" s="4" t="s">
-        <v>120</v>
+        <v>55</v>
       </c>
       <c r="L52" s="4" t="s">
-        <v>121</v>
+        <v>84</v>
       </c>
       <c r="M52" s="4">
         <v>0</v>
@@ -3320,19 +3317,19 @@
         <v>23</v>
       </c>
       <c r="H53" s="4" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="I53" s="4" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="J53" s="4">
         <v>90</v>
       </c>
       <c r="K53" s="4" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="L53" s="4" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="M53" s="4">
         <v>0</v>
@@ -3368,19 +3365,19 @@
         <v>23</v>
       </c>
       <c r="H54" s="4" t="s">
-        <v>74</v>
+        <v>121</v>
       </c>
       <c r="I54" s="4" t="s">
-        <v>86</v>
+        <v>122</v>
       </c>
       <c r="J54" s="4">
-        <v>480</v>
+        <v>90</v>
       </c>
       <c r="K54" s="4" t="s">
-        <v>74</v>
+        <v>121</v>
       </c>
       <c r="L54" s="4" t="s">
-        <v>86</v>
+        <v>122</v>
       </c>
       <c r="M54" s="4">
         <v>0</v>
@@ -3395,10 +3392,10 @@
     </row>
     <row r="55">
       <c r="A55" s="3" t="s">
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="C55" s="3" t="s">
         <v>19</v>
@@ -3407,7 +3404,7 @@
         <v>20</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="F55" s="3" t="s">
         <v>22</v>
@@ -3416,19 +3413,19 @@
         <v>23</v>
       </c>
       <c r="H55" s="4" t="s">
-        <v>124</v>
+        <v>88</v>
       </c>
       <c r="I55" s="4" t="s">
-        <v>125</v>
+        <v>31</v>
       </c>
       <c r="J55" s="4">
-        <v>90</v>
+        <v>480</v>
       </c>
       <c r="K55" s="4" t="s">
-        <v>124</v>
+        <v>88</v>
       </c>
       <c r="L55" s="4" t="s">
-        <v>125</v>
+        <v>31</v>
       </c>
       <c r="M55" s="4">
         <v>0</v>
@@ -3464,19 +3461,19 @@
         <v>23</v>
       </c>
       <c r="H56" s="4" t="s">
-        <v>126</v>
+        <v>63</v>
       </c>
       <c r="I56" s="4" t="s">
-        <v>48</v>
+        <v>123</v>
       </c>
       <c r="J56" s="4">
-        <v>480</v>
+        <v>90</v>
       </c>
       <c r="K56" s="4" t="s">
-        <v>126</v>
+        <v>63</v>
       </c>
       <c r="L56" s="4" t="s">
-        <v>48</v>
+        <v>123</v>
       </c>
       <c r="M56" s="4">
         <v>0</v>
@@ -3491,10 +3488,10 @@
     </row>
     <row r="57">
       <c r="A57" s="3" t="s">
-        <v>127</v>
+        <v>107</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>128</v>
+        <v>108</v>
       </c>
       <c r="C57" s="3" t="s">
         <v>19</v>
@@ -3503,7 +3500,7 @@
         <v>20</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>93</v>
+        <v>109</v>
       </c>
       <c r="F57" s="3" t="s">
         <v>22</v>
@@ -3512,19 +3509,19 @@
         <v>23</v>
       </c>
       <c r="H57" s="4" t="s">
-        <v>126</v>
+        <v>52</v>
       </c>
       <c r="I57" s="4" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="J57" s="4">
         <v>480</v>
       </c>
       <c r="K57" s="4" t="s">
-        <v>126</v>
+        <v>52</v>
       </c>
       <c r="L57" s="4" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="M57" s="4">
         <v>0</v>
@@ -3539,10 +3536,10 @@
     </row>
     <row r="58">
       <c r="A58" s="3" t="s">
-        <v>127</v>
+        <v>107</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>128</v>
+        <v>108</v>
       </c>
       <c r="C58" s="3" t="s">
         <v>19</v>
@@ -3551,7 +3548,7 @@
         <v>20</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>93</v>
+        <v>109</v>
       </c>
       <c r="F58" s="3" t="s">
         <v>22</v>
@@ -3560,19 +3557,19 @@
         <v>23</v>
       </c>
       <c r="H58" s="4" t="s">
-        <v>58</v>
+        <v>35</v>
       </c>
       <c r="I58" s="4" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="J58" s="4">
         <v>480</v>
       </c>
       <c r="K58" s="4" t="s">
-        <v>58</v>
+        <v>35</v>
       </c>
       <c r="L58" s="4" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="M58" s="4">
         <v>0</v>
@@ -3582,15 +3579,15 @@
         <v>26</v>
       </c>
       <c r="P58" s="4" t="s">
-        <v>129</v>
+        <v>27</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="s">
-        <v>127</v>
+        <v>107</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>128</v>
+        <v>108</v>
       </c>
       <c r="C59" s="3" t="s">
         <v>19</v>
@@ -3599,7 +3596,7 @@
         <v>20</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>93</v>
+        <v>109</v>
       </c>
       <c r="F59" s="3" t="s">
         <v>22</v>
@@ -3608,19 +3605,19 @@
         <v>23</v>
       </c>
       <c r="H59" s="4" t="s">
-        <v>74</v>
+        <v>124</v>
       </c>
       <c r="I59" s="4" t="s">
-        <v>86</v>
+        <v>125</v>
       </c>
       <c r="J59" s="4">
-        <v>480</v>
+        <v>90</v>
       </c>
       <c r="K59" s="4" t="s">
-        <v>74</v>
+        <v>124</v>
       </c>
       <c r="L59" s="4" t="s">
-        <v>86</v>
+        <v>125</v>
       </c>
       <c r="M59" s="4">
         <v>0</v>
@@ -3635,10 +3632,10 @@
     </row>
     <row r="60">
       <c r="A60" s="3" t="s">
-        <v>55</v>
+        <v>107</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>56</v>
+        <v>108</v>
       </c>
       <c r="C60" s="3" t="s">
         <v>19</v>
@@ -3647,7 +3644,7 @@
         <v>20</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>57</v>
+        <v>109</v>
       </c>
       <c r="F60" s="3" t="s">
         <v>22</v>
@@ -3659,16 +3656,16 @@
         <v>126</v>
       </c>
       <c r="I60" s="4" t="s">
-        <v>48</v>
+        <v>127</v>
       </c>
       <c r="J60" s="4">
-        <v>480</v>
+        <v>90</v>
       </c>
       <c r="K60" s="4" t="s">
         <v>126</v>
       </c>
       <c r="L60" s="4" t="s">
-        <v>48</v>
+        <v>127</v>
       </c>
       <c r="M60" s="4">
         <v>0</v>
@@ -3683,10 +3680,10 @@
     </row>
     <row r="61">
       <c r="A61" s="3" t="s">
-        <v>55</v>
+        <v>107</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>56</v>
+        <v>108</v>
       </c>
       <c r="C61" s="3" t="s">
         <v>19</v>
@@ -3695,7 +3692,7 @@
         <v>20</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>57</v>
+        <v>109</v>
       </c>
       <c r="F61" s="3" t="s">
         <v>22</v>
@@ -3704,19 +3701,19 @@
         <v>23</v>
       </c>
       <c r="H61" s="4" t="s">
-        <v>74</v>
+        <v>47</v>
       </c>
       <c r="I61" s="4" t="s">
-        <v>86</v>
+        <v>128</v>
       </c>
       <c r="J61" s="4">
-        <v>480</v>
+        <v>90</v>
       </c>
       <c r="K61" s="4" t="s">
-        <v>74</v>
+        <v>47</v>
       </c>
       <c r="L61" s="4" t="s">
-        <v>86</v>
+        <v>128</v>
       </c>
       <c r="M61" s="4">
         <v>0</v>
@@ -3731,11 +3728,11 @@
     </row>
     <row r="62">
       <c r="A62" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="B62" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="B62" s="3" t="s">
-        <v>131</v>
-      </c>
       <c r="C62" s="3" t="s">
         <v>19</v>
       </c>
@@ -3743,7 +3740,7 @@
         <v>20</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>93</v>
+        <v>30</v>
       </c>
       <c r="F62" s="3" t="s">
         <v>22</v>
@@ -3752,19 +3749,19 @@
         <v>23</v>
       </c>
       <c r="H62" s="4" t="s">
-        <v>79</v>
+        <v>52</v>
       </c>
       <c r="I62" s="4" t="s">
-        <v>65</v>
+        <v>53</v>
       </c>
       <c r="J62" s="4">
         <v>480</v>
       </c>
       <c r="K62" s="4" t="s">
-        <v>79</v>
+        <v>52</v>
       </c>
       <c r="L62" s="4" t="s">
-        <v>65</v>
+        <v>53</v>
       </c>
       <c r="M62" s="4">
         <v>0</v>
@@ -3779,11 +3776,11 @@
     </row>
     <row r="63">
       <c r="A63" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="B63" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="B63" s="3" t="s">
-        <v>131</v>
-      </c>
       <c r="C63" s="3" t="s">
         <v>19</v>
       </c>
@@ -3791,7 +3788,7 @@
         <v>20</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>93</v>
+        <v>30</v>
       </c>
       <c r="F63" s="3" t="s">
         <v>22</v>
@@ -3800,19 +3797,19 @@
         <v>23</v>
       </c>
       <c r="H63" s="4" t="s">
-        <v>86</v>
+        <v>35</v>
       </c>
       <c r="I63" s="4" t="s">
-        <v>87</v>
+        <v>55</v>
       </c>
       <c r="J63" s="4">
         <v>480</v>
       </c>
       <c r="K63" s="4" t="s">
-        <v>86</v>
+        <v>35</v>
       </c>
       <c r="L63" s="4" t="s">
-        <v>87</v>
+        <v>55</v>
       </c>
       <c r="M63" s="4">
         <v>0</v>
@@ -3827,11 +3824,11 @@
     </row>
     <row r="64">
       <c r="A64" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="B64" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="B64" s="3" t="s">
-        <v>131</v>
-      </c>
       <c r="C64" s="3" t="s">
         <v>19</v>
       </c>
@@ -3839,7 +3836,7 @@
         <v>20</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>93</v>
+        <v>30</v>
       </c>
       <c r="F64" s="3" t="s">
         <v>22</v>
@@ -3848,19 +3845,19 @@
         <v>23</v>
       </c>
       <c r="H64" s="4" t="s">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="I64" s="4" t="s">
-        <v>49</v>
+        <v>67</v>
       </c>
       <c r="J64" s="4">
         <v>480</v>
       </c>
       <c r="K64" s="4" t="s">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="L64" s="4" t="s">
-        <v>49</v>
+        <v>67</v>
       </c>
       <c r="M64" s="4">
         <v>0</v>

--- a/data/hrm_sync_actual_2.xlsx
+++ b/data/hrm_sync_actual_2.xlsx
@@ -12,7 +12,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0">Sheet!$A$2:$I$6333</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">Sheet!$2:$2</definedName>
   </definedNames>
-  <calcPr calcId="181029"/>
+  <calcPr/>
 </workbook>
 </file>
 
@@ -68,6 +68,360 @@
   </si>
   <si>
     <t>Trạng thái duyệt</t>
+  </si>
+  <si>
+    <t>02020947</t>
+  </si>
+  <si>
+    <t>Nguyễn Hoàng Duy</t>
+  </si>
+  <si>
+    <t>Plastic Extrusion</t>
+  </si>
+  <si>
+    <t>Pulverize</t>
+  </si>
+  <si>
+    <t xml:space="preserve">chuẩn bị kiểm kê </t>
+  </si>
+  <si>
+    <t>Nguyễn Chí Cường</t>
+  </si>
+  <si>
+    <t>Thân Trọng Tuấn</t>
+  </si>
+  <si>
+    <t>24/09/2026 16:30:00</t>
+  </si>
+  <si>
+    <t>24/09/2026 18:00:00</t>
+  </si>
+  <si>
+    <t>Bằng KH</t>
+  </si>
+  <si>
+    <t>Đã duyệt</t>
+  </si>
+  <si>
+    <t>02222350</t>
+  </si>
+  <si>
+    <t>Hoàng Văn Nguyên</t>
+  </si>
+  <si>
+    <t>Tăng cường sản xuất</t>
+  </si>
+  <si>
+    <t>26/09/2026 22:00:00</t>
+  </si>
+  <si>
+    <t>27/09/2026 06:00:00</t>
+  </si>
+  <si>
+    <t>chuẩn bị kiểm kê</t>
+  </si>
+  <si>
+    <t>23/09/2026 16:30:00</t>
+  </si>
+  <si>
+    <t>23/09/2026 18:00:00</t>
+  </si>
+  <si>
+    <t>19/09/2026 06:00:00</t>
+  </si>
+  <si>
+    <t>19/09/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>22/09/2026 16:30:00</t>
+  </si>
+  <si>
+    <t>22/09/2026 18:00:00</t>
+  </si>
+  <si>
+    <t>12/09/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>12/09/2026 22:00:00</t>
+  </si>
+  <si>
+    <t>lắp đặt thiết bị</t>
+  </si>
+  <si>
+    <t>12/09/2026 07:45:00</t>
+  </si>
+  <si>
+    <t>12/09/2026 16:30:00</t>
+  </si>
+  <si>
+    <t>02223605</t>
+  </si>
+  <si>
+    <t>Võ Minh Bắc</t>
+  </si>
+  <si>
+    <t>tăng cường sản xuất</t>
+  </si>
+  <si>
+    <t>26/09/2026 06:00:00</t>
+  </si>
+  <si>
+    <t>26/09/2026 14:00:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">vận chuyển nguyên vật liệu </t>
+  </si>
+  <si>
+    <t>26/09/2026 07:45:00</t>
+  </si>
+  <si>
+    <t>26/09/2026 16:30:00</t>
+  </si>
+  <si>
+    <t>13/09/2026 06:00:00</t>
+  </si>
+  <si>
+    <t>29/09/2026 16:30:00</t>
+  </si>
+  <si>
+    <t>29/09/2026 19:00:00</t>
+  </si>
+  <si>
+    <t>29/09/2026 18:00:00</t>
+  </si>
+  <si>
+    <t>Lớn hơn KH</t>
+  </si>
+  <si>
+    <t>02121404</t>
+  </si>
+  <si>
+    <t>Lê Hoàng Minh Tâm</t>
+  </si>
+  <si>
+    <t>02243654</t>
+  </si>
+  <si>
+    <t>Lưu Văn Giang</t>
+  </si>
+  <si>
+    <t>Tăng Cường Sản Xuất</t>
+  </si>
+  <si>
+    <t>02223526</t>
+  </si>
+  <si>
+    <t>Nguyễn Thiên Phú</t>
+  </si>
+  <si>
+    <t>19/09/2026 22:00:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">vận chuyển nguyên vật liệu nghiền </t>
+  </si>
+  <si>
+    <t>19/09/2026 07:45:00</t>
+  </si>
+  <si>
+    <t>19/09/2026 16:30:00</t>
+  </si>
+  <si>
+    <t>20/09/2026 06:00:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tăng cường sản xuất </t>
+  </si>
+  <si>
+    <t>12/09/2026 06:00:00</t>
+  </si>
+  <si>
+    <t>02644057</t>
+  </si>
+  <si>
+    <t>Phạm Văn Công</t>
+  </si>
+  <si>
+    <t>tăng ca đáp ứng tiến độ sản xuất</t>
+  </si>
+  <si>
+    <t>14/09/2026 20:30:00</t>
+  </si>
+  <si>
+    <t>14/09/2026 22:00:00</t>
+  </si>
+  <si>
+    <t>17/09/2026 20:30:00</t>
+  </si>
+  <si>
+    <t>17/09/2026 22:00:00</t>
+  </si>
+  <si>
+    <t>02644066</t>
+  </si>
+  <si>
+    <t>Nguyễn Hữu Tình</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tang ca cat ong nhua </t>
+  </si>
+  <si>
+    <t>15/09/2026 12:30:00</t>
+  </si>
+  <si>
+    <t>15/09/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>tang ca cat ong nhua</t>
+  </si>
+  <si>
+    <t>18/09/2026 12:30:00</t>
+  </si>
+  <si>
+    <t>18/09/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>25/09/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>25/09/2026 15:30:00</t>
+  </si>
+  <si>
+    <t>21/09/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>21/09/2026 15:30:00</t>
+  </si>
+  <si>
+    <t>21/09/2026 12:30:00</t>
+  </si>
+  <si>
+    <t>24/09/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>24/09/2026 15:30:00</t>
+  </si>
+  <si>
+    <t>24/09/2026 12:30:00</t>
+  </si>
+  <si>
+    <t>tăng ca cǎt ông nhua</t>
+  </si>
+  <si>
+    <t>14/09/2026 12:30:00</t>
+  </si>
+  <si>
+    <t>14/09/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>17/09/2026 12:30:00</t>
+  </si>
+  <si>
+    <t>17/09/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>23/09/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>23/09/2026 15:30:00</t>
+  </si>
+  <si>
+    <t>18/09/2026 20:30:00</t>
+  </si>
+  <si>
+    <t>18/09/2026 22:00:00</t>
+  </si>
+  <si>
+    <t>25/09/2026 12:30:00</t>
+  </si>
+  <si>
+    <t>tang ca van hanh may nghien</t>
+  </si>
+  <si>
+    <t>15/09/2026 20:30:00</t>
+  </si>
+  <si>
+    <t>15/09/2026 22:00:00</t>
+  </si>
+  <si>
+    <t>22/09/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>22/09/2026 15:30:00</t>
+  </si>
+  <si>
+    <t>02622116</t>
+  </si>
+  <si>
+    <t>Trịnh Nhựt Khánh</t>
+  </si>
+  <si>
+    <t>23/09/2026 12:30:00</t>
+  </si>
+  <si>
+    <t>16/09/2026 20:30:00</t>
+  </si>
+  <si>
+    <t>16/09/2026 22:00:00</t>
+  </si>
+  <si>
+    <t>22/09/2026 12:30:00</t>
+  </si>
+  <si>
+    <t>02644075</t>
+  </si>
+  <si>
+    <t>Huỳnh Đại Nhân</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tăng cường sản xuất </t>
+  </si>
+  <si>
+    <t>14/09/2026 15:30:00</t>
+  </si>
+  <si>
+    <t>15/09/2026 15:30:00</t>
+  </si>
+  <si>
+    <t>24/09/2026 20:30:00</t>
+  </si>
+  <si>
+    <t>24/09/2026 22:00:00</t>
+  </si>
+  <si>
+    <t>25/09/2026 20:30:00</t>
+  </si>
+  <si>
+    <t>25/09/2026 22:30:00</t>
+  </si>
+  <si>
+    <t>23/09/2026 20:30:00</t>
+  </si>
+  <si>
+    <t>23/09/2026 22:00:00</t>
+  </si>
+  <si>
+    <t>18/09/2026 15:30:00</t>
+  </si>
+  <si>
+    <t>17/09/2026 15:30:00</t>
+  </si>
+  <si>
+    <t>22/09/2026 20:30:00</t>
+  </si>
+  <si>
+    <t>22/09/2026 22:00:00</t>
+  </si>
+  <si>
+    <t>16/09/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>16/09/2026 15:30:00</t>
+  </si>
+  <si>
+    <t>21/09/2026 20:30:00</t>
+  </si>
+  <si>
+    <t>21/09/2026 22:00:00</t>
   </si>
 </sst>
 </file>
@@ -553,490 +907,3028 @@
       </c>
     </row>
     <row r="3" s="2" customFormat="1">
-      <c r="A3" s="7"/>
-      <c r="B3" s="7"/>
-      <c r="C3" s="7"/>
-      <c r="D3" s="7"/>
-      <c r="E3" s="7"/>
-      <c r="F3" s="7"/>
-      <c r="G3" s="7"/>
-      <c r="H3" s="8"/>
-      <c r="I3" s="8"/>
-      <c r="J3" s="8"/>
-      <c r="K3" s="8"/>
-      <c r="L3" s="8"/>
-      <c r="M3" s="8"/>
+      <c r="A3" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="F3" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G3" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="H3" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="I3" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="J3" s="8">
+        <v>90</v>
+      </c>
+      <c r="K3" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L3" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="M3" s="8">
+        <v>0</v>
+      </c>
       <c r="N3" s="7"/>
-      <c r="O3" s="8"/>
-      <c r="P3" s="8"/>
+      <c r="O3" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="P3" s="8" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="4" s="2" customFormat="1">
-      <c r="A4" s="7"/>
-      <c r="B4" s="7"/>
-      <c r="C4" s="7"/>
-      <c r="D4" s="7"/>
-      <c r="E4" s="7"/>
-      <c r="F4" s="7"/>
-      <c r="G4" s="7"/>
-      <c r="H4" s="8"/>
-      <c r="I4" s="8"/>
-      <c r="J4" s="8"/>
-      <c r="K4" s="8"/>
-      <c r="L4" s="8"/>
-      <c r="M4" s="8"/>
+      <c r="A4" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G4" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="H4" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="I4" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="J4" s="8">
+        <v>480</v>
+      </c>
+      <c r="K4" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="L4" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="M4" s="8">
+        <v>0</v>
+      </c>
       <c r="N4" s="7"/>
-      <c r="O4" s="8"/>
-      <c r="P4" s="8"/>
+      <c r="O4" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="P4" s="8" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="5" s="2" customFormat="1">
-      <c r="A5" s="7"/>
-      <c r="B5" s="7"/>
-      <c r="C5" s="7"/>
-      <c r="D5" s="7"/>
-      <c r="E5" s="7"/>
-      <c r="F5" s="7"/>
-      <c r="G5" s="7"/>
-      <c r="H5" s="8"/>
-      <c r="I5" s="8"/>
-      <c r="J5" s="8"/>
-      <c r="K5" s="8"/>
-      <c r="L5" s="8"/>
-      <c r="M5" s="8"/>
+      <c r="A5" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="F5" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G5" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="H5" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="I5" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="J5" s="8">
+        <v>90</v>
+      </c>
+      <c r="K5" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="L5" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="M5" s="8">
+        <v>0</v>
+      </c>
       <c r="N5" s="7"/>
-      <c r="O5" s="8"/>
-      <c r="P5" s="8"/>
+      <c r="O5" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="P5" s="8" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="6" s="2" customFormat="1">
-      <c r="A6" s="7"/>
-      <c r="B6" s="7"/>
-      <c r="C6" s="7"/>
-      <c r="D6" s="7"/>
-      <c r="E6" s="7"/>
-      <c r="F6" s="7"/>
-      <c r="G6" s="7"/>
-      <c r="H6" s="8"/>
-      <c r="I6" s="8"/>
-      <c r="J6" s="8"/>
-      <c r="K6" s="8"/>
-      <c r="L6" s="8"/>
-      <c r="M6" s="8"/>
+      <c r="A6" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="F6" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G6" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="H6" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="I6" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="J6" s="8">
+        <v>480</v>
+      </c>
+      <c r="K6" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="L6" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="M6" s="8">
+        <v>0</v>
+      </c>
       <c r="N6" s="7"/>
-      <c r="O6" s="8"/>
-      <c r="P6" s="8"/>
+      <c r="O6" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="P6" s="8" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="7" s="2" customFormat="1">
-      <c r="A7" s="7"/>
-      <c r="B7" s="7"/>
-      <c r="C7" s="7"/>
-      <c r="D7" s="7"/>
-      <c r="E7" s="7"/>
-      <c r="F7" s="7"/>
-      <c r="G7" s="7"/>
-      <c r="H7" s="8"/>
-      <c r="I7" s="8"/>
-      <c r="J7" s="8"/>
-      <c r="K7" s="8"/>
-      <c r="L7" s="8"/>
-      <c r="M7" s="8"/>
+      <c r="A7" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G7" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="H7" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="I7" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="J7" s="8">
+        <v>90</v>
+      </c>
+      <c r="K7" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="L7" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="M7" s="8">
+        <v>0</v>
+      </c>
       <c r="N7" s="7"/>
-      <c r="O7" s="8"/>
-      <c r="P7" s="8"/>
+      <c r="O7" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="P7" s="8" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="8" s="2" customFormat="1">
-      <c r="A8" s="7"/>
-      <c r="B8" s="7"/>
-      <c r="C8" s="7"/>
-      <c r="D8" s="7"/>
-      <c r="E8" s="7"/>
-      <c r="F8" s="7"/>
-      <c r="G8" s="7"/>
-      <c r="H8" s="8"/>
-      <c r="I8" s="8"/>
-      <c r="J8" s="8"/>
-      <c r="K8" s="8"/>
-      <c r="L8" s="8"/>
-      <c r="M8" s="8"/>
+      <c r="A8" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="F8" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G8" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="H8" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="I8" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="J8" s="8">
+        <v>480</v>
+      </c>
+      <c r="K8" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="L8" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="M8" s="8">
+        <v>0</v>
+      </c>
       <c r="N8" s="7"/>
-      <c r="O8" s="8"/>
-      <c r="P8" s="8"/>
+      <c r="O8" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="P8" s="8" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="9" s="2" customFormat="1">
-      <c r="A9" s="7"/>
-      <c r="B9" s="7"/>
-      <c r="C9" s="7"/>
-      <c r="D9" s="7"/>
-      <c r="E9" s="7"/>
-      <c r="F9" s="7"/>
-      <c r="G9" s="7"/>
-      <c r="H9" s="8"/>
-      <c r="I9" s="8"/>
-      <c r="J9" s="8"/>
-      <c r="K9" s="8"/>
-      <c r="L9" s="8"/>
-      <c r="M9" s="8"/>
+      <c r="A9" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="F9" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G9" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="H9" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="I9" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="J9" s="8">
+        <v>480</v>
+      </c>
+      <c r="K9" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="L9" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="M9" s="8">
+        <v>0</v>
+      </c>
       <c r="N9" s="7"/>
-      <c r="O9" s="8"/>
-      <c r="P9" s="8"/>
+      <c r="O9" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="P9" s="8" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="10" s="2" customFormat="1">
-      <c r="A10" s="7"/>
-      <c r="B10" s="7"/>
-      <c r="C10" s="7"/>
-      <c r="D10" s="7"/>
-      <c r="E10" s="7"/>
-      <c r="F10" s="7"/>
-      <c r="G10" s="7"/>
-      <c r="H10" s="8"/>
-      <c r="I10" s="8"/>
-      <c r="J10" s="8"/>
-      <c r="K10" s="8"/>
-      <c r="L10" s="8"/>
-      <c r="M10" s="8"/>
+      <c r="A10" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="F10" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G10" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="H10" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="I10" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="J10" s="8">
+        <v>480</v>
+      </c>
+      <c r="K10" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="L10" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="M10" s="8">
+        <v>0</v>
+      </c>
       <c r="N10" s="7"/>
-      <c r="O10" s="8"/>
-      <c r="P10" s="8"/>
+      <c r="O10" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="P10" s="8" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="11" s="2" customFormat="1">
-      <c r="A11" s="7"/>
-      <c r="B11" s="7"/>
-      <c r="C11" s="7"/>
-      <c r="D11" s="7"/>
-      <c r="E11" s="7"/>
-      <c r="F11" s="7"/>
-      <c r="G11" s="7"/>
-      <c r="H11" s="8"/>
-      <c r="I11" s="8"/>
-      <c r="J11" s="8"/>
-      <c r="K11" s="8"/>
-      <c r="L11" s="8"/>
-      <c r="M11" s="8"/>
+      <c r="A11" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="F11" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G11" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="H11" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="I11" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="J11" s="8">
+        <v>480</v>
+      </c>
+      <c r="K11" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="L11" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="M11" s="8">
+        <v>0</v>
+      </c>
       <c r="N11" s="7"/>
-      <c r="O11" s="8"/>
-      <c r="P11" s="8"/>
+      <c r="O11" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="P11" s="8" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="12" s="2" customFormat="1">
-      <c r="A12" s="7"/>
-      <c r="B12" s="7"/>
-      <c r="C12" s="7"/>
-      <c r="D12" s="7"/>
-      <c r="E12" s="7"/>
-      <c r="F12" s="7"/>
-      <c r="G12" s="7"/>
-      <c r="H12" s="8"/>
-      <c r="I12" s="8"/>
-      <c r="J12" s="8"/>
-      <c r="K12" s="8"/>
-      <c r="L12" s="8"/>
-      <c r="M12" s="8"/>
+      <c r="A12" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E12" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="F12" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G12" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="H12" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="I12" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="J12" s="8">
+        <v>480</v>
+      </c>
+      <c r="K12" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="L12" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="M12" s="8">
+        <v>0</v>
+      </c>
       <c r="N12" s="7"/>
-      <c r="O12" s="8"/>
-      <c r="P12" s="8"/>
+      <c r="O12" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="P12" s="8" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="13" s="2" customFormat="1">
-      <c r="A13" s="7"/>
-      <c r="B13" s="7"/>
-      <c r="C13" s="7"/>
-      <c r="D13" s="7"/>
-      <c r="E13" s="7"/>
-      <c r="F13" s="7"/>
-      <c r="G13" s="7"/>
-      <c r="H13" s="8"/>
-      <c r="I13" s="8"/>
-      <c r="J13" s="8"/>
-      <c r="K13" s="8"/>
-      <c r="L13" s="8"/>
-      <c r="M13" s="8"/>
+      <c r="A13" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E13" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="F13" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G13" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="H13" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="I13" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="J13" s="8">
+        <v>150</v>
+      </c>
+      <c r="K13" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="L13" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="M13" s="8">
+        <v>60</v>
+      </c>
       <c r="N13" s="7"/>
-      <c r="O13" s="8"/>
-      <c r="P13" s="8"/>
+      <c r="O13" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="P13" s="8" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="14" s="2" customFormat="1">
-      <c r="A14" s="7"/>
-      <c r="B14" s="7"/>
-      <c r="C14" s="7"/>
-      <c r="D14" s="7"/>
-      <c r="E14" s="7"/>
-      <c r="F14" s="7"/>
-      <c r="G14" s="7"/>
-      <c r="H14" s="8"/>
-      <c r="I14" s="8"/>
-      <c r="J14" s="8"/>
-      <c r="K14" s="8"/>
-      <c r="L14" s="8"/>
-      <c r="M14" s="8"/>
+      <c r="A14" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E14" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="F14" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G14" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="H14" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="I14" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="J14" s="8">
+        <v>480</v>
+      </c>
+      <c r="K14" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="L14" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="M14" s="8">
+        <v>0</v>
+      </c>
       <c r="N14" s="7"/>
-      <c r="O14" s="8"/>
-      <c r="P14" s="8"/>
+      <c r="O14" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="P14" s="8" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="15" s="2" customFormat="1">
-      <c r="A15" s="7"/>
-      <c r="B15" s="7"/>
-      <c r="C15" s="7"/>
-      <c r="D15" s="7"/>
-      <c r="E15" s="7"/>
-      <c r="F15" s="7"/>
-      <c r="G15" s="7"/>
-      <c r="H15" s="8"/>
-      <c r="I15" s="8"/>
-      <c r="J15" s="8"/>
-      <c r="K15" s="8"/>
-      <c r="L15" s="8"/>
-      <c r="M15" s="8"/>
+      <c r="A15" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="F15" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G15" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="H15" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="I15" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="J15" s="8">
+        <v>480</v>
+      </c>
+      <c r="K15" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="L15" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="M15" s="8">
+        <v>0</v>
+      </c>
       <c r="N15" s="7"/>
-      <c r="O15" s="8"/>
-      <c r="P15" s="8"/>
+      <c r="O15" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="P15" s="8" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="16" s="2" customFormat="1">
-      <c r="A16" s="7"/>
-      <c r="B16" s="7"/>
-      <c r="C16" s="7"/>
-      <c r="D16" s="7"/>
-      <c r="E16" s="7"/>
-      <c r="F16" s="7"/>
-      <c r="G16" s="7"/>
-      <c r="H16" s="8"/>
-      <c r="I16" s="8"/>
-      <c r="J16" s="8"/>
-      <c r="K16" s="8"/>
-      <c r="L16" s="8"/>
-      <c r="M16" s="8"/>
+      <c r="A16" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E16" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="F16" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G16" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="H16" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="I16" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="J16" s="8">
+        <v>480</v>
+      </c>
+      <c r="K16" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="L16" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="M16" s="8">
+        <v>0</v>
+      </c>
       <c r="N16" s="7"/>
-      <c r="O16" s="8"/>
-      <c r="P16" s="8"/>
+      <c r="O16" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="P16" s="8" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="17" s="2" customFormat="1">
-      <c r="A17" s="7"/>
-      <c r="B17" s="7"/>
-      <c r="C17" s="7"/>
-      <c r="D17" s="7"/>
-      <c r="E17" s="7"/>
-      <c r="F17" s="7"/>
-      <c r="G17" s="7"/>
-      <c r="H17" s="8"/>
-      <c r="I17" s="8"/>
-      <c r="J17" s="8"/>
-      <c r="K17" s="8"/>
-      <c r="L17" s="8"/>
-      <c r="M17" s="8"/>
+      <c r="A17" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E17" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="F17" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G17" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="H17" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="I17" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="J17" s="8">
+        <v>480</v>
+      </c>
+      <c r="K17" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="L17" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="M17" s="8">
+        <v>0</v>
+      </c>
       <c r="N17" s="7"/>
-      <c r="O17" s="8"/>
-      <c r="P17" s="8"/>
+      <c r="O17" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="P17" s="8" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="18" s="2" customFormat="1">
-      <c r="A18" s="7"/>
-      <c r="B18" s="7"/>
-      <c r="C18" s="7"/>
-      <c r="D18" s="7"/>
-      <c r="E18" s="7"/>
-      <c r="F18" s="7"/>
-      <c r="G18" s="7"/>
-      <c r="H18" s="8"/>
-      <c r="I18" s="8"/>
-      <c r="J18" s="8"/>
-      <c r="K18" s="8"/>
-      <c r="L18" s="8"/>
-      <c r="M18" s="8"/>
+      <c r="A18" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D18" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E18" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="F18" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G18" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="H18" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="I18" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="J18" s="8">
+        <v>480</v>
+      </c>
+      <c r="K18" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="L18" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="M18" s="8">
+        <v>0</v>
+      </c>
       <c r="N18" s="7"/>
-      <c r="O18" s="8"/>
-      <c r="P18" s="8"/>
+      <c r="O18" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="P18" s="8" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="19" s="2" customFormat="1">
-      <c r="A19" s="7"/>
-      <c r="B19" s="7"/>
-      <c r="C19" s="7"/>
-      <c r="D19" s="7"/>
-      <c r="E19" s="7"/>
-      <c r="F19" s="7"/>
-      <c r="G19" s="7"/>
-      <c r="H19" s="8"/>
-      <c r="I19" s="8"/>
-      <c r="J19" s="8"/>
-      <c r="K19" s="8"/>
-      <c r="L19" s="8"/>
-      <c r="M19" s="8"/>
+      <c r="A19" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D19" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E19" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="F19" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G19" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="H19" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="I19" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="J19" s="8">
+        <v>480</v>
+      </c>
+      <c r="K19" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="L19" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="M19" s="8">
+        <v>0</v>
+      </c>
       <c r="N19" s="7"/>
-      <c r="O19" s="8"/>
-      <c r="P19" s="8"/>
+      <c r="O19" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="P19" s="8" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="20" s="2" customFormat="1">
-      <c r="A20" s="7"/>
-      <c r="B20" s="7"/>
-      <c r="C20" s="7"/>
-      <c r="D20" s="7"/>
-      <c r="E20" s="7"/>
-      <c r="F20" s="7"/>
-      <c r="G20" s="7"/>
-      <c r="H20" s="8"/>
-      <c r="I20" s="8"/>
-      <c r="J20" s="8"/>
-      <c r="K20" s="8"/>
-      <c r="L20" s="8"/>
-      <c r="M20" s="8"/>
+      <c r="A20" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D20" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E20" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="F20" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G20" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="H20" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="I20" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="J20" s="8">
+        <v>480</v>
+      </c>
+      <c r="K20" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="L20" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="M20" s="8">
+        <v>0</v>
+      </c>
       <c r="N20" s="7"/>
-      <c r="O20" s="8"/>
-      <c r="P20" s="8"/>
+      <c r="O20" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="P20" s="8" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="21" s="2" customFormat="1">
-      <c r="A21" s="7"/>
-      <c r="B21" s="7"/>
-      <c r="C21" s="7"/>
-      <c r="D21" s="7"/>
-      <c r="E21" s="7"/>
-      <c r="F21" s="7"/>
-      <c r="G21" s="7"/>
-      <c r="H21" s="8"/>
-      <c r="I21" s="8"/>
-      <c r="J21" s="8"/>
-      <c r="K21" s="8"/>
-      <c r="L21" s="8"/>
-      <c r="M21" s="8"/>
+      <c r="A21" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="C21" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D21" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E21" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="F21" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G21" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="H21" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="I21" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="J21" s="8">
+        <v>480</v>
+      </c>
+      <c r="K21" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="L21" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="M21" s="8">
+        <v>0</v>
+      </c>
       <c r="N21" s="7"/>
-      <c r="O21" s="8"/>
-      <c r="P21" s="8"/>
+      <c r="O21" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="P21" s="8" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="22" s="2" customFormat="1">
-      <c r="A22" s="7"/>
-      <c r="B22" s="7"/>
-      <c r="C22" s="7"/>
-      <c r="D22" s="7"/>
-      <c r="E22" s="7"/>
-      <c r="F22" s="7"/>
-      <c r="G22" s="7"/>
-      <c r="H22" s="8"/>
-      <c r="I22" s="8"/>
-      <c r="J22" s="8"/>
-      <c r="K22" s="8"/>
-      <c r="L22" s="8"/>
-      <c r="M22" s="8"/>
+      <c r="A22" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="B22" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="C22" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D22" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E22" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="F22" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G22" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="H22" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="I22" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="J22" s="8">
+        <v>480</v>
+      </c>
+      <c r="K22" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="L22" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="M22" s="8">
+        <v>0</v>
+      </c>
       <c r="N22" s="7"/>
-      <c r="O22" s="8"/>
-      <c r="P22" s="8"/>
+      <c r="O22" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="P22" s="8" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="23" s="2" customFormat="1">
-      <c r="A23" s="7"/>
-      <c r="B23" s="7"/>
-      <c r="C23" s="7"/>
-      <c r="D23" s="7"/>
-      <c r="E23" s="7"/>
-      <c r="F23" s="7"/>
-      <c r="G23" s="7"/>
-      <c r="H23" s="8"/>
-      <c r="I23" s="8"/>
-      <c r="J23" s="8"/>
-      <c r="K23" s="8"/>
-      <c r="L23" s="8"/>
-      <c r="M23" s="8"/>
+      <c r="A23" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="B23" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="C23" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D23" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E23" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="F23" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G23" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="H23" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="I23" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="J23" s="8">
+        <v>90</v>
+      </c>
+      <c r="K23" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="L23" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="M23" s="8">
+        <v>0</v>
+      </c>
       <c r="N23" s="7"/>
-      <c r="O23" s="8"/>
-      <c r="P23" s="8"/>
+      <c r="O23" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="P23" s="8" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="24" s="2" customFormat="1">
-      <c r="A24" s="7"/>
-      <c r="B24" s="7"/>
-      <c r="C24" s="7"/>
-      <c r="D24" s="7"/>
-      <c r="E24" s="7"/>
-      <c r="F24" s="7"/>
-      <c r="G24" s="7"/>
-      <c r="H24" s="8"/>
-      <c r="I24" s="8"/>
-      <c r="J24" s="8"/>
-      <c r="K24" s="8"/>
-      <c r="L24" s="8"/>
-      <c r="M24" s="8"/>
+      <c r="A24" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="B24" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="C24" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D24" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E24" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="F24" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G24" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="H24" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="I24" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="J24" s="8">
+        <v>480</v>
+      </c>
+      <c r="K24" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="L24" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="M24" s="8">
+        <v>0</v>
+      </c>
       <c r="N24" s="7"/>
-      <c r="O24" s="8"/>
-      <c r="P24" s="8"/>
+      <c r="O24" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="P24" s="8" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="25" s="2" customFormat="1">
-      <c r="A25" s="7"/>
-      <c r="B25" s="7"/>
-      <c r="C25" s="7"/>
-      <c r="D25" s="7"/>
-      <c r="E25" s="7"/>
-      <c r="F25" s="7"/>
-      <c r="G25" s="7"/>
-      <c r="H25" s="8"/>
-      <c r="I25" s="8"/>
-      <c r="J25" s="8"/>
-      <c r="K25" s="8"/>
-      <c r="L25" s="8"/>
-      <c r="M25" s="8"/>
+      <c r="A25" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="B25" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="C25" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D25" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E25" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="F25" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G25" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="H25" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="I25" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="J25" s="8">
+        <v>90</v>
+      </c>
+      <c r="K25" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="L25" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="M25" s="8">
+        <v>0</v>
+      </c>
       <c r="N25" s="7"/>
-      <c r="O25" s="8"/>
-      <c r="P25" s="8"/>
+      <c r="O25" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="P25" s="8" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="26" s="2" customFormat="1">
-      <c r="A26" s="7"/>
-      <c r="B26" s="7"/>
-      <c r="C26" s="7"/>
-      <c r="D26" s="7"/>
-      <c r="E26" s="7"/>
-      <c r="F26" s="7"/>
-      <c r="G26" s="7"/>
-      <c r="H26" s="8"/>
-      <c r="I26" s="8"/>
-      <c r="J26" s="8"/>
-      <c r="K26" s="8"/>
-      <c r="L26" s="8"/>
-      <c r="M26" s="8"/>
+      <c r="A26" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="B26" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="C26" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D26" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E26" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="F26" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G26" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="H26" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="I26" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="J26" s="8">
+        <v>480</v>
+      </c>
+      <c r="K26" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="L26" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="M26" s="8">
+        <v>0</v>
+      </c>
       <c r="N26" s="7"/>
-      <c r="O26" s="8"/>
-      <c r="P26" s="8"/>
+      <c r="O26" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="P26" s="8" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="27" s="2" customFormat="1">
-      <c r="A27" s="7"/>
-      <c r="B27" s="7"/>
-      <c r="C27" s="7"/>
-      <c r="D27" s="7"/>
-      <c r="E27" s="7"/>
-      <c r="F27" s="7"/>
-      <c r="G27" s="7"/>
-      <c r="H27" s="8"/>
-      <c r="I27" s="8"/>
-      <c r="J27" s="8"/>
-      <c r="K27" s="8"/>
-      <c r="L27" s="8"/>
-      <c r="M27" s="8"/>
+      <c r="A27" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="B27" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="C27" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D27" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="F27" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G27" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="H27" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="I27" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="J27" s="8">
+        <v>90</v>
+      </c>
+      <c r="K27" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="L27" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="M27" s="8">
+        <v>0</v>
+      </c>
       <c r="N27" s="7"/>
-      <c r="O27" s="8"/>
-      <c r="P27" s="8"/>
+      <c r="O27" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="P27" s="8" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="28" s="2" customFormat="1">
-      <c r="A28" s="7"/>
-      <c r="B28" s="7"/>
-      <c r="C28" s="7"/>
-      <c r="D28" s="7"/>
-      <c r="E28" s="7"/>
-      <c r="F28" s="7"/>
-      <c r="G28" s="7"/>
-      <c r="H28" s="8"/>
-      <c r="I28" s="8"/>
-      <c r="J28" s="8"/>
-      <c r="K28" s="8"/>
-      <c r="L28" s="8"/>
-      <c r="M28" s="8"/>
+      <c r="A28" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="B28" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="C28" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D28" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="F28" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G28" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="H28" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="I28" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="J28" s="8">
+        <v>90</v>
+      </c>
+      <c r="K28" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="L28" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="M28" s="8">
+        <v>0</v>
+      </c>
       <c r="N28" s="7"/>
-      <c r="O28" s="8"/>
-      <c r="P28" s="8"/>
+      <c r="O28" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="P28" s="8" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="29" s="2" customFormat="1">
-      <c r="A29" s="7"/>
-      <c r="B29" s="7"/>
-      <c r="C29" s="7"/>
-      <c r="D29" s="7"/>
-      <c r="E29" s="7"/>
-      <c r="F29" s="7"/>
-      <c r="G29" s="7"/>
-      <c r="H29" s="8"/>
-      <c r="I29" s="8"/>
-      <c r="J29" s="8"/>
-      <c r="K29" s="8"/>
-      <c r="L29" s="8"/>
-      <c r="M29" s="8"/>
+      <c r="A29" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="B29" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="C29" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D29" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E29" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="F29" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G29" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="H29" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="I29" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="J29" s="8">
+        <v>90</v>
+      </c>
+      <c r="K29" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="L29" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="M29" s="8">
+        <v>0</v>
+      </c>
       <c r="N29" s="7"/>
-      <c r="O29" s="8"/>
-      <c r="P29" s="8"/>
+      <c r="O29" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="P29" s="8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="F30" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G30" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H30" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="I30" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="J30" s="4">
+        <v>480</v>
+      </c>
+      <c r="K30" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="L30" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="M30" s="4">
+        <v>0</v>
+      </c>
+      <c r="N30" s="3"/>
+      <c r="O30" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="P30" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="F31" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G31" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H31" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="I31" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="J31" s="4">
+        <v>90</v>
+      </c>
+      <c r="K31" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="L31" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="M31" s="4">
+        <v>0</v>
+      </c>
+      <c r="N31" s="3"/>
+      <c r="O31" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="P31" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H32" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="I32" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="J32" s="4">
+        <v>90</v>
+      </c>
+      <c r="K32" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="L32" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="M32" s="4">
+        <v>0</v>
+      </c>
+      <c r="N32" s="3"/>
+      <c r="O32" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="P32" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="F33" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G33" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H33" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="I33" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="J33" s="4">
+        <v>90</v>
+      </c>
+      <c r="K33" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="L33" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="M33" s="4">
+        <v>0</v>
+      </c>
+      <c r="N33" s="3"/>
+      <c r="O33" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="P33" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="F34" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G34" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H34" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="I34" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="J34" s="4">
+        <v>90</v>
+      </c>
+      <c r="K34" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="L34" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="M34" s="4">
+        <v>0</v>
+      </c>
+      <c r="N34" s="3"/>
+      <c r="O34" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="P34" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="F35" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G35" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H35" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="I35" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="J35" s="4">
+        <v>90</v>
+      </c>
+      <c r="K35" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="L35" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="M35" s="4">
+        <v>0</v>
+      </c>
+      <c r="N35" s="3"/>
+      <c r="O35" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="P35" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E36" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="F36" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G36" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H36" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="I36" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="J36" s="4">
+        <v>480</v>
+      </c>
+      <c r="K36" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="L36" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="M36" s="4">
+        <v>0</v>
+      </c>
+      <c r="N36" s="3"/>
+      <c r="O36" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="P36" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E37" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="F37" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G37" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H37" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="I37" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="J37" s="4">
+        <v>90</v>
+      </c>
+      <c r="K37" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="L37" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="M37" s="4">
+        <v>0</v>
+      </c>
+      <c r="N37" s="3"/>
+      <c r="O37" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="P37" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="F38" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G38" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H38" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="I38" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="J38" s="4">
+        <v>90</v>
+      </c>
+      <c r="K38" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="L38" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="M38" s="4">
+        <v>0</v>
+      </c>
+      <c r="N38" s="3"/>
+      <c r="O38" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="P38" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D39" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E39" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="F39" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G39" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H39" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="I39" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="J39" s="4">
+        <v>90</v>
+      </c>
+      <c r="K39" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="L39" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="M39" s="4">
+        <v>0</v>
+      </c>
+      <c r="N39" s="3"/>
+      <c r="O39" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="P39" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D40" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E40" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="F40" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G40" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H40" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="I40" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="J40" s="4">
+        <v>90</v>
+      </c>
+      <c r="K40" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="L40" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="M40" s="4">
+        <v>0</v>
+      </c>
+      <c r="N40" s="3"/>
+      <c r="O40" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="P40" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D41" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="F41" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G41" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H41" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="I41" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="J41" s="4">
+        <v>480</v>
+      </c>
+      <c r="K41" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="L41" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="M41" s="4">
+        <v>0</v>
+      </c>
+      <c r="N41" s="3"/>
+      <c r="O41" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="P41" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D42" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E42" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="F42" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G42" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H42" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="I42" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="J42" s="4">
+        <v>90</v>
+      </c>
+      <c r="K42" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="L42" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="M42" s="4">
+        <v>0</v>
+      </c>
+      <c r="N42" s="3"/>
+      <c r="O42" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="P42" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D43" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="F43" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G43" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H43" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="I43" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="J43" s="4">
+        <v>90</v>
+      </c>
+      <c r="K43" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="L43" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="M43" s="4">
+        <v>0</v>
+      </c>
+      <c r="N43" s="3"/>
+      <c r="O43" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="P43" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D44" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H44" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="I44" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="J44" s="4">
+        <v>480</v>
+      </c>
+      <c r="K44" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="L44" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="M44" s="4">
+        <v>0</v>
+      </c>
+      <c r="N44" s="3"/>
+      <c r="O44" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="P44" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="C45" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D45" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H45" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="I45" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="J45" s="4">
+        <v>480</v>
+      </c>
+      <c r="K45" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="L45" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="M45" s="4">
+        <v>0</v>
+      </c>
+      <c r="N45" s="3"/>
+      <c r="O45" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="P45" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D46" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E46" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F46" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G46" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H46" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="I46" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="J46" s="4">
+        <v>480</v>
+      </c>
+      <c r="K46" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="L46" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="M46" s="4">
+        <v>0</v>
+      </c>
+      <c r="N46" s="3"/>
+      <c r="O46" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="P46" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="C47" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D47" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H47" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="I47" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="J47" s="4">
+        <v>480</v>
+      </c>
+      <c r="K47" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="L47" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="M47" s="4">
+        <v>0</v>
+      </c>
+      <c r="N47" s="3"/>
+      <c r="O47" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="P47" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="C48" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D48" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E48" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F48" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G48" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H48" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="I48" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="J48" s="4">
+        <v>480</v>
+      </c>
+      <c r="K48" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="L48" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="M48" s="4">
+        <v>0</v>
+      </c>
+      <c r="N48" s="3"/>
+      <c r="O48" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="P48" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="C49" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D49" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E49" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="F49" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G49" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H49" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="I49" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="J49" s="4">
+        <v>90</v>
+      </c>
+      <c r="K49" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="L49" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="M49" s="4">
+        <v>0</v>
+      </c>
+      <c r="N49" s="3"/>
+      <c r="O49" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="P49" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="C50" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D50" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E50" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F50" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G50" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H50" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="I50" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="J50" s="4">
+        <v>480</v>
+      </c>
+      <c r="K50" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="L50" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="M50" s="4">
+        <v>0</v>
+      </c>
+      <c r="N50" s="3"/>
+      <c r="O50" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="P50" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="C51" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D51" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E51" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="F51" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G51" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H51" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="I51" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="J51" s="4">
+        <v>90</v>
+      </c>
+      <c r="K51" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="L51" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="M51" s="4">
+        <v>0</v>
+      </c>
+      <c r="N51" s="3"/>
+      <c r="O51" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="P51" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="C52" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D52" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="F52" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G52" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H52" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="I52" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="J52" s="4">
+        <v>90</v>
+      </c>
+      <c r="K52" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="L52" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="M52" s="4">
+        <v>0</v>
+      </c>
+      <c r="N52" s="3"/>
+      <c r="O52" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="P52" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="C53" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D53" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E53" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="F53" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G53" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H53" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="I53" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="J53" s="4">
+        <v>90</v>
+      </c>
+      <c r="K53" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="L53" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="M53" s="4">
+        <v>0</v>
+      </c>
+      <c r="N53" s="3"/>
+      <c r="O53" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="P53" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="C54" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D54" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E54" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="F54" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G54" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H54" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="I54" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="J54" s="4">
+        <v>90</v>
+      </c>
+      <c r="K54" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="L54" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="M54" s="4">
+        <v>0</v>
+      </c>
+      <c r="N54" s="3"/>
+      <c r="O54" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="P54" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="C55" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D55" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E55" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="F55" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G55" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H55" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="I55" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="J55" s="4">
+        <v>90</v>
+      </c>
+      <c r="K55" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="L55" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="M55" s="4">
+        <v>0</v>
+      </c>
+      <c r="N55" s="3"/>
+      <c r="O55" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="P55" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="C56" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D56" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E56" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="F56" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G56" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H56" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="I56" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="J56" s="4">
+        <v>90</v>
+      </c>
+      <c r="K56" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="L56" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="M56" s="4">
+        <v>0</v>
+      </c>
+      <c r="N56" s="3"/>
+      <c r="O56" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="P56" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="B57" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="C57" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D57" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E57" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="F57" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G57" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H57" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="I57" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="J57" s="4">
+        <v>480</v>
+      </c>
+      <c r="K57" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="L57" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="M57" s="4">
+        <v>0</v>
+      </c>
+      <c r="N57" s="3"/>
+      <c r="O57" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="P57" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="C58" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D58" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E58" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="F58" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G58" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H58" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="I58" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="J58" s="4">
+        <v>90</v>
+      </c>
+      <c r="K58" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="L58" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="M58" s="4">
+        <v>0</v>
+      </c>
+      <c r="N58" s="3"/>
+      <c r="O58" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="P58" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="C59" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D59" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E59" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="F59" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G59" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H59" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="I59" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="J59" s="4">
+        <v>480</v>
+      </c>
+      <c r="K59" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="L59" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="M59" s="4">
+        <v>0</v>
+      </c>
+      <c r="N59" s="3"/>
+      <c r="O59" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="P59" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="C60" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D60" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E60" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="F60" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G60" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H60" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="I60" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="J60" s="4">
+        <v>90</v>
+      </c>
+      <c r="K60" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="L60" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="M60" s="4">
+        <v>0</v>
+      </c>
+      <c r="N60" s="3"/>
+      <c r="O60" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="P60" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="B61" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="C61" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D61" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E61" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="F61" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G61" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H61" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="I61" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="J61" s="4">
+        <v>480</v>
+      </c>
+      <c r="K61" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="L61" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="M61" s="4">
+        <v>0</v>
+      </c>
+      <c r="N61" s="3"/>
+      <c r="O61" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="P61" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="B62" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="C62" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D62" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H62" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="I62" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="J62" s="4">
+        <v>90</v>
+      </c>
+      <c r="K62" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="L62" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="M62" s="4">
+        <v>0</v>
+      </c>
+      <c r="N62" s="3"/>
+      <c r="O62" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="P62" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="B63" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="C63" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D63" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E63" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="F63" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G63" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H63" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="I63" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="J63" s="4">
+        <v>90</v>
+      </c>
+      <c r="K63" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="L63" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="M63" s="4">
+        <v>0</v>
+      </c>
+      <c r="N63" s="3"/>
+      <c r="O63" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="P63" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="B64" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="C64" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D64" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E64" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="F64" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G64" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H64" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="I64" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="J64" s="4">
+        <v>90</v>
+      </c>
+      <c r="K64" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="L64" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="M64" s="4">
+        <v>0</v>
+      </c>
+      <c r="N64" s="3"/>
+      <c r="O64" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="P64" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="B65" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="C65" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D65" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E65" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="F65" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G65" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H65" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I65" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="J65" s="4">
+        <v>90</v>
+      </c>
+      <c r="K65" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="L65" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="M65" s="4">
+        <v>0</v>
+      </c>
+      <c r="N65" s="3"/>
+      <c r="O65" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="P65" s="4" t="s">
+        <v>27</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/data/hrm_sync_actual_2.xlsx
+++ b/data/hrm_sync_actual_2.xlsx
@@ -100,7 +100,25 @@
     <t>Bằng KH</t>
   </si>
   <si>
-    <t>Chờ cấp trên gian tiếp</t>
+    <t>Đã duyệt</t>
+  </si>
+  <si>
+    <t>02644066</t>
+  </si>
+  <si>
+    <t>Nguyễn Hữu Tình</t>
+  </si>
+  <si>
+    <t>tang ca van hanh may nghien</t>
+  </si>
+  <si>
+    <t>05/10/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>05/10/2026 15:30:00</t>
+  </si>
+  <si>
+    <t>Chưa duyệt</t>
   </si>
 </sst>
 </file>
@@ -634,22 +652,52 @@
       </c>
     </row>
     <row r="4" s="2" customFormat="1">
-      <c r="A4" s="7"/>
-      <c r="B4" s="7"/>
-      <c r="C4" s="7"/>
-      <c r="D4" s="7"/>
-      <c r="E4" s="7"/>
-      <c r="F4" s="7"/>
-      <c r="G4" s="7"/>
-      <c r="H4" s="8"/>
-      <c r="I4" s="8"/>
-      <c r="J4" s="8"/>
-      <c r="K4" s="8"/>
-      <c r="L4" s="8"/>
-      <c r="M4" s="8"/>
+      <c r="A4" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G4" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="H4" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="I4" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="J4" s="8">
+        <v>90</v>
+      </c>
+      <c r="K4" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="L4" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="M4" s="8">
+        <v>0</v>
+      </c>
       <c r="N4" s="7"/>
-      <c r="O4" s="8"/>
-      <c r="P4" s="8"/>
+      <c r="O4" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="P4" s="8" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="5" s="2" customFormat="1">
       <c r="A5" s="7"/>

--- a/data/hrm_sync_actual_2.xlsx
+++ b/data/hrm_sync_actual_2.xlsx
@@ -103,6 +103,42 @@
     <t>Đã duyệt</t>
   </si>
   <si>
+    <t>02644057</t>
+  </si>
+  <si>
+    <t>Phạm Văn Công</t>
+  </si>
+  <si>
+    <t>vận hành máy nghiền</t>
+  </si>
+  <si>
+    <t>05/10/2026 20:30:00</t>
+  </si>
+  <si>
+    <t>05/10/2026 22:00:00</t>
+  </si>
+  <si>
+    <t>02644075</t>
+  </si>
+  <si>
+    <t>Huỳnh Đại Nhân</t>
+  </si>
+  <si>
+    <t xml:space="preserve">vận hành máy nghiền </t>
+  </si>
+  <si>
+    <t>05/10/2026 12:30:00</t>
+  </si>
+  <si>
+    <t>05/10/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>06/10/2026 12:30:00</t>
+  </si>
+  <si>
+    <t>06/10/2026 14:00:00</t>
+  </si>
+  <si>
     <t>02644066</t>
   </si>
   <si>
@@ -112,13 +148,10 @@
     <t>tang ca van hanh may nghien</t>
   </si>
   <si>
-    <t>05/10/2026 14:00:00</t>
-  </si>
-  <si>
     <t>05/10/2026 15:30:00</t>
   </si>
   <si>
-    <t>Chưa duyệt</t>
+    <t>06/10/2026 15:30:00</t>
   </si>
 </sst>
 </file>
@@ -696,80 +729,200 @@
         <v>26</v>
       </c>
       <c r="P4" s="8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="5" s="2" customFormat="1">
+      <c r="A5" s="7" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="5" s="2" customFormat="1">
-      <c r="A5" s="7"/>
-      <c r="B5" s="7"/>
-      <c r="C5" s="7"/>
-      <c r="D5" s="7"/>
-      <c r="E5" s="7"/>
-      <c r="F5" s="7"/>
-      <c r="G5" s="7"/>
-      <c r="H5" s="8"/>
-      <c r="I5" s="8"/>
-      <c r="J5" s="8"/>
-      <c r="K5" s="8"/>
-      <c r="L5" s="8"/>
-      <c r="M5" s="8"/>
+      <c r="B5" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="F5" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G5" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="H5" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="I5" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="J5" s="8">
+        <v>90</v>
+      </c>
+      <c r="K5" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="L5" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="M5" s="8">
+        <v>0</v>
+      </c>
       <c r="N5" s="7"/>
-      <c r="O5" s="8"/>
-      <c r="P5" s="8"/>
+      <c r="O5" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="P5" s="8" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="6" s="2" customFormat="1">
-      <c r="A6" s="7"/>
-      <c r="B6" s="7"/>
-      <c r="C6" s="7"/>
-      <c r="D6" s="7"/>
-      <c r="E6" s="7"/>
-      <c r="F6" s="7"/>
-      <c r="G6" s="7"/>
-      <c r="H6" s="8"/>
-      <c r="I6" s="8"/>
-      <c r="J6" s="8"/>
-      <c r="K6" s="8"/>
-      <c r="L6" s="8"/>
-      <c r="M6" s="8"/>
+      <c r="A6" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="F6" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G6" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="H6" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="I6" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="J6" s="8">
+        <v>90</v>
+      </c>
+      <c r="K6" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="L6" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="M6" s="8">
+        <v>0</v>
+      </c>
       <c r="N6" s="7"/>
-      <c r="O6" s="8"/>
-      <c r="P6" s="8"/>
+      <c r="O6" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="P6" s="8" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="7" s="2" customFormat="1">
-      <c r="A7" s="7"/>
-      <c r="B7" s="7"/>
-      <c r="C7" s="7"/>
-      <c r="D7" s="7"/>
-      <c r="E7" s="7"/>
-      <c r="F7" s="7"/>
-      <c r="G7" s="7"/>
-      <c r="H7" s="8"/>
-      <c r="I7" s="8"/>
-      <c r="J7" s="8"/>
-      <c r="K7" s="8"/>
-      <c r="L7" s="8"/>
-      <c r="M7" s="8"/>
+      <c r="A7" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G7" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="H7" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="I7" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="J7" s="8">
+        <v>90</v>
+      </c>
+      <c r="K7" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="L7" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="M7" s="8">
+        <v>0</v>
+      </c>
       <c r="N7" s="7"/>
-      <c r="O7" s="8"/>
-      <c r="P7" s="8"/>
+      <c r="O7" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="P7" s="8" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="8" s="2" customFormat="1">
-      <c r="A8" s="7"/>
-      <c r="B8" s="7"/>
-      <c r="C8" s="7"/>
-      <c r="D8" s="7"/>
-      <c r="E8" s="7"/>
-      <c r="F8" s="7"/>
-      <c r="G8" s="7"/>
-      <c r="H8" s="8"/>
-      <c r="I8" s="8"/>
-      <c r="J8" s="8"/>
-      <c r="K8" s="8"/>
-      <c r="L8" s="8"/>
-      <c r="M8" s="8"/>
+      <c r="A8" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="F8" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G8" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="H8" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="I8" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="J8" s="8">
+        <v>90</v>
+      </c>
+      <c r="K8" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="L8" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="M8" s="8">
+        <v>0</v>
+      </c>
       <c r="N8" s="7"/>
-      <c r="O8" s="8"/>
-      <c r="P8" s="8"/>
+      <c r="O8" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="P8" s="8" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="9" s="2" customFormat="1">
       <c r="A9" s="7"/>

--- a/data/hrm_sync_actual_2.xlsx
+++ b/data/hrm_sync_actual_2.xlsx
@@ -70,55 +70,136 @@
     <t>Trạng thái duyệt</t>
   </si>
   <si>
+    <t>02644066</t>
+  </si>
+  <si>
+    <t>Nguyễn Hữu Tình</t>
+  </si>
+  <si>
+    <t>Plastic Extrusion</t>
+  </si>
+  <si>
+    <t>Pulverize</t>
+  </si>
+  <si>
+    <t>tang ca van hanh may nghien</t>
+  </si>
+  <si>
+    <t>Nguyễn Chí Cường</t>
+  </si>
+  <si>
+    <t>Thân Trọng Tuấn</t>
+  </si>
+  <si>
+    <t>05/10/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>05/10/2026 15:30:00</t>
+  </si>
+  <si>
+    <t>Bằng KH</t>
+  </si>
+  <si>
+    <t>Đã duyệt</t>
+  </si>
+  <si>
+    <t>06/10/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>06/10/2026 15:30:00</t>
+  </si>
+  <si>
+    <t>07/10/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>07/10/2026 15:30:00</t>
+  </si>
+  <si>
     <t>02020947</t>
   </si>
   <si>
     <t>Nguyễn Hoàng Duy</t>
   </si>
   <si>
-    <t>Plastic Extrusion</t>
-  </si>
-  <si>
-    <t>Pulverize</t>
-  </si>
-  <si>
     <t xml:space="preserve">di chuyển nguyên vật liệu nghiền </t>
   </si>
   <si>
-    <t>Nguyễn Chí Cường</t>
-  </si>
-  <si>
-    <t>Thân Trọng Tuấn</t>
-  </si>
-  <si>
     <t>02/10/2026 16:30:00</t>
   </si>
   <si>
     <t>02/10/2026 18:00:00</t>
   </si>
   <si>
-    <t>Bằng KH</t>
-  </si>
-  <si>
-    <t>Đã duyệt</t>
-  </si>
-  <si>
-    <t>02644066</t>
-  </si>
-  <si>
-    <t>Nguyễn Hữu Tình</t>
-  </si>
-  <si>
-    <t>tang ca van hanh may nghien</t>
-  </si>
-  <si>
-    <t>05/10/2026 14:00:00</t>
-  </si>
-  <si>
-    <t>05/10/2026 15:30:00</t>
+    <t>08/10/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>08/10/2026 15:30:00</t>
+  </si>
+  <si>
+    <t>09/10/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>09/10/2026 15:30:00</t>
   </si>
   <si>
     <t>Chưa duyệt</t>
+  </si>
+  <si>
+    <t>02644057</t>
+  </si>
+  <si>
+    <t>Phạm Văn Công</t>
+  </si>
+  <si>
+    <t>vận hành máy nghiền</t>
+  </si>
+  <si>
+    <t>05/10/2026 20:30:00</t>
+  </si>
+  <si>
+    <t>05/10/2026 22:00:00</t>
+  </si>
+  <si>
+    <t>06/10/2026 20:30:00</t>
+  </si>
+  <si>
+    <t>06/10/2026 22:00:00</t>
+  </si>
+  <si>
+    <t>07/10/2026 20:30:00</t>
+  </si>
+  <si>
+    <t>07/10/2026 22:00:00</t>
+  </si>
+  <si>
+    <t>08/10/2026 20:30:00</t>
+  </si>
+  <si>
+    <t>08/10/2026 22:00:00</t>
+  </si>
+  <si>
+    <t>02644075</t>
+  </si>
+  <si>
+    <t>Huỳnh Đại Nhân</t>
+  </si>
+  <si>
+    <t xml:space="preserve">vận hành máy nghiền </t>
+  </si>
+  <si>
+    <t>05/10/2026 12:30:00</t>
+  </si>
+  <si>
+    <t>07/10/2026 12:30:00</t>
+  </si>
+  <si>
+    <t>08/10/2026 12:30:00</t>
+  </si>
+  <si>
+    <t>09/10/2026 12:30:00</t>
+  </si>
+  <si>
+    <t>06/10/2026 12:30:00</t>
   </si>
 </sst>
 </file>
@@ -653,10 +734,10 @@
     </row>
     <row r="4" s="2" customFormat="1">
       <c r="A4" s="7" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="C4" s="7" t="s">
         <v>19</v>
@@ -665,7 +746,7 @@
         <v>20</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="F4" s="7" t="s">
         <v>22</v>
@@ -674,19 +755,19 @@
         <v>23</v>
       </c>
       <c r="H4" s="8" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="I4" s="8" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="J4" s="8">
         <v>90</v>
       </c>
       <c r="K4" s="8" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="L4" s="8" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="M4" s="8">
         <v>0</v>
@@ -696,242 +777,632 @@
         <v>26</v>
       </c>
       <c r="P4" s="8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="5" s="2" customFormat="1">
+      <c r="A5" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="F5" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G5" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="H5" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="I5" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="J5" s="8">
+        <v>90</v>
+      </c>
+      <c r="K5" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="L5" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="M5" s="8">
+        <v>0</v>
+      </c>
+      <c r="N5" s="7"/>
+      <c r="O5" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="P5" s="8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="6" s="2" customFormat="1">
+      <c r="A6" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="B6" s="7" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="5" s="2" customFormat="1">
-      <c r="A5" s="7"/>
-      <c r="B5" s="7"/>
-      <c r="C5" s="7"/>
-      <c r="D5" s="7"/>
-      <c r="E5" s="7"/>
-      <c r="F5" s="7"/>
-      <c r="G5" s="7"/>
-      <c r="H5" s="8"/>
-      <c r="I5" s="8"/>
-      <c r="J5" s="8"/>
-      <c r="K5" s="8"/>
-      <c r="L5" s="8"/>
-      <c r="M5" s="8"/>
-      <c r="N5" s="7"/>
-      <c r="O5" s="8"/>
-      <c r="P5" s="8"/>
-    </row>
-    <row r="6" s="2" customFormat="1">
-      <c r="A6" s="7"/>
-      <c r="B6" s="7"/>
-      <c r="C6" s="7"/>
-      <c r="D6" s="7"/>
-      <c r="E6" s="7"/>
-      <c r="F6" s="7"/>
-      <c r="G6" s="7"/>
-      <c r="H6" s="8"/>
-      <c r="I6" s="8"/>
-      <c r="J6" s="8"/>
-      <c r="K6" s="8"/>
-      <c r="L6" s="8"/>
-      <c r="M6" s="8"/>
+      <c r="C6" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="F6" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G6" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="H6" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="I6" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="J6" s="8">
+        <v>90</v>
+      </c>
+      <c r="K6" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="L6" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="M6" s="8">
+        <v>0</v>
+      </c>
       <c r="N6" s="7"/>
-      <c r="O6" s="8"/>
-      <c r="P6" s="8"/>
+      <c r="O6" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="P6" s="8" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="7" s="2" customFormat="1">
-      <c r="A7" s="7"/>
-      <c r="B7" s="7"/>
-      <c r="C7" s="7"/>
-      <c r="D7" s="7"/>
-      <c r="E7" s="7"/>
-      <c r="F7" s="7"/>
-      <c r="G7" s="7"/>
-      <c r="H7" s="8"/>
-      <c r="I7" s="8"/>
-      <c r="J7" s="8"/>
-      <c r="K7" s="8"/>
-      <c r="L7" s="8"/>
-      <c r="M7" s="8"/>
+      <c r="A7" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G7" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="H7" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="I7" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="J7" s="8">
+        <v>90</v>
+      </c>
+      <c r="K7" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="L7" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="M7" s="8">
+        <v>0</v>
+      </c>
       <c r="N7" s="7"/>
-      <c r="O7" s="8"/>
-      <c r="P7" s="8"/>
+      <c r="O7" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="P7" s="8" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="8" s="2" customFormat="1">
-      <c r="A8" s="7"/>
-      <c r="B8" s="7"/>
-      <c r="C8" s="7"/>
-      <c r="D8" s="7"/>
-      <c r="E8" s="7"/>
-      <c r="F8" s="7"/>
-      <c r="G8" s="7"/>
-      <c r="H8" s="8"/>
-      <c r="I8" s="8"/>
-      <c r="J8" s="8"/>
-      <c r="K8" s="8"/>
-      <c r="L8" s="8"/>
-      <c r="M8" s="8"/>
+      <c r="A8" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="F8" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G8" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="H8" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="I8" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="J8" s="8">
+        <v>90</v>
+      </c>
+      <c r="K8" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="L8" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="M8" s="8">
+        <v>0</v>
+      </c>
       <c r="N8" s="7"/>
-      <c r="O8" s="8"/>
-      <c r="P8" s="8"/>
+      <c r="O8" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="P8" s="8" t="s">
+        <v>41</v>
+      </c>
     </row>
     <row r="9" s="2" customFormat="1">
-      <c r="A9" s="7"/>
-      <c r="B9" s="7"/>
-      <c r="C9" s="7"/>
-      <c r="D9" s="7"/>
-      <c r="E9" s="7"/>
-      <c r="F9" s="7"/>
-      <c r="G9" s="7"/>
-      <c r="H9" s="8"/>
-      <c r="I9" s="8"/>
-      <c r="J9" s="8"/>
-      <c r="K9" s="8"/>
-      <c r="L9" s="8"/>
-      <c r="M9" s="8"/>
+      <c r="A9" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="F9" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G9" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="H9" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="I9" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="J9" s="8">
+        <v>90</v>
+      </c>
+      <c r="K9" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="L9" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="M9" s="8">
+        <v>0</v>
+      </c>
       <c r="N9" s="7"/>
-      <c r="O9" s="8"/>
-      <c r="P9" s="8"/>
+      <c r="O9" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="P9" s="8" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="10" s="2" customFormat="1">
-      <c r="A10" s="7"/>
-      <c r="B10" s="7"/>
-      <c r="C10" s="7"/>
-      <c r="D10" s="7"/>
-      <c r="E10" s="7"/>
-      <c r="F10" s="7"/>
-      <c r="G10" s="7"/>
-      <c r="H10" s="8"/>
-      <c r="I10" s="8"/>
-      <c r="J10" s="8"/>
-      <c r="K10" s="8"/>
-      <c r="L10" s="8"/>
-      <c r="M10" s="8"/>
+      <c r="A10" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="F10" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G10" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="H10" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="I10" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="J10" s="8">
+        <v>90</v>
+      </c>
+      <c r="K10" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="L10" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="M10" s="8">
+        <v>0</v>
+      </c>
       <c r="N10" s="7"/>
-      <c r="O10" s="8"/>
-      <c r="P10" s="8"/>
+      <c r="O10" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="P10" s="8" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="11" s="2" customFormat="1">
-      <c r="A11" s="7"/>
-      <c r="B11" s="7"/>
-      <c r="C11" s="7"/>
-      <c r="D11" s="7"/>
-      <c r="E11" s="7"/>
-      <c r="F11" s="7"/>
-      <c r="G11" s="7"/>
-      <c r="H11" s="8"/>
-      <c r="I11" s="8"/>
-      <c r="J11" s="8"/>
-      <c r="K11" s="8"/>
-      <c r="L11" s="8"/>
-      <c r="M11" s="8"/>
+      <c r="A11" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="F11" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G11" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="H11" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="I11" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="J11" s="8">
+        <v>90</v>
+      </c>
+      <c r="K11" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="L11" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="M11" s="8">
+        <v>0</v>
+      </c>
       <c r="N11" s="7"/>
-      <c r="O11" s="8"/>
-      <c r="P11" s="8"/>
+      <c r="O11" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="P11" s="8" t="s">
+        <v>41</v>
+      </c>
     </row>
     <row r="12" s="2" customFormat="1">
-      <c r="A12" s="7"/>
-      <c r="B12" s="7"/>
-      <c r="C12" s="7"/>
-      <c r="D12" s="7"/>
-      <c r="E12" s="7"/>
-      <c r="F12" s="7"/>
-      <c r="G12" s="7"/>
-      <c r="H12" s="8"/>
-      <c r="I12" s="8"/>
-      <c r="J12" s="8"/>
-      <c r="K12" s="8"/>
-      <c r="L12" s="8"/>
-      <c r="M12" s="8"/>
+      <c r="A12" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E12" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="F12" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G12" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="H12" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="I12" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="J12" s="8">
+        <v>90</v>
+      </c>
+      <c r="K12" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="L12" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="M12" s="8">
+        <v>0</v>
+      </c>
       <c r="N12" s="7"/>
-      <c r="O12" s="8"/>
-      <c r="P12" s="8"/>
+      <c r="O12" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="P12" s="8" t="s">
+        <v>41</v>
+      </c>
     </row>
     <row r="13" s="2" customFormat="1">
-      <c r="A13" s="7"/>
-      <c r="B13" s="7"/>
-      <c r="C13" s="7"/>
-      <c r="D13" s="7"/>
-      <c r="E13" s="7"/>
-      <c r="F13" s="7"/>
-      <c r="G13" s="7"/>
-      <c r="H13" s="8"/>
-      <c r="I13" s="8"/>
-      <c r="J13" s="8"/>
-      <c r="K13" s="8"/>
-      <c r="L13" s="8"/>
-      <c r="M13" s="8"/>
+      <c r="A13" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E13" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="F13" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G13" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="H13" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="I13" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="J13" s="8">
+        <v>90</v>
+      </c>
+      <c r="K13" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="L13" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="M13" s="8">
+        <v>0</v>
+      </c>
       <c r="N13" s="7"/>
-      <c r="O13" s="8"/>
-      <c r="P13" s="8"/>
+      <c r="O13" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="P13" s="8" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="14" s="2" customFormat="1">
-      <c r="A14" s="7"/>
-      <c r="B14" s="7"/>
-      <c r="C14" s="7"/>
-      <c r="D14" s="7"/>
-      <c r="E14" s="7"/>
-      <c r="F14" s="7"/>
-      <c r="G14" s="7"/>
-      <c r="H14" s="8"/>
-      <c r="I14" s="8"/>
-      <c r="J14" s="8"/>
-      <c r="K14" s="8"/>
-      <c r="L14" s="8"/>
-      <c r="M14" s="8"/>
+      <c r="A14" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E14" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="F14" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G14" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="H14" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="I14" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="J14" s="8">
+        <v>90</v>
+      </c>
+      <c r="K14" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="L14" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="M14" s="8">
+        <v>0</v>
+      </c>
       <c r="N14" s="7"/>
-      <c r="O14" s="8"/>
-      <c r="P14" s="8"/>
+      <c r="O14" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="P14" s="8" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="15" s="2" customFormat="1">
-      <c r="A15" s="7"/>
-      <c r="B15" s="7"/>
-      <c r="C15" s="7"/>
-      <c r="D15" s="7"/>
-      <c r="E15" s="7"/>
-      <c r="F15" s="7"/>
-      <c r="G15" s="7"/>
-      <c r="H15" s="8"/>
-      <c r="I15" s="8"/>
-      <c r="J15" s="8"/>
-      <c r="K15" s="8"/>
-      <c r="L15" s="8"/>
-      <c r="M15" s="8"/>
+      <c r="A15" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="F15" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G15" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="H15" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="I15" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="J15" s="8">
+        <v>90</v>
+      </c>
+      <c r="K15" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="L15" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="M15" s="8">
+        <v>0</v>
+      </c>
       <c r="N15" s="7"/>
-      <c r="O15" s="8"/>
-      <c r="P15" s="8"/>
+      <c r="O15" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="P15" s="8" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="16" s="2" customFormat="1">
-      <c r="A16" s="7"/>
-      <c r="B16" s="7"/>
-      <c r="C16" s="7"/>
-      <c r="D16" s="7"/>
-      <c r="E16" s="7"/>
-      <c r="F16" s="7"/>
-      <c r="G16" s="7"/>
-      <c r="H16" s="8"/>
-      <c r="I16" s="8"/>
-      <c r="J16" s="8"/>
-      <c r="K16" s="8"/>
-      <c r="L16" s="8"/>
-      <c r="M16" s="8"/>
+      <c r="A16" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E16" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="F16" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G16" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="H16" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="I16" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="J16" s="8">
+        <v>90</v>
+      </c>
+      <c r="K16" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="L16" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="M16" s="8">
+        <v>0</v>
+      </c>
       <c r="N16" s="7"/>
-      <c r="O16" s="8"/>
-      <c r="P16" s="8"/>
+      <c r="O16" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="P16" s="8" t="s">
+        <v>41</v>
+      </c>
     </row>
     <row r="17" s="2" customFormat="1">
-      <c r="A17" s="7"/>
-      <c r="B17" s="7"/>
-      <c r="C17" s="7"/>
-      <c r="D17" s="7"/>
-      <c r="E17" s="7"/>
-      <c r="F17" s="7"/>
-      <c r="G17" s="7"/>
-      <c r="H17" s="8"/>
-      <c r="I17" s="8"/>
-      <c r="J17" s="8"/>
-      <c r="K17" s="8"/>
-      <c r="L17" s="8"/>
-      <c r="M17" s="8"/>
+      <c r="A17" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E17" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="F17" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G17" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="H17" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="I17" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="J17" s="8">
+        <v>90</v>
+      </c>
+      <c r="K17" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="L17" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="M17" s="8">
+        <v>0</v>
+      </c>
       <c r="N17" s="7"/>
-      <c r="O17" s="8"/>
-      <c r="P17" s="8"/>
+      <c r="O17" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="P17" s="8" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="18" s="2" customFormat="1">
       <c r="A18" s="7"/>

--- a/data/hrm_sync_actual_2.xlsx
+++ b/data/hrm_sync_actual_2.xlsx
@@ -70,37 +70,88 @@
     <t>Trạng thái duyệt</t>
   </si>
   <si>
+    <t>02020947</t>
+  </si>
+  <si>
+    <t>Nguyễn Hoàng Duy</t>
+  </si>
+  <si>
+    <t>Plastic Extrusion</t>
+  </si>
+  <si>
+    <t>Pulverize</t>
+  </si>
+  <si>
+    <t xml:space="preserve">di chuyển nguyên vật liệu nghiền </t>
+  </si>
+  <si>
+    <t>Nguyễn Chí Cường</t>
+  </si>
+  <si>
+    <t>Thân Trọng Tuấn</t>
+  </si>
+  <si>
+    <t>02/10/2026 16:30:00</t>
+  </si>
+  <si>
+    <t>02/10/2026 18:00:00</t>
+  </si>
+  <si>
+    <t>Bằng KH</t>
+  </si>
+  <si>
+    <t>Đã duyệt</t>
+  </si>
+  <si>
     <t>02644066</t>
   </si>
   <si>
     <t>Nguyễn Hữu Tình</t>
   </si>
   <si>
-    <t>Plastic Extrusion</t>
-  </si>
-  <si>
-    <t>Pulverize</t>
-  </si>
-  <si>
     <t>tang ca van hanh may nghien</t>
   </si>
   <si>
-    <t>Nguyễn Chí Cường</t>
-  </si>
-  <si>
-    <t>Thân Trọng Tuấn</t>
-  </si>
-  <si>
     <t>05/10/2026 14:00:00</t>
   </si>
   <si>
     <t>05/10/2026 15:30:00</t>
   </si>
   <si>
-    <t>Bằng KH</t>
-  </si>
-  <si>
-    <t>Đã duyệt</t>
+    <t>02644075</t>
+  </si>
+  <si>
+    <t>Huỳnh Đại Nhân</t>
+  </si>
+  <si>
+    <t xml:space="preserve">vận hành máy nghiền </t>
+  </si>
+  <si>
+    <t>05/10/2026 12:30:00</t>
+  </si>
+  <si>
+    <t>02644057</t>
+  </si>
+  <si>
+    <t>Phạm Văn Công</t>
+  </si>
+  <si>
+    <t>vận hành máy nghiền</t>
+  </si>
+  <si>
+    <t>05/10/2026 20:30:00</t>
+  </si>
+  <si>
+    <t>05/10/2026 22:00:00</t>
+  </si>
+  <si>
+    <t>06/10/2026 20:30:00</t>
+  </si>
+  <si>
+    <t>06/10/2026 22:00:00</t>
+  </si>
+  <si>
+    <t>06/10/2026 12:30:00</t>
   </si>
   <si>
     <t>06/10/2026 14:00:00</t>
@@ -109,25 +160,25 @@
     <t>06/10/2026 15:30:00</t>
   </si>
   <si>
+    <t>07/10/2026 20:30:00</t>
+  </si>
+  <si>
+    <t>07/10/2026 22:00:00</t>
+  </si>
+  <si>
     <t>07/10/2026 14:00:00</t>
   </si>
   <si>
     <t>07/10/2026 15:30:00</t>
   </si>
   <si>
-    <t>02020947</t>
-  </si>
-  <si>
-    <t>Nguyễn Hoàng Duy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">di chuyển nguyên vật liệu nghiền </t>
-  </si>
-  <si>
-    <t>02/10/2026 16:30:00</t>
-  </si>
-  <si>
-    <t>02/10/2026 18:00:00</t>
+    <t>07/10/2026 12:30:00</t>
+  </si>
+  <si>
+    <t>08/10/2026 20:30:00</t>
+  </si>
+  <si>
+    <t>08/10/2026 22:00:00</t>
   </si>
   <si>
     <t>08/10/2026 14:00:00</t>
@@ -136,70 +187,106 @@
     <t>08/10/2026 15:30:00</t>
   </si>
   <si>
+    <t>08/10/2026 12:30:00</t>
+  </si>
+  <si>
+    <t>09/10/2026 20:30:00</t>
+  </si>
+  <si>
+    <t>09/10/2026 22:00:00</t>
+  </si>
+  <si>
     <t>09/10/2026 14:00:00</t>
   </si>
   <si>
     <t>09/10/2026 15:30:00</t>
   </si>
   <si>
+    <t>09/10/2026 12:30:00</t>
+  </si>
+  <si>
+    <t>02243654</t>
+  </si>
+  <si>
+    <t>Lưu Văn Giang</t>
+  </si>
+  <si>
+    <t>Tăng Cường Sản Xuất</t>
+  </si>
+  <si>
+    <t>10/10/2026 22:00:00</t>
+  </si>
+  <si>
+    <t>11/10/2026 06:00:00</t>
+  </si>
+  <si>
+    <t>10/10/2026 06:00:00</t>
+  </si>
+  <si>
+    <t>10/10/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>02622116</t>
+  </si>
+  <si>
+    <t>Trịnh Nhựt Khánh</t>
+  </si>
+  <si>
+    <t>tăng cường sản xuất</t>
+  </si>
+  <si>
+    <t>02222350</t>
+  </si>
+  <si>
+    <t>Hoàng Văn Nguyên</t>
+  </si>
+  <si>
+    <t>Tăng cường sản xuất</t>
+  </si>
+  <si>
+    <t>02121404</t>
+  </si>
+  <si>
+    <t>Lê Hoàng Minh Tâm</t>
+  </si>
+  <si>
+    <t>02223605</t>
+  </si>
+  <si>
+    <t>Võ Minh Bắc</t>
+  </si>
+  <si>
+    <t>tǎng ca Vân hành máy nghiên</t>
+  </si>
+  <si>
+    <t>12/10/2026 20:30:00</t>
+  </si>
+  <si>
+    <t>12/10/2026 22:00:00</t>
+  </si>
+  <si>
+    <t>12/10/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>12/10/2026 15:30:00</t>
+  </si>
+  <si>
+    <t>13/10/2026 12:30:00</t>
+  </si>
+  <si>
+    <t>13/10/2026 14:00:00</t>
+  </si>
+  <si>
     <t>Chưa duyệt</t>
   </si>
   <si>
-    <t>02644057</t>
-  </si>
-  <si>
-    <t>Phạm Văn Công</t>
-  </si>
-  <si>
-    <t>vận hành máy nghiền</t>
-  </si>
-  <si>
-    <t>05/10/2026 20:30:00</t>
-  </si>
-  <si>
-    <t>05/10/2026 22:00:00</t>
-  </si>
-  <si>
-    <t>06/10/2026 20:30:00</t>
-  </si>
-  <si>
-    <t>06/10/2026 22:00:00</t>
-  </si>
-  <si>
-    <t>07/10/2026 20:30:00</t>
-  </si>
-  <si>
-    <t>07/10/2026 22:00:00</t>
-  </si>
-  <si>
-    <t>08/10/2026 20:30:00</t>
-  </si>
-  <si>
-    <t>08/10/2026 22:00:00</t>
-  </si>
-  <si>
-    <t>02644075</t>
-  </si>
-  <si>
-    <t>Huỳnh Đại Nhân</t>
-  </si>
-  <si>
-    <t xml:space="preserve">vận hành máy nghiền </t>
-  </si>
-  <si>
-    <t>05/10/2026 12:30:00</t>
-  </si>
-  <si>
-    <t>07/10/2026 12:30:00</t>
-  </si>
-  <si>
-    <t>08/10/2026 12:30:00</t>
-  </si>
-  <si>
-    <t>09/10/2026 12:30:00</t>
-  </si>
-  <si>
-    <t>06/10/2026 12:30:00</t>
+    <t>13/10/2026 20:30:00</t>
+  </si>
+  <si>
+    <t>13/10/2026 22:00:00</t>
+  </si>
+  <si>
+    <t>13/10/2026 15:30:00</t>
   </si>
 </sst>
 </file>
@@ -734,10 +821,10 @@
     </row>
     <row r="4" s="2" customFormat="1">
       <c r="A4" s="7" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="C4" s="7" t="s">
         <v>19</v>
@@ -746,7 +833,7 @@
         <v>20</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="F4" s="7" t="s">
         <v>22</v>
@@ -755,19 +842,19 @@
         <v>23</v>
       </c>
       <c r="H4" s="8" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="I4" s="8" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="J4" s="8">
         <v>90</v>
       </c>
       <c r="K4" s="8" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="L4" s="8" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="M4" s="8">
         <v>0</v>
@@ -782,10 +869,10 @@
     </row>
     <row r="5" s="2" customFormat="1">
       <c r="A5" s="7" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="C5" s="7" t="s">
         <v>19</v>
@@ -794,7 +881,7 @@
         <v>20</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="F5" s="7" t="s">
         <v>22</v>
@@ -803,7 +890,7 @@
         <v>23</v>
       </c>
       <c r="H5" s="8" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="I5" s="8" t="s">
         <v>31</v>
@@ -812,7 +899,7 @@
         <v>90</v>
       </c>
       <c r="K5" s="8" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="L5" s="8" t="s">
         <v>31</v>
@@ -830,10 +917,10 @@
     </row>
     <row r="6" s="2" customFormat="1">
       <c r="A6" s="7" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="C6" s="7" t="s">
         <v>19</v>
@@ -842,7 +929,7 @@
         <v>20</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="F6" s="7" t="s">
         <v>22</v>
@@ -851,19 +938,19 @@
         <v>23</v>
       </c>
       <c r="H6" s="8" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="I6" s="8" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="J6" s="8">
         <v>90</v>
       </c>
       <c r="K6" s="8" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="L6" s="8" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="M6" s="8">
         <v>0</v>
@@ -878,10 +965,10 @@
     </row>
     <row r="7" s="2" customFormat="1">
       <c r="A7" s="7" t="s">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="C7" s="7" t="s">
         <v>19</v>
@@ -890,7 +977,7 @@
         <v>20</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="F7" s="7" t="s">
         <v>22</v>
@@ -899,19 +986,19 @@
         <v>23</v>
       </c>
       <c r="H7" s="8" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="I7" s="8" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="J7" s="8">
         <v>90</v>
       </c>
       <c r="K7" s="8" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="L7" s="8" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="M7" s="8">
         <v>0</v>
@@ -926,10 +1013,10 @@
     </row>
     <row r="8" s="2" customFormat="1">
       <c r="A8" s="7" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="C8" s="7" t="s">
         <v>19</v>
@@ -938,7 +1025,7 @@
         <v>20</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="F8" s="7" t="s">
         <v>22</v>
@@ -947,19 +1034,19 @@
         <v>23</v>
       </c>
       <c r="H8" s="8" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="I8" s="8" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="J8" s="8">
         <v>90</v>
       </c>
       <c r="K8" s="8" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="L8" s="8" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="M8" s="8">
         <v>0</v>
@@ -969,15 +1056,15 @@
         <v>26</v>
       </c>
       <c r="P8" s="8" t="s">
-        <v>41</v>
+        <v>27</v>
       </c>
     </row>
     <row r="9" s="2" customFormat="1">
       <c r="A9" s="7" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="C9" s="7" t="s">
         <v>19</v>
@@ -986,7 +1073,7 @@
         <v>20</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="F9" s="7" t="s">
         <v>22</v>
@@ -1022,10 +1109,10 @@
     </row>
     <row r="10" s="2" customFormat="1">
       <c r="A10" s="7" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="C10" s="7" t="s">
         <v>19</v>
@@ -1034,7 +1121,7 @@
         <v>20</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="F10" s="7" t="s">
         <v>22</v>
@@ -1070,10 +1157,10 @@
     </row>
     <row r="11" s="2" customFormat="1">
       <c r="A11" s="7" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="C11" s="7" t="s">
         <v>19</v>
@@ -1082,7 +1169,7 @@
         <v>20</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="F11" s="7" t="s">
         <v>22</v>
@@ -1113,15 +1200,15 @@
         <v>26</v>
       </c>
       <c r="P11" s="8" t="s">
-        <v>41</v>
+        <v>27</v>
       </c>
     </row>
     <row r="12" s="2" customFormat="1">
       <c r="A12" s="7" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="C12" s="7" t="s">
         <v>19</v>
@@ -1130,7 +1217,7 @@
         <v>20</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="F12" s="7" t="s">
         <v>22</v>
@@ -1142,7 +1229,7 @@
         <v>51</v>
       </c>
       <c r="I12" s="8" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="J12" s="8">
         <v>90</v>
@@ -1151,7 +1238,7 @@
         <v>51</v>
       </c>
       <c r="L12" s="8" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="M12" s="8">
         <v>0</v>
@@ -1161,45 +1248,45 @@
         <v>26</v>
       </c>
       <c r="P12" s="8" t="s">
-        <v>41</v>
+        <v>27</v>
       </c>
     </row>
     <row r="13" s="2" customFormat="1">
       <c r="A13" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E13" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="F13" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G13" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="H13" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="I13" s="8" t="s">
         <v>53</v>
-      </c>
-      <c r="B13" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="C13" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="D13" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="E13" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="F13" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="G13" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="H13" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="I13" s="8" t="s">
-        <v>24</v>
       </c>
       <c r="J13" s="8">
         <v>90</v>
       </c>
       <c r="K13" s="8" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="L13" s="8" t="s">
-        <v>24</v>
+        <v>53</v>
       </c>
       <c r="M13" s="8">
         <v>0</v>
@@ -1214,40 +1301,40 @@
     </row>
     <row r="14" s="2" customFormat="1">
       <c r="A14" s="7" t="s">
-        <v>53</v>
+        <v>28</v>
       </c>
       <c r="B14" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E14" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="F14" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G14" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="H14" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="C14" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="D14" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="E14" s="7" t="s">
+      <c r="I14" s="8" t="s">
         <v>55</v>
-      </c>
-      <c r="F14" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="G14" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="H14" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="I14" s="8" t="s">
-        <v>30</v>
       </c>
       <c r="J14" s="8">
         <v>90</v>
       </c>
       <c r="K14" s="8" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="L14" s="8" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="M14" s="8">
         <v>0</v>
@@ -1262,40 +1349,40 @@
     </row>
     <row r="15" s="2" customFormat="1">
       <c r="A15" s="7" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="B15" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="F15" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G15" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="H15" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="I15" s="8" t="s">
         <v>54</v>
-      </c>
-      <c r="C15" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="D15" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="F15" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="G15" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="H15" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="I15" s="8" t="s">
-        <v>37</v>
       </c>
       <c r="J15" s="8">
         <v>90</v>
       </c>
       <c r="K15" s="8" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="L15" s="8" t="s">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="M15" s="8">
         <v>0</v>
@@ -1310,10 +1397,10 @@
     </row>
     <row r="16" s="2" customFormat="1">
       <c r="A16" s="7" t="s">
-        <v>53</v>
+        <v>37</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>54</v>
+        <v>38</v>
       </c>
       <c r="C16" s="7" t="s">
         <v>19</v>
@@ -1322,7 +1409,7 @@
         <v>20</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="F16" s="7" t="s">
         <v>22</v>
@@ -1331,19 +1418,19 @@
         <v>23</v>
       </c>
       <c r="H16" s="8" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="I16" s="8" t="s">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="J16" s="8">
         <v>90</v>
       </c>
       <c r="K16" s="8" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="L16" s="8" t="s">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="M16" s="8">
         <v>0</v>
@@ -1353,15 +1440,15 @@
         <v>26</v>
       </c>
       <c r="P16" s="8" t="s">
-        <v>41</v>
+        <v>27</v>
       </c>
     </row>
     <row r="17" s="2" customFormat="1">
       <c r="A17" s="7" t="s">
-        <v>53</v>
+        <v>28</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>54</v>
+        <v>29</v>
       </c>
       <c r="C17" s="7" t="s">
         <v>19</v>
@@ -1370,7 +1457,7 @@
         <v>20</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="F17" s="7" t="s">
         <v>22</v>
@@ -1379,19 +1466,19 @@
         <v>23</v>
       </c>
       <c r="H17" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="I17" s="8" t="s">
         <v>60</v>
-      </c>
-      <c r="I17" s="8" t="s">
-        <v>28</v>
       </c>
       <c r="J17" s="8">
         <v>90</v>
       </c>
       <c r="K17" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="L17" s="8" t="s">
         <v>60</v>
-      </c>
-      <c r="L17" s="8" t="s">
-        <v>28</v>
       </c>
       <c r="M17" s="8">
         <v>0</v>
@@ -1405,220 +1492,676 @@
       </c>
     </row>
     <row r="18" s="2" customFormat="1">
-      <c r="A18" s="7"/>
-      <c r="B18" s="7"/>
-      <c r="C18" s="7"/>
-      <c r="D18" s="7"/>
-      <c r="E18" s="7"/>
-      <c r="F18" s="7"/>
-      <c r="G18" s="7"/>
-      <c r="H18" s="8"/>
-      <c r="I18" s="8"/>
-      <c r="J18" s="8"/>
-      <c r="K18" s="8"/>
-      <c r="L18" s="8"/>
-      <c r="M18" s="8"/>
+      <c r="A18" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D18" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E18" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="F18" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G18" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="H18" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="I18" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="J18" s="8">
+        <v>90</v>
+      </c>
+      <c r="K18" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="L18" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="M18" s="8">
+        <v>0</v>
+      </c>
       <c r="N18" s="7"/>
-      <c r="O18" s="8"/>
-      <c r="P18" s="8"/>
+      <c r="O18" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="P18" s="8" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="19" s="2" customFormat="1">
-      <c r="A19" s="7"/>
-      <c r="B19" s="7"/>
-      <c r="C19" s="7"/>
-      <c r="D19" s="7"/>
-      <c r="E19" s="7"/>
-      <c r="F19" s="7"/>
-      <c r="G19" s="7"/>
-      <c r="H19" s="8"/>
-      <c r="I19" s="8"/>
-      <c r="J19" s="8"/>
-      <c r="K19" s="8"/>
-      <c r="L19" s="8"/>
-      <c r="M19" s="8"/>
+      <c r="A19" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D19" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E19" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="F19" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G19" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="H19" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="I19" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="J19" s="8">
+        <v>480</v>
+      </c>
+      <c r="K19" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="L19" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="M19" s="8">
+        <v>0</v>
+      </c>
       <c r="N19" s="7"/>
-      <c r="O19" s="8"/>
-      <c r="P19" s="8"/>
+      <c r="O19" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="P19" s="8" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="20" s="2" customFormat="1">
-      <c r="A20" s="7"/>
-      <c r="B20" s="7"/>
-      <c r="C20" s="7"/>
-      <c r="D20" s="7"/>
-      <c r="E20" s="7"/>
-      <c r="F20" s="7"/>
-      <c r="G20" s="7"/>
-      <c r="H20" s="8"/>
-      <c r="I20" s="8"/>
-      <c r="J20" s="8"/>
-      <c r="K20" s="8"/>
-      <c r="L20" s="8"/>
-      <c r="M20" s="8"/>
+      <c r="A20" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D20" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E20" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="F20" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G20" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="H20" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="I20" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="J20" s="8">
+        <v>480</v>
+      </c>
+      <c r="K20" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="L20" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="M20" s="8">
+        <v>0</v>
+      </c>
       <c r="N20" s="7"/>
-      <c r="O20" s="8"/>
-      <c r="P20" s="8"/>
+      <c r="O20" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="P20" s="8" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="21" s="2" customFormat="1">
-      <c r="A21" s="7"/>
-      <c r="B21" s="7"/>
-      <c r="C21" s="7"/>
-      <c r="D21" s="7"/>
-      <c r="E21" s="7"/>
-      <c r="F21" s="7"/>
-      <c r="G21" s="7"/>
-      <c r="H21" s="8"/>
-      <c r="I21" s="8"/>
-      <c r="J21" s="8"/>
-      <c r="K21" s="8"/>
-      <c r="L21" s="8"/>
-      <c r="M21" s="8"/>
+      <c r="A21" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="C21" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D21" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E21" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="F21" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G21" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="H21" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="I21" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="J21" s="8">
+        <v>480</v>
+      </c>
+      <c r="K21" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="L21" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="M21" s="8">
+        <v>0</v>
+      </c>
       <c r="N21" s="7"/>
-      <c r="O21" s="8"/>
-      <c r="P21" s="8"/>
+      <c r="O21" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="P21" s="8" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="22" s="2" customFormat="1">
-      <c r="A22" s="7"/>
-      <c r="B22" s="7"/>
-      <c r="C22" s="7"/>
-      <c r="D22" s="7"/>
-      <c r="E22" s="7"/>
-      <c r="F22" s="7"/>
-      <c r="G22" s="7"/>
-      <c r="H22" s="8"/>
-      <c r="I22" s="8"/>
-      <c r="J22" s="8"/>
-      <c r="K22" s="8"/>
-      <c r="L22" s="8"/>
-      <c r="M22" s="8"/>
+      <c r="A22" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="B22" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="C22" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D22" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E22" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="F22" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G22" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="H22" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="I22" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="J22" s="8">
+        <v>480</v>
+      </c>
+      <c r="K22" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="L22" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="M22" s="8">
+        <v>0</v>
+      </c>
       <c r="N22" s="7"/>
-      <c r="O22" s="8"/>
-      <c r="P22" s="8"/>
+      <c r="O22" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="P22" s="8" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="23" s="2" customFormat="1">
-      <c r="A23" s="7"/>
-      <c r="B23" s="7"/>
-      <c r="C23" s="7"/>
-      <c r="D23" s="7"/>
-      <c r="E23" s="7"/>
-      <c r="F23" s="7"/>
-      <c r="G23" s="7"/>
-      <c r="H23" s="8"/>
-      <c r="I23" s="8"/>
-      <c r="J23" s="8"/>
-      <c r="K23" s="8"/>
-      <c r="L23" s="8"/>
-      <c r="M23" s="8"/>
+      <c r="A23" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="B23" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C23" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D23" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E23" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="F23" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G23" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="H23" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="I23" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="J23" s="8">
+        <v>480</v>
+      </c>
+      <c r="K23" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="L23" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="M23" s="8">
+        <v>0</v>
+      </c>
       <c r="N23" s="7"/>
-      <c r="O23" s="8"/>
-      <c r="P23" s="8"/>
+      <c r="O23" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="P23" s="8" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="24" s="2" customFormat="1">
-      <c r="A24" s="7"/>
-      <c r="B24" s="7"/>
-      <c r="C24" s="7"/>
-      <c r="D24" s="7"/>
-      <c r="E24" s="7"/>
-      <c r="F24" s="7"/>
-      <c r="G24" s="7"/>
-      <c r="H24" s="8"/>
-      <c r="I24" s="8"/>
-      <c r="J24" s="8"/>
-      <c r="K24" s="8"/>
-      <c r="L24" s="8"/>
-      <c r="M24" s="8"/>
+      <c r="A24" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="B24" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="C24" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D24" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E24" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="F24" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G24" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="H24" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="I24" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="J24" s="8">
+        <v>480</v>
+      </c>
+      <c r="K24" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="L24" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="M24" s="8">
+        <v>0</v>
+      </c>
       <c r="N24" s="7"/>
-      <c r="O24" s="8"/>
-      <c r="P24" s="8"/>
+      <c r="O24" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="P24" s="8" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="25" s="2" customFormat="1">
-      <c r="A25" s="7"/>
-      <c r="B25" s="7"/>
-      <c r="C25" s="7"/>
-      <c r="D25" s="7"/>
-      <c r="E25" s="7"/>
-      <c r="F25" s="7"/>
-      <c r="G25" s="7"/>
-      <c r="H25" s="8"/>
-      <c r="I25" s="8"/>
-      <c r="J25" s="8"/>
-      <c r="K25" s="8"/>
-      <c r="L25" s="8"/>
-      <c r="M25" s="8"/>
+      <c r="A25" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="B25" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="C25" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D25" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E25" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="F25" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G25" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="H25" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="I25" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="J25" s="8">
+        <v>480</v>
+      </c>
+      <c r="K25" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="L25" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="M25" s="8">
+        <v>0</v>
+      </c>
       <c r="N25" s="7"/>
-      <c r="O25" s="8"/>
-      <c r="P25" s="8"/>
+      <c r="O25" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="P25" s="8" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="26" s="2" customFormat="1">
-      <c r="A26" s="7"/>
-      <c r="B26" s="7"/>
-      <c r="C26" s="7"/>
-      <c r="D26" s="7"/>
-      <c r="E26" s="7"/>
-      <c r="F26" s="7"/>
-      <c r="G26" s="7"/>
-      <c r="H26" s="8"/>
-      <c r="I26" s="8"/>
-      <c r="J26" s="8"/>
-      <c r="K26" s="8"/>
-      <c r="L26" s="8"/>
-      <c r="M26" s="8"/>
+      <c r="A26" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="B26" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="C26" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D26" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E26" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="F26" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G26" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="H26" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="I26" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="J26" s="8">
+        <v>480</v>
+      </c>
+      <c r="K26" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="L26" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="M26" s="8">
+        <v>0</v>
+      </c>
       <c r="N26" s="7"/>
-      <c r="O26" s="8"/>
-      <c r="P26" s="8"/>
+      <c r="O26" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="P26" s="8" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="27" s="2" customFormat="1">
-      <c r="A27" s="7"/>
-      <c r="B27" s="7"/>
-      <c r="C27" s="7"/>
-      <c r="D27" s="7"/>
-      <c r="E27" s="7"/>
-      <c r="F27" s="7"/>
-      <c r="G27" s="7"/>
-      <c r="H27" s="8"/>
-      <c r="I27" s="8"/>
-      <c r="J27" s="8"/>
-      <c r="K27" s="8"/>
-      <c r="L27" s="8"/>
-      <c r="M27" s="8"/>
+      <c r="A27" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="B27" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="C27" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D27" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="F27" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G27" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="H27" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="I27" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="J27" s="8">
+        <v>90</v>
+      </c>
+      <c r="K27" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="L27" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="M27" s="8">
+        <v>0</v>
+      </c>
       <c r="N27" s="7"/>
-      <c r="O27" s="8"/>
-      <c r="P27" s="8"/>
+      <c r="O27" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="P27" s="8" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="28" s="2" customFormat="1">
-      <c r="A28" s="7"/>
-      <c r="B28" s="7"/>
-      <c r="C28" s="7"/>
-      <c r="D28" s="7"/>
-      <c r="E28" s="7"/>
-      <c r="F28" s="7"/>
-      <c r="G28" s="7"/>
-      <c r="H28" s="8"/>
-      <c r="I28" s="8"/>
-      <c r="J28" s="8"/>
-      <c r="K28" s="8"/>
-      <c r="L28" s="8"/>
-      <c r="M28" s="8"/>
+      <c r="A28" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="B28" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C28" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D28" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="F28" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G28" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="H28" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="I28" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="J28" s="8">
+        <v>90</v>
+      </c>
+      <c r="K28" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="L28" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="M28" s="8">
+        <v>0</v>
+      </c>
       <c r="N28" s="7"/>
-      <c r="O28" s="8"/>
-      <c r="P28" s="8"/>
+      <c r="O28" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="P28" s="8" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="29" s="2" customFormat="1">
-      <c r="A29" s="7"/>
-      <c r="B29" s="7"/>
-      <c r="C29" s="7"/>
-      <c r="D29" s="7"/>
-      <c r="E29" s="7"/>
-      <c r="F29" s="7"/>
-      <c r="G29" s="7"/>
-      <c r="H29" s="8"/>
-      <c r="I29" s="8"/>
-      <c r="J29" s="8"/>
-      <c r="K29" s="8"/>
-      <c r="L29" s="8"/>
-      <c r="M29" s="8"/>
+      <c r="A29" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="B29" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="C29" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D29" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E29" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="F29" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G29" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="H29" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="I29" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="J29" s="8">
+        <v>90</v>
+      </c>
+      <c r="K29" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="L29" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="M29" s="8">
+        <v>0</v>
+      </c>
       <c r="N29" s="7"/>
-      <c r="O29" s="8"/>
-      <c r="P29" s="8"/>
+      <c r="O29" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="P29" s="8" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="F30" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G30" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H30" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="I30" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="J30" s="4">
+        <v>90</v>
+      </c>
+      <c r="K30" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="L30" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="M30" s="4">
+        <v>0</v>
+      </c>
+      <c r="N30" s="3"/>
+      <c r="O30" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="P30" s="4" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="F31" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G31" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H31" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="I31" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="J31" s="4">
+        <v>90</v>
+      </c>
+      <c r="K31" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="L31" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="M31" s="4">
+        <v>0</v>
+      </c>
+      <c r="N31" s="3"/>
+      <c r="O31" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="P31" s="4" t="s">
+        <v>86</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/data/hrm_sync_actual_2.xlsx
+++ b/data/hrm_sync_actual_2.xlsx
@@ -277,9 +277,6 @@
     <t>13/10/2026 14:00:00</t>
   </si>
   <si>
-    <t>Chưa duyệt</t>
-  </si>
-  <si>
     <t>13/10/2026 20:30:00</t>
   </si>
   <si>
@@ -287,6 +284,75 @@
   </si>
   <si>
     <t>13/10/2026 15:30:00</t>
+  </si>
+  <si>
+    <t>tăng ca Vân hành máy nghiêń</t>
+  </si>
+  <si>
+    <t>14/10/2026 20:30:00</t>
+  </si>
+  <si>
+    <t>14/10/2026 22:00:00</t>
+  </si>
+  <si>
+    <t>14/10/2026 12:30:00</t>
+  </si>
+  <si>
+    <t>14/10/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>14/10/2026 15:30:00</t>
+  </si>
+  <si>
+    <t>15/10/2026 12:30:00</t>
+  </si>
+  <si>
+    <t>15/10/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>15/10/2026 20:30:00</t>
+  </si>
+  <si>
+    <t>15/10/2026 22:00:00</t>
+  </si>
+  <si>
+    <t>15/10/2026 15:30:00</t>
+  </si>
+  <si>
+    <t>16/10/2026 12:30:00</t>
+  </si>
+  <si>
+    <t>16/10/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>16/10/2026 20:30:00</t>
+  </si>
+  <si>
+    <t>16/10/2026 22:00:00</t>
+  </si>
+  <si>
+    <t>17/10/2026 22:00:00</t>
+  </si>
+  <si>
+    <t>18/10/2026 06:00:00</t>
+  </si>
+  <si>
+    <t>02223526</t>
+  </si>
+  <si>
+    <t>Nguyễn Thiên Phú</t>
+  </si>
+  <si>
+    <t>17/10/2026 06:00:00</t>
+  </si>
+  <si>
+    <t>17/10/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>Vận hành máy nghiền</t>
+  </si>
+  <si>
+    <t>vận chuyển nguyên vật liệu</t>
   </si>
 </sst>
 </file>
@@ -2064,7 +2130,7 @@
         <v>26</v>
       </c>
       <c r="P29" s="8" t="s">
-        <v>86</v>
+        <v>27</v>
       </c>
     </row>
     <row r="30">
@@ -2090,19 +2156,19 @@
         <v>23</v>
       </c>
       <c r="H30" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="I30" s="4" t="s">
         <v>87</v>
-      </c>
-      <c r="I30" s="4" t="s">
-        <v>88</v>
       </c>
       <c r="J30" s="4">
         <v>90</v>
       </c>
       <c r="K30" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="L30" s="4" t="s">
         <v>87</v>
-      </c>
-      <c r="L30" s="4" t="s">
-        <v>88</v>
       </c>
       <c r="M30" s="4">
         <v>0</v>
@@ -2112,7 +2178,7 @@
         <v>26</v>
       </c>
       <c r="P30" s="4" t="s">
-        <v>86</v>
+        <v>27</v>
       </c>
     </row>
     <row r="31">
@@ -2141,7 +2207,7 @@
         <v>85</v>
       </c>
       <c r="I31" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="J31" s="4">
         <v>90</v>
@@ -2150,7 +2216,7 @@
         <v>85</v>
       </c>
       <c r="L31" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="M31" s="4">
         <v>0</v>
@@ -2160,7 +2226,775 @@
         <v>26</v>
       </c>
       <c r="P31" s="4" t="s">
-        <v>86</v>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H32" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="I32" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="J32" s="4">
+        <v>90</v>
+      </c>
+      <c r="K32" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="L32" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="M32" s="4">
+        <v>0</v>
+      </c>
+      <c r="N32" s="3"/>
+      <c r="O32" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="P32" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="F33" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G33" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H33" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="I33" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="J33" s="4">
+        <v>90</v>
+      </c>
+      <c r="K33" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="L33" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="M33" s="4">
+        <v>0</v>
+      </c>
+      <c r="N33" s="3"/>
+      <c r="O33" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="P33" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="F34" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G34" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H34" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="I34" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="J34" s="4">
+        <v>90</v>
+      </c>
+      <c r="K34" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="L34" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="M34" s="4">
+        <v>0</v>
+      </c>
+      <c r="N34" s="3"/>
+      <c r="O34" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="P34" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="F35" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G35" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H35" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="I35" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="J35" s="4">
+        <v>90</v>
+      </c>
+      <c r="K35" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="L35" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="M35" s="4">
+        <v>0</v>
+      </c>
+      <c r="N35" s="3"/>
+      <c r="O35" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="P35" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E36" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="F36" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G36" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H36" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="I36" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="J36" s="4">
+        <v>90</v>
+      </c>
+      <c r="K36" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="L36" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="M36" s="4">
+        <v>0</v>
+      </c>
+      <c r="N36" s="3"/>
+      <c r="O36" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="P36" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E37" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="F37" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G37" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H37" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="I37" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="J37" s="4">
+        <v>90</v>
+      </c>
+      <c r="K37" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="L37" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="M37" s="4">
+        <v>0</v>
+      </c>
+      <c r="N37" s="3"/>
+      <c r="O37" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="P37" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="F38" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G38" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H38" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="I38" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="J38" s="4">
+        <v>90</v>
+      </c>
+      <c r="K38" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="L38" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="M38" s="4">
+        <v>0</v>
+      </c>
+      <c r="N38" s="3"/>
+      <c r="O38" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="P38" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D39" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E39" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="F39" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G39" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H39" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="I39" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="J39" s="4">
+        <v>90</v>
+      </c>
+      <c r="K39" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="L39" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="M39" s="4">
+        <v>0</v>
+      </c>
+      <c r="N39" s="3"/>
+      <c r="O39" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="P39" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D40" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E40" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="F40" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G40" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H40" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="I40" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="J40" s="4">
+        <v>480</v>
+      </c>
+      <c r="K40" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="L40" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="M40" s="4">
+        <v>0</v>
+      </c>
+      <c r="N40" s="3"/>
+      <c r="O40" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="P40" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D41" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="F41" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G41" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H41" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="I41" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="J41" s="4">
+        <v>480</v>
+      </c>
+      <c r="K41" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="L41" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="M41" s="4">
+        <v>0</v>
+      </c>
+      <c r="N41" s="3"/>
+      <c r="O41" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="P41" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D42" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E42" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="F42" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G42" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H42" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="I42" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="J42" s="4">
+        <v>480</v>
+      </c>
+      <c r="K42" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="L42" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="M42" s="4">
+        <v>0</v>
+      </c>
+      <c r="N42" s="3"/>
+      <c r="O42" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="P42" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D43" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="F43" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G43" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H43" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="I43" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="J43" s="4">
+        <v>480</v>
+      </c>
+      <c r="K43" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="L43" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="M43" s="4">
+        <v>0</v>
+      </c>
+      <c r="N43" s="3"/>
+      <c r="O43" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="P43" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D44" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H44" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="I44" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="J44" s="4">
+        <v>480</v>
+      </c>
+      <c r="K44" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="L44" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="M44" s="4">
+        <v>0</v>
+      </c>
+      <c r="N44" s="3"/>
+      <c r="O44" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="P44" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C45" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D45" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H45" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="I45" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="J45" s="4">
+        <v>480</v>
+      </c>
+      <c r="K45" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="L45" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="M45" s="4">
+        <v>0</v>
+      </c>
+      <c r="N45" s="3"/>
+      <c r="O45" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="P45" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D46" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E46" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="F46" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G46" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H46" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="I46" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="J46" s="4">
+        <v>480</v>
+      </c>
+      <c r="K46" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="L46" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="M46" s="4">
+        <v>0</v>
+      </c>
+      <c r="N46" s="3"/>
+      <c r="O46" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="P46" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="C47" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D47" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H47" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="I47" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="J47" s="4">
+        <v>480</v>
+      </c>
+      <c r="K47" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="L47" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="M47" s="4">
+        <v>0</v>
+      </c>
+      <c r="N47" s="3"/>
+      <c r="O47" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="P47" s="4" t="s">
+        <v>27</v>
       </c>
     </row>
   </sheetData>
